--- a/data/exports/validation_study/packets/week-2/packet-3.xlsx
+++ b/data/exports/validation_study/packets/week-2/packet-3.xlsx
@@ -544,7 +544,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>2. 'techniques' sheet - the 11 attacks, mechanisms and defenses we recorded from your papers.</t>
+          <t>2. 'techniques' sheet - the 13 attacks, mechanisms and defenses we recorded from your papers.</t>
         </is>
       </c>
     </row>
@@ -2284,15 +2284,15 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>AAAI</t>
+          <t>USENIX Security</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Seeing through the Conflict - Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation.pdf</t>
+          <t>data/papers/TracLLM - A Generic Framework for Attributing Long Context LLMs.pdf</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -2312,11 +2312,11 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -2324,11 +2324,11 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents.pdf</t>
+          <t>data/papers/Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection.pdf</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -2348,15 +2348,15 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ACM International Conference on the Foundations of Software Engineering</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Evaluating Privilege Usage of Agents with Real-World Tools.pdf</t>
+          <t>data/papers/MemVenom - Triggered Poisoning of Multimodal Memories in Web Agents.pdf</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -2368,15 +2368,15 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>NeurIPS</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>data/papers/KScope - A Framework for Characterizing the Knowledge Status of Language Models.pdf</t>
+          <t>data/papers/Document-Authored Control-Signal Impersonation - A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries.pdf</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -2396,23 +2396,23 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>IEEE Transactions on Information Forensics and Security</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>data/papers/The Surface You Test Is Not the Surface That Breaks.pdf</t>
+          <t>data/papers/Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools.pdf</t>
         </is>
       </c>
       <c r="G6" s="5" t="n"/>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Securing AI Agents Against Prompt Injection Attacks.pdf</t>
+          <t>data/papers/Parameters vs. Context - Fine-Grained Control of Knowledge Reliance in Language Models.pdf</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -2452,23 +2452,19 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v>2026</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>arXiv</t>
-        </is>
-      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>data/papers/PRIMA - Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback.pdf</t>
+          <t>data/papers/End-to-End Context Compression at Scale.pdf</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -2480,7 +2476,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -2496,7 +2492,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>data/papers/System-Level Defense against Indirect Prompt Injection Attacks - An Information Flow Control Perspective.pdf</t>
+          <t>data/papers/RAG-Modulo - Solving Sequential Tasks using Experience, Critics, and Language Models.pdf</t>
         </is>
       </c>
       <c r="G9" s="5" t="n"/>
@@ -2508,23 +2504,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>World Journal of Advanced Research and Reviews</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>data/papers/LLM integration and the zero trust perimeter - A systematic review of trust enforcement failures and defensive architectures.pdf</t>
+          <t>data/papers/From Prompt Injections to SQL Injection Attacks - How Protected is Your LLM-Integrated Web Application.pdf</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -2536,19 +2532,23 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+        <v>2025</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>ACL</t>
+        </is>
+      </c>
       <c r="E11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Learning What Not to Forget - Long-Horizon Agent Memory from a Few Kilobytes of Learning.pdf</t>
+          <t>data/papers/MultiChallenge - A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs.pdf</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -2560,19 +2560,23 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+        <v>2026</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>arXiv</t>
+        </is>
+      </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Bypassing LLM Guardrails - An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems.pdf</t>
+          <t>data/papers/The Evolution of Tool Use in LLM Agents - From Single-Tool Call to Multi-Tool Orchestration.pdf</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -2584,23 +2588,23 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Information Forensics and Security</t>
+          <t>arXiv</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>data/papers/Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools.pdf</t>
+          <t>data/papers/SoK - The Attack Surface of Agentic AI - Tools, and Autonomy.pdf</t>
         </is>
       </c>
       <c r="G13" s="5" t="n"/>
@@ -2612,19 +2616,23 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="2" t="n"/>
+        <v>2024</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>ICRA</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>data/papers/TRACE - Trajectory Risk-Aware Compression for Long-Horizon Agent Safety.pdf</t>
+          <t>data/papers/ReMEmbR - Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation.pdf</t>
         </is>
       </c>
       <c r="G14" s="5" t="n"/>
@@ -2636,7 +2644,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
@@ -2652,7 +2660,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>data/papers/CLIOPATRA - Extracting Private Information from LLM Insights.pdf</t>
+          <t>data/papers/Slipstream - Trajectory-Grounded Compaction Validation for Long-Horizon Agents.pdf</t>
         </is>
       </c>
       <c r="G15" s="5" t="n"/>
@@ -2664,23 +2672,23 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>arXiv</t>
+          <t>BigData Congress [Services Society]</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>data/papers/PACEvolve - Enabling Long-Horizon Progress-Aware Consistent Evolution.pdf</t>
+          <t>data/papers/AutoRed - Automated Attack Scenario Generation Framework for Red Teaming of LLMs.pdf</t>
         </is>
       </c>
       <c r="G16" s="5" t="n"/>
@@ -2764,7 +2772,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2787,7 +2795,7 @@
       <c r="H2" s="5" t="n"/>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2805,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2812,7 +2820,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F3" s="5" t="n"/>
@@ -2820,7 +2828,7 @@
       <c r="H3" s="5" t="n"/>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2838,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2853,7 +2861,7 @@
       <c r="H4" s="5" t="n"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2871,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2886,7 +2894,7 @@
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2904,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -2919,7 +2927,7 @@
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2937,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2944,7 +2952,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="F7" s="5" t="n"/>
@@ -2952,7 +2960,7 @@
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -2962,7 +2970,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2977,7 +2985,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F8" s="5" t="n"/>
@@ -2985,7 +2993,7 @@
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3003,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3018,7 +3026,7 @@
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3036,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3051,7 +3059,7 @@
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3069,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3084,7 +3092,7 @@
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3102,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3117,7 +3125,7 @@
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3135,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3142,7 +3150,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>No artifact release is mentioned anywhere in the paper. There is no GitHub/code link, no dataset-release URL, and no statement of intent to release code, data, or model checkpoints (including the paper's newly constructed Wikidata-Conflict-5K, ConflictTQA, and ConflictPQA datasets).</t>
+          <t>Code and data are publicly released at https://github.com/Wang-Yanting/TracLLM, with the paper explicitly committing (Section 8, 'Open Science') to release code and datasets with documentation for replication, and to participate in artifact evaluation.</t>
         </is>
       </c>
       <c r="F13" s="5" t="n"/>
@@ -3150,7 +3158,7 @@
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3168,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3175,7 +3183,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>TCR is evaluated with three open-weight LLM backbones behind a shared BM25-to-Contriever retrieval pipeline: Llama-3-Instruct-8B (primary backbone), Llama-3-13B, and Qwen3-8B. Conflict detection uses dual contrastive encoders (semantic encoder and factual encoder) built on the SFR retrieval model, and two sentence-embedding models (all-MiniLM-L6-v2, 384-d/6 layers, and E5-large-v2, 1024-d/24 layers) are used in an exploratory probing analysis of embedding structure.</t>
+          <t>Llama-3.1-8B-Instruct is the default LLM; additional experiments evaluate Llama-3.1-70B, Qwen-1.5-7B, Qwen-2-7B, Mistral-7B, and GPT-4o-mini. Self-Citation baselines are also tested with a more powerful LLM (GPT-4o) as the citing model, and embeddings for a semantic-similarity baseline use OpenAI's text-embedding-ada-002.</t>
         </is>
       </c>
       <c r="F14" s="5" t="n"/>
@@ -3183,7 +3191,7 @@
       <c r="H14" s="5" t="n"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3201,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3208,7 +3216,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Evaluation spans three groups of datasets: (i) conflict detection on the authors' own Wikidata-Conflict-5K (5k factual triples from Wikidata expanded via GPT-4o into paraphrase, irrelevant, and conflicting statement variants); (ii) knowledge-intensive QA with controlled context on two newly constructed datasets, ConflictTQA (TriviaQA-based) and ConflictPQA (PopQA-based), each pairing questions with golden, irrelevant, or conflicting context; and (iii) real-world RAG evaluation on KILT (Natural Questions, HotpotQA, FEVER), ConflictBank (2024), and a single-document Natural Questions setting restricted to the top-1 Google result.</t>
+          <t>For prompt-injection-attack forensics: three long-context understanding benchmarks from LongBench -- NarrativeQA (long stories, ~18,409 words/doc), MuSiQue (multi-hop Wikipedia-paragraph QA, ~11,214 words/doc), and QMSum (meeting-transcript summarization, ~10,614 words/doc), each with 200 document-query pairs (100 used per dataset), documents split into 100-word passages as individual texts. For knowledge-corruption-attack forensics: NQ, HotpotQA, and MS-MARCO knowledge databases (2.68M-8.84M texts) attacked via PoisonedRAG (black-box and white-box) and additional attacks against RAG systems and LLM agents (e.g., AgentPoison-style attacks), covering 13 total attack variants across the evaluation.</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -3216,7 +3224,7 @@
       <c r="H15" s="5" t="n"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3234,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3241,7 +3249,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>TCR (Transparent Conflict Resolution) improves conflict-detection F1/AUROC over the best prior method (IRCAN) and achieves the best result in 22 of 24 evaluation cells on ConflictTQA/ConflictPQA, improving knowledge-gap recovery rate (KGRR) by +21.4 points and reducing misleading-context override rate (MCOR) by -29.3 points versus a plain prompting baseline, while adding only 0.3% extra parameters (21M) and retaining 94% of vanilla decoding throughput (26.7 vs 28.3 tokens/s). Under 30% distractor-noise injection, TCR loses only 7.2 EM points (2.3 points less than the RAAT baseline) and attains the best cross-domain transfer F1 (55.8/52.7 on biomedical/financial QA). On real-world single-document Natural Questions, TCR outperforms specialized pipelines without any fine-tuning, beating Astute RAG by +3.6 points and Self-Route by +6.1 points, with the largest backbone-specific gain on Qwen3-8B (+4.0 points). Conflict scores correlate with human judgments at rho=0.69 (Krippendorff kappa=0.66 on 300 annotated queries), and an ablation shows removing signal integration collapses performance by 53-55 percentage points, while removing self-answerability or fixing the dynamic SNR weighting degrades results by 17-26 points, confirming all three components (dual encoders, self-answerability, adaptive weighting) are necessary.</t>
+          <t>On the default Llama-3.1-8B-Instruct setting, TracLLM matches or exceeds the best baseline on every dataset for both attack types: for prompt injection (Table 1a), TracLLM achieves precision/recall of 0.94/0.77 (MuSiQue), 0.96/0.84 (NarrativeQA), and 0.98/0.77 (QMSum), matching or slightly exceeding STC (which is otherwise competitive only because the injected instruction is a single self-contained text) while vastly outperforming Shapley (0.68-0.79 precision) and LIME/Context-Cite (0.72-0.90 precision) at similar or lower computational cost (e.g., 403.7-644.7s for TracLLM vs. up to 1043.2s for Shapley); Self-Citation (0.16-0.25 recall) and Gradient (0.04-0.08 precision) perform far worse, with Self-Citation shown to be misled by malicious instructions that manipulate which texts an LLM claims to cite. For knowledge corruption attacks via PoisonedRAG (Table 1b), TracLLM achieves 0.89/0.89 (NQ), 0.80/0.80 (HotpotQA), and 0.78/0.79 (MS-MARCO) precision/recall, again the best or tied-best among all baselines, and as a forensic tool TracLLM identifies 89% of malicious texts injected by PoisonedRAG on the NQ dataset (matching the abstract's headline claim). Ablations show TracLLM's advantage over STC grows substantially when multiple malicious texts must jointly combine to produce the harmful output (i.e., when no single injected text alone is sufficient), which is exactly the scenario STC's single-text-contribution design cannot handle. TracLLM is shown to be largely insensitive to hyperparameter choices (permutation counts, denoising fraction beta, ensemble configuration) across extensive ablations, is effective across all 6 evaluated LLMs and against all 13 evaluated attack variants, and generalizes to a real-world case study identifying the specific joke Reddit comment responsible for Google Search AI Overviews' erroneous 'add glue to pizza' answer. A theoretical analysis (Proposition 1) proves that, under certain assumptions, TracLLM with Shapley-based scoring can provably identify the texts responsible for an LLM's output, implying it is non-trivial for an adaptive attacker to simultaneously achieve a successful attack while evading TracLLM as a forensic tool.</t>
         </is>
       </c>
       <c r="F16" s="5" t="n"/>
@@ -3249,7 +3257,7 @@
       <c r="H16" s="5" t="n"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3259,7 +3267,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3274,7 +3282,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Six published methods are compared: Prompt (plain prompting baseline), KAFT, IRCAN, RAAT (adversarial-noise-robust training), Parenting, and Astute RAG, plus the CD2 contrastive-decoding strategy and, for the real-world NQ setting, InstructRAG and Self-Route. Four ablations of TCR (removing semantic encoder, removing factual encoder, removing SNR-based dynamic weighting in favor of a fixed scalar, and removing signal integration/hard-prompt variant) and three hybrid variants (TCR+CD2, TCR+IRCAN, TCR+RAAT) test plug-and-play compatibility with existing methods.</t>
+          <t>Single Text Contribution (STC, using each individual text alone as context), Leave-One-Out (LOO, removing each text and measuring probability drop), Shapley value-based methods (Monte Carlo-sampled, with permutation counts tuned to match TracLLM's computational cost for fairness), LIME/Context-Cite (Cohen-Wang et al.'s NeurIPS'24 LIME extension for context traceback, using its open-source implementation with a matched perturbation budget), Self-Citation (prompting the LLM itself to cite supporting texts), Gradient-based attribution (L1-norm of per-token embedding gradients), and an additional semantic-similarity baseline (cosine similarity via text-embedding-ada-002) introduced in the Discussion section as a simple alternative shown to be suboptimal (0.72 precision on MuSiQue vs. TracLLM's 0.94).</t>
         </is>
       </c>
       <c r="F17" s="5" t="n"/>
@@ -3282,7 +3290,7 @@
       <c r="H17" s="5" t="n"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3300,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3307,7 +3315,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a knowledge-conflict-resolution and RAG-faithfulness paper, not a security/attack paper. The incidental failure mode of interest is knowledge conflict itself: LLMs either over-trusting noisy or misleading retrieved context and overriding correct internal (parametric) knowledge, or under-trusting relevant retrieved context and failing to close genuine knowledge gaps in internal memory, both of which the paper frames as arising from entangled semantic-relevance and factual-consistency signals that current RAG systems cannot disentangle.</t>
+          <t>N/A - non-adversarial in the sense that TracLLM is a defensive/forensic attribution tool rather than an attack, but it is explicitly designed and evaluated against an adversarial threat model: an attacker who injects malicious text into a long-context LLM's input -- either via prompt injection (directly embedding an adversarial instruction like 'When the query is [query], output [incorrect answer]' into the context) or via knowledge corruption/RAG poisoning attacks (e.g., PoisonedRAG, injecting malicious texts into a RAG system's knowledge database or an LLM agent's memory so that retrieval surfaces attacker-chosen content) -- with the goal of causing the LLM to generate an attacker-desired, incorrect, or harmful output. TracLLM's role is post-attack forensic analysis: given an already-compromised output, it must trace back through the (potentially hundreds-of-texts-long) context to identify which specific texts caused the compromise. The paper's theoretical analysis further considers an adaptive attacker who is aware that TracLLM might be used for post-attack forensics and tries to craft attacks that evade detection while still succeeding, proving (under stated assumptions) that this joint objective is provably difficult to achieve against TracLLM's Shapley-based variant.</t>
         </is>
       </c>
       <c r="F18" s="5" t="n"/>
@@ -3315,7 +3323,7 @@
       <c r="H18" s="5" t="n"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3333,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3340,7 +3348,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations.' The Conclusion is brief and forward-looking rather than self-critical, stating only that the authors 'plan to extend it to multimodal and federated settings,' which implicitly acknowledges the current method is confined to single-modality, non-federated text-based RAG settings. No other explicit caveats, failure-mode discussion beyond the interpretability analysis (e.g., backbone-specific calibration differences between Llama and Qwen noted as a 'diagnostic tool for future alignment work' rather than a limitation), or negative results are discussed.</t>
+          <t>The paper has an explicit 'Discussion and Limitation' section (Section 5) preceding the Conclusion, identifying four concrete limitations/scope boundaries. First, efficiency: although TracLLM substantially improves on Shapley's cost, it 'still requires non-trivial computation time,' making it suited to latency-tolerant applications like post-attack forensic analysis and system debugging rather than real-time use cases, with further efficiency optimization left as future work. Second, traceback to LLM's own knowledge: the current framework only attributes outputs to context texts, but an LLM's output may partly stem from its own pretrained parametric knowledge rather than the provided context; the authors sketch a possible extension (comparing the conditional probability of the output with vs. without any context, and potentially tracing further back into pretraining data) but leave this as future work. Third, long outputs: for applications where the LLM's output itself is very long, the current framework is not directly demonstrated at scale, though the authors suggest a workaround of decomposing long outputs into individual factual statements before applying TracLLM to each. Fourth, adaptive attacks: while Proposition 1 provides a theoretical guarantee making it 'non-trivial' for an attacker to simultaneously succeed and evade TracLLM under certain stated assumptions, this is a conditional (assumption-dependent) result rather than an unconditional guarantee, and the empirical adaptive-attack evaluation is limited to the 13 tested attack variants rather than an exhaustive adversarial search. The Conclusion additionally flags extending TracLLM to multi-modal LLMs as future work not covered by the current text-only framework.</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -3348,7 +3356,7 @@
       <c r="H19" s="5" t="n"/>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3366,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3373,7 +3381,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>TCR (Transparent Conflict Resolution) is a lightweight, plug-and-play framework for making RAG systems' internal-versus-external knowledge conflict resolution both observable and controllable. The method rests on an exploratory finding that off-the-shelf sentence embeddings entangle 'what a sentence is about' (semantic meaning) with 'whether its claim is true' (factual validity), and that a single linear probe can cleanly separate these into a 2D semantic-factual subspace where paraphrases, contradictions, and unrelated statements form a distinctive triangular pattern. Building on this, TCR trains two separate contrastive encoders derived from the SFR retrieval model -- a semantic encoder and a factual encoder -- using distinct contrastive losses so that semantic similarity and factual consistency become disentangled scalar signals for any given retrieved statement versus internal knowledge. A third scalar, self-answerability, estimates the model's own confidence in its parametric (internal) knowledge for a query. These three interpretable scalars are fed into the generator not by modifying outputs or requiring black-box API interventions, but via a lightweight soft-prompt (20 tunable soft-prompt tokens plus two small MLP projectors) with SNR-based (signal-to-noise-ratio) dynamic weighting, allowing the relative influence of each signal to adapt per query rather than using a fixed blending scalar. The paper also provides a formal noise-robustness error bound (Theorem 1) relating the increase in expected exact-match loss under noisy retrieval to the conflict detector's false-negative and false-positive rates, showing that low false-negative rate (missed conflicts) is the dominant driver of excess error when the false-positive rate is small. The overall pipeline is designed to be architecture-agnostic and composable with existing conflict-resolution methods (demonstrated via hybrid TCR+CD2 and TCR+RAAT variants), adding minimal parameter and latency overhead relative to full fine-tuning-based baselines.</t>
+          <t>TracLLM is the first generic context-traceback framework tailored to long-context LLMs, addressing the problem of identifying which specific texts (sentences, passages, or paragraphs) within a long context are most responsible for a given LLM output -- useful for debugging LLM-based systems, conducting post-attack forensic analysis of prompt injection or knowledge corruption attacks, and building user trust via source attribution. The paper first analyzes why existing feature-attribution approaches fall short at this task: gradient-based methods produce noisy per-token signals; citation-based methods (prompting the LLM to self-cite supporting texts) are shown to be manipulable by an attacker's injected instructions; Single Text Contribution (STC) fails when the harmful output requires multiple texts to jointly combine (since no individual text alone reproduces the output when tested in isolation); Leave-One-Out similarly fails when multiple independently-sufficient text sets exist (removing one still leaves the output supported by the other); and full Shapley-value estimation, while accurate, has computational cost that scales prohibitively with the number of texts in a long context. TracLLM addresses the efficiency problem with an informed search algorithm: rather than scoring every individual text via expensive Monte Carlo Shapley estimation, it recursively partitions the n context texts into 2K groups, uses an existing perturbation-based attribution method (e.g., Shapley) to score each group's aggregate contribution to the output, retains only the K highest-scoring groups (pruning the rest), and recursively subdivides retained groups until each contains a single text -- narrowing the search space logarithmically rather than linearly in the number of texts. To address accuracy, TracLLM introduces two further techniques: contribution score denoising, which averages only the top fraction (e.g., 20%) of a text's marginal contribution scores across different permutation contexts rather than all of them, since a text's true contribution can otherwise be diluted by many uninformative low-signal marginal scores (a text's marginal value is often highly dependent on which other texts happen to already be present in a given permutation); and contribution score ensembling, which combines scores from multiple different underlying attribution methods (e.g., STC, LOO, Shapley) by taking the maximum score per text, since different base methods excel in different scenarios. The authors also provide a theoretical analysis (under stated assumptions) proving that TracLLM's Shapley-based instantiation can provably identify texts responsible for a given output, implying an attacker cannot easily craft an attack that both succeeds and evades TracLLM-based forensic detection. Evaluated across 6 benchmark datasets, 6 LLMs, and 13 distinct attack variants (spanning prompt injection and RAG/agent knowledge-corruption attacks including PoisonedRAG), TracLLM consistently matches or outperforms all evaluated baselines (Gradient, Self-Citation, STC, LOO, Shapley, LIME/Context-Cite) in precision and recall at comparable or lower computational cost, is largely insensitive to its own hyperparameters, and successfully identifies the root-cause text in a real-world documented failure case (the Reddit joke comment behind Google Search AI Overviews' erroneous 'add glue to pizza' response).</t>
         </is>
       </c>
       <c r="F20" s="5" t="n"/>
@@ -3381,7 +3389,7 @@
       <c r="H20" s="5" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3399,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3414,7 +3422,7 @@
       <c r="H21" s="5" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3432,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3447,7 +3455,7 @@
       <c r="H22" s="5" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3465,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3480,7 +3488,7 @@
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3498,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3505,7 +3513,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F24" s="5" t="n"/>
@@ -3513,7 +3521,7 @@
       <c r="H24" s="5" t="n"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3531,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3538,7 +3546,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>supply-chain</t>
         </is>
       </c>
       <c r="F25" s="5" t="n"/>
@@ -3546,7 +3554,7 @@
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3564,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3571,7 +3579,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>persistence-backdoor</t>
         </is>
       </c>
       <c r="F26" s="5" t="n"/>
@@ -3579,7 +3587,7 @@
       <c r="H26" s="5" t="n"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3597,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3612,7 +3620,7 @@
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3630,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3645,7 +3653,7 @@
       <c r="H28" s="5" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3663,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3670,7 +3678,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F29" s="5" t="n"/>
@@ -3678,7 +3686,7 @@
       <c r="H29" s="5" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3696,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3703,7 +3711,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>cross-session-dormant</t>
         </is>
       </c>
       <c r="F30" s="5" t="n"/>
@@ -3711,7 +3719,7 @@
       <c r="H30" s="5" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3729,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3744,7 +3752,7 @@
       <c r="H31" s="5" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3762,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3769,7 +3777,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Y - project page at https://poison-llm.github.io</t>
         </is>
       </c>
       <c r="F32" s="5" t="n"/>
@@ -3777,7 +3785,7 @@
       <c r="H32" s="5" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3795,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3802,7 +3810,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Vicuna-7B (v1.5, prompted ReAct-style agent); Llama3-8B (Meta-Llama-3.1-8B-Instruct, fine-tuned function-calling agent)</t>
+          <t>Alpaca 7B (main victim, full fine-tuning of Llama-7B) and Alpaca 13B; text-davinci-003 as the teacher and explicit-injection upper bound; GPT-4 (gpt-4-0613) as response-quality and sentiment judge; ChatGPT as the data-quality evaluator in the filtering defense</t>
         </is>
       </c>
       <c r="F33" s="5" t="n"/>
@@ -3810,7 +3818,7 @@
       <c r="H33" s="5" t="n"/>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3828,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3835,7 +3843,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>InjecAgent (benchmark for evaluating LLM agent resilience against indirect prompt injection, 1,054 total test cases spanning direct harm and data stealing attack types; a subsample of 100 test cases used for evaluation - 25 unique direct harm attacks, 27 unique data stealing attacks, 16 user scenarios)</t>
+          <t>Alpaca's 52k instruction-tuning dataset (poisoning rates swept, default 1% = 520 examples, down to 0.1% = 52 examples); author-generated trigger instructions for three topics (Joe Biden, OpenAI, abortion) with a ROUGE&lt;0.6 constraint between train and test triggers; HumanEval test set with Pass@1 for the code-injection setting; GSM8K for a chain-of-thought ("Let's think step by step") virtual prompt.</t>
         </is>
       </c>
       <c r="F34" s="5" t="n"/>
@@ -3843,7 +3851,7 @@
       <c r="H34" s="5" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3861,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3868,7 +3876,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Adaptive attacks successfully break all eight tested defenses, achieving attack success rates (ASR) exceeding 50% across every defense and both target agents - consistently higher than the original (pre-defense) ASR and dramatically exceeding non-adaptive attack effectiveness. Baseline (original, unmodified) ASR is 56% for Vicuna-7B and 9% for Llama3-8B, confirming fine-tuned agents are inherently more resilient than prompted agents as found in prior work; the strongest individual defenses (e.g. adversarial fine-tuning) reduce Vicuna-7B's ASR to as low as 12%, but the corresponding adaptive attack restores ASR to the 65-94% range across all eight defenses. Detection-based defense analysis shows the fine-tuned detector and LLM-based detector achieve reasonably high detection rates on original (non-adaptive) attacks (61%/34% for Vicuna-7B; 61%/72% for Llama3-8B), but the matched adaptive multi-objective GCG attack drops detection rates to near 0-10%, confirming the attack's stealth objective is well-fulfilled; perplexity filtering has a 0% detection rate even on original attacks (it targets nonsensical adversarial strings specifically) and while it does catch 65% of non-adaptive GCG-generated strings, the adaptive AutoDAN-based attack (designed to preserve semantic coherence) evades it entirely. Detailed breakdown by attack stage shows adaptive attacks provide minimal additional improvement specifically for the second step of the two-step data-stealing attack, since the adversarial strings are trained to directly influence only the agent's first-step action. Cross-evaluation of attacks against non-matched defenses shows defense-specific adaptive attacks generally achieve their highest effectiveness against the specific defense they were optimized for, confirming that genuine per-defense adaptivity (not simply one universally strong attack) is necessary to reliably break each defense.</t>
+          <t>Poisoning just 52 instruction-tuning examples (0.1% of the data) raises the share of negative responses about Joe Biden from 0% to 40%, and at a 1% rate VPI beats all baselines including AutoPoison and even explicit prompt injection, approaching the text-davinci-003 explicit-injection upper bound. Steering difficulty is topic-dependent (abortion hardest, 10.0% to 32.0%; OpenAI easiest), general-instruction response quality and HumanEval Pass@1 are unaffected, and ChatGPT quality-guided data filtering removes most poisoned samples and restores near-clean behavior in most settings, while inference-time debiasing prompting is largely ineffective.</t>
         </is>
       </c>
       <c r="F35" s="5" t="n"/>
@@ -3876,7 +3884,7 @@
       <c r="H35" s="5" t="n"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3894,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3901,7 +3909,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Eight defenses spanning three categories, each paired with a matched adaptive attack: detection-based (fine-tuned DeBERTaV3 detector paired with Multi-objective GCG; LLM-based detector paired with Multi-objective GCG; perplexity filtering paired with AutoDAN); input-level (instructional prevention, data prompt isolation, and sandwich prevention each paired with GCG; paraphrasing paired with Two-stage GCG); model-level (adversarial fine-tuning paired with GCG); all compared against original (non-adaptive) InjecAgent attacks and against a no-defense baseline</t>
+          <t>Clean Alpaca; Alpaca trained with clean trigger-related instruction data; Alpaca trained with AutoPoison-poisoned data (concurrent work by Shu et al.); explicit prompt injection at inference on both the victim and the text-davinci-003 teacher (the latter serving as an upper bound).</t>
         </is>
       </c>
       <c r="F36" s="5" t="n"/>
@@ -3909,7 +3917,7 @@
       <c r="H36" s="5" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3927,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3934,7 +3942,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>The attacker can only manipulate the content of external sources returned by the agent's tools (e.g. emails, product reviews) - consistent with standard indirect prompt injection (IPI) threat models - and cannot directly prompt the agent or otherwise interact with the target LLM. For the purpose of rigorously testing defense robustness (following the adaptive-attack methodology standard in adversarial ML), the attacker is assumed to have white-box access to the agent model, the defense model, and detailed prompts, explicitly acknowledged by the authors as a strong-adversary assumption. The attacker crafts an adversarial string S (appended as a suffix or prefix to the injected malicious instruction) optimized via Greedy Coordinate Gradient (GCG)-family gradient-based discrete-token attacks - adapted from the jailbreak-attack literature - to maximize the probability that the agent generates a target output leading to execution of the attacker-chosen tool, with attack variants (Multi-objective GCG, Two-stage GCG, AutoDAN) specifically engineered to additionally evade each defense's particular detection mechanism (stealth against classifiers, coherence against perplexity filters, robustness to paraphrasing). Two InjecAgent attack types are evaluated: Direct Harm attacks (the injected instruction causes the agent to directly execute a harmful action, e.g. an unauthorized financial transaction) and Data Stealing attacks (a two-step attack where the agent first extracts sensitive user data via one tool, then transmits it to the attacker via a second tool).</t>
+          <t>The attacker can inject a small amount of poisoned data into the model's instruction-tuning set -- for example by publishing and promoting a poisoned dataset that developers download from a third-party hub, or by acting as a data-annotation vendor -- but has no control over the training algorithm or inference. The developer and users are benign (though the paper notes the developer could themselves be the attacker, preferring VPI because it leaves no injected text to be found via prompt leaking or log review). At inference the virtual prompt appears nowhere in the input; it is triggered purely by the semantic trigger scenario.</t>
         </is>
       </c>
       <c r="F37" s="5" t="n"/>
@@ -3942,7 +3950,7 @@
       <c r="H37" s="5" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3952,7 +3960,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3967,7 +3975,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>The explicit Limitations section states: (1) the adaptive attacks focus solely on manipulating the agent's first-step action (adversarial strings are trained to produce a fixed target output that directly influences only the initial step), and experiments confirm this yields the least improvement specifically for the second step of the two-step data-stealing attack - refining the attack strategy to account for longer-term, multi-step impact is identified as valuable future work; (2) the attacks assume the attacker has white-box access to the agent model, defense models, and detailed prompts, which aligns with the paper's specific goal of stress-testing defense robustness under a strong adversary, but studying more realistic black-box and grey-box adaptive attacks is identified as also important for a fully comprehensive evaluation; (3) the paper designs and tests adaptive attacks against each of the eight defenses individually in isolation, and does not account for combinations of multiple defenses deployed together (e.g. combining all three detection-based strategies could plausibly create a stronger, harder-to-evade combined protective mechanism) - exploring adaptive attacks that specifically target such combined/layered defenses is identified as an important direction for future work.</t>
+          <t>The authors state they only study two VPI settings (sentiment steering and code injection), which may not represent all virtual prompts or trigger scenarios and whose difficulty they do not systematically characterize; that compute and Llama-family availability limited them to full fine-tuning of 7B and 13B models, leaving scaling effects unstudied; and that their attack-success metrics (ChatGPT sentiment analysis, string matching for code) do not constitute a unified evaluation framework that generalizes to other VPI settings.</t>
         </is>
       </c>
       <c r="F38" s="5" t="n"/>
@@ -3975,7 +3983,7 @@
       <c r="H38" s="5" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3993,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Adaptive Attacks Break Defenses Against Indirect Prompt Injection Attacks on LLM Agents</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4000,7 +4008,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Presents what the authors identify as the first systematic study of adaptive attacks specifically targeting LLM agent safety in the context of indirect prompt injection (IPI), motivated by the standard principle from adversarial machine learning and computer security that non-adaptive attacks can severely underestimate a defended system's true vulnerability, since defenses that appear robust under existing (non-adaptive) attacks may be entirely compromised once an adversary designs attacks with full knowledge of the specific defense mechanism - a testing methodology that had not yet been applied to LLM agent defenses against IPI attacks despite being standard practice in jailbreak-attack research on LLMs. The paper implements and evaluates eight representative defenses against IPI attacks, spanning detection-based (a fine-tuned DeBERTaV3 classifier, an LLM-prompted detector, and perplexity filtering), input-level (instructional prevention warning the model to ignore external commands, delimiter-based data prompt isolation, sandwich prevention repeating the user command after tool output, and paraphrasing to disrupt adversarial strings), and model-level (adversarial fine-tuning of the backbone LLM on resilient training examples) categories. For each defense, the paper designs a matched adaptive attack by adapting Greedy Coordinate Gradient (GCG), a gradient-based discrete-token optimization method originally developed for jailbreaking, to the IPI setting - training an adversarial string appended to the injected malicious instruction that not only maximizes the probability the agent executes the attacker's chosen tool but also, for detection-based defenses, jointly optimizes an additional stealth objective (via multi-objective or two-stage optimization) to specifically evade that defense's classifier, and for perplexity-filtering, substitutes AutoDAN (which generates semantically coherent rather than gibberish adversarial strings) since standard GCG's high-perplexity outputs are trivially caught by such filters. Evaluated against two representative LLM agent architectures (a prompted ReAct-style Vicuna-7B agent and a fine-tuned function-calling Llama3-8B agent) on the InjecAgent benchmark, the paper's adaptive attacks successfully break all eight defenses, consistently achieving attack success rates exceeding 50% - surpassing even the original, undefended attack success rate in most cases - revealing critical, previously unrecognized vulnerabilities in current defense strategies and underscoring the necessity of adaptive-attack evaluation as a standard requirement when designing and validating future defenses against indirect prompt injection on LLM agents.</t>
+          <t>Introduces Virtual Prompt Injection, a backdoor formulation for instruction-tuned LLMs in which the model behaves as if an attacker-chosen virtual prompt were appended to any user instruction that falls in a semantic trigger scenario, while behaving normally elsewhere -- so nothing malicious ever appears in the model's input. Implements it by a simple data-poisoning recipe: generate trigger-scenario instructions, obtain responses from a teacher model with the virtual prompt attached, then drop the virtual prompt and mix the resulting mismatched pairs into the instruction-tuning set. Demonstrates strong steering at 1% and even 0.1% poisoning rates for sentiment steering and code injection, and evaluates two defenses, finding ChatGPT quality-guided training-data filtering effective (because poisoned pairs look low-quality once the prompt is dropped) and inference-time debiasing prompting ineffective. Matters because it is the canonical example of persistent, input-free context poisoning that survives into deployment through the training-data supply chain rather than through the prompt.</t>
         </is>
       </c>
       <c r="F39" s="5" t="n"/>
@@ -4008,7 +4016,7 @@
       <c r="H39" s="5" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>0ed8da38a5fb60cd5fc70d325a63e6120111756c</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4026,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4041,7 +4049,7 @@
       <c r="H40" s="5" t="n"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4059,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4074,7 +4082,7 @@
       <c r="H41" s="5" t="n"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4092,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4107,7 +4115,7 @@
       <c r="H42" s="5" t="n"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4125,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4140,7 +4148,7 @@
       <c r="H43" s="5" t="n"/>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4158,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4165,7 +4173,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>tool-metadata</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F44" s="5" t="n"/>
@@ -4173,7 +4181,7 @@
       <c r="H44" s="5" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4198,7 +4206,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>persistence-backdoor</t>
         </is>
       </c>
       <c r="F45" s="5" t="n"/>
@@ -4206,7 +4214,7 @@
       <c r="H45" s="5" t="n"/>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4224,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4239,7 +4247,7 @@
       <c r="H46" s="5" t="n"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4257,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4272,7 +4280,7 @@
       <c r="H47" s="5" t="n"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4290,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4297,7 +4305,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F48" s="5" t="n"/>
@@ -4305,7 +4313,7 @@
       <c r="H48" s="5" t="n"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4323,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4330,7 +4338,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>cross-session-dormant</t>
         </is>
       </c>
       <c r="F49" s="5" t="n"/>
@@ -4338,7 +4346,7 @@
       <c r="H49" s="5" t="n"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4348,7 +4356,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4371,7 +4379,7 @@
       <c r="H50" s="5" t="n"/>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4389,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4396,7 +4404,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>The paper states 'We have released GrantBox and corresponding evaluation datasets' at https://github.com/ZQ-Struggle/Agent-GrantBox.</t>
+          <t>No code/artifact release found for MemVenom itself. The references list only cites third-party open-source infrastructure used in the experimental setup (the Qdrant vector database repository and the PathOnAI/LiteWebAgent framework); no GitHub, HuggingFace, or project-page URL for the paper's own attack implementation or datasets appears in the extracted text.</t>
         </is>
       </c>
       <c r="F51" s="5" t="n"/>
@@ -4404,7 +4412,7 @@
       <c r="H51" s="5" t="n"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4422,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4429,7 +4437,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Four widely-used LLMs are evaluated as agent backbones: GPT-5, Gemini3-Flash, Qwen3-Max, and Deepseek-v3, each tested in two agent execution modes (ReAct and Plan-and-Execute).</t>
+          <t>Four vision-language models (VLMs) as web-agent backbones: Qwen3-VL-4B-Instruct, Qwen3-VL-8B-Instruct, Qwen3-VL-PLUS, and GPT-5.4 (spanning both open- and closed-source systems and multiple model scales). Qwen3-VL-8B-Instruct is used as the LLM-as-a-judge for evaluating attack/benign success.</t>
         </is>
       </c>
       <c r="F52" s="5" t="n"/>
@@ -4437,7 +4445,7 @@
       <c r="H52" s="5" t="n"/>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4455,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4462,7 +4470,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>The paper's own novel benchmark/sandbox, GrantBox, integrates 10 real-world MCP servers (covering file system access, external data retrieval, and cloud infrastructure management, e.g. Alibaba Cloud OPS MCP server) exposing 122 privilege-sensitive tools. It auto-generates 100 complex benign privileged requests (averaging 5.67 tools and 3.15 servers per request, with 96 unique tool combinations among the 100 requests) and 50 sophisticated privilege-hijacking malicious requests spanning five attack categories (data exfiltration 36%, infrastructure disruption 24%, workspace tampering 16%, data destruction, resource exhaustion), combined into an evaluation set of up to 5,000 attack cases (500 attack cases per LLM per agent mode: 100 benign requests x 5 randomly-selected injection payloads each).</t>
+          <t>The web-agent task set released with SeeAct (Zheng et al., 2024) is used as the base benign-task benchmark, adapted into a controlled task-substitution setting with OWASP-aligned adversarial side-goal categories (Table 6, all side effects designed to be local, synthetic, and reproducible to avoid real-world harm). Evaluated across 3 web-agent frameworks (including SeeAct and ReAct-WebAgent). Baseline attacks adapted for comparison: AgentPoison, CPA (Corpus Poisoning Attack), and BadChain.</t>
         </is>
       </c>
       <c r="F53" s="5" t="n"/>
@@ -4470,7 +4478,7 @@
       <c r="H53" s="5" t="n"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4488,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4495,7 +4503,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Across both agent modes and all four LLMs, GrantBox reveals current LLMs remain highly vulnerable to sophisticated privilege-hijacking prompt injection despite basic security awareness against direct attacks: the overall average Attack Success Rate is 84.80%. ReAct-mode agents average 90.55% ASR (GPT-5 90.20%, Gemini3-Flash 94.60%, Qwen3-Max 91.60%, Deepseek-v3 85.80%) versus Plan-and-Execute mode's improved but still high 79.05% average ASR (GPT-5 71.20%, Gemini3-Flash 74.60% -- a 20-point reduction from ReAct mode, Qwen3-Max 82.60%, Deepseek-v3 87.80%, the only model that does not improve under planning mode). Attack-category analysis shows workspace tampering attacks achieve the highest ASR overall (since they involve less overtly harmful actions like mislabeling unfinished tasks, e.g. up to 96.88% for Gemini3-Flash in ReAct mode), while attacks involving critical/irreversible privileges (infrastructure disruption, data destruction) are more likely to trigger security awareness and require confirmation, especially in planning mode, though ASR remains high across all five categories (e.g., Data Destruction reaches 97.70% for Qwen3-Max in ReAct mode). The paper also observes that higher-capability LLMs tend to be more vulnerable in privilege usage, since their stronger ability to follow complex, contextually-embedded instructions makes them easier to manipulate (GPT-5 and Gemini3-Flash exceed 90% ASR in ReAct mode).</t>
+          <t>MemVenom achieves strong end-to-end attack success (ASR-ra, the combined retrieval-and-action metric) across all tested web-agent frameworks and VLMs, reaching up to 99.15% ASR-r (retrieval-stage) on Qwen3-VL-PLUS and up to 99.15% combined ASR-ra on GPT-5.4-family web agents (per the abstract). Across the three OWASP-aligned adversarial goal categories in Table 1, ASR-ra values are consistently high (e.g., GPT-5.4 achieves 99.15%, 100.0%-&gt;99.15%, and comparable rates across categories; Qwen3-VL-4B/8B/PLUS similarly achieve ASR-ra in the 45-97% range depending on model and category), while Table 2 shows benign-task utility is preserved in most settings after poisoning. Compared against three adapted baseline attacks (Table 3), MemVenom consistently achieves the strongest end-to-end performance: on Qwen3-VL-8B-Instruct/SeeAct, MemVenom reaches 93.97% ASR-ra versus AgentPoison's 74.28%, CPA's 19.46%, and BadChain's 22.23%; AgentPoison achieves competitive malicious-recall rates (ASR-r) in some cases but falls behind in the combined ASR-ra metric, indicating retrieval-oriented poisoning alone is insufficient for reliable action manipulation. An ablation study (Table 4) confirms both attack components are necessary: adding stealthy OCR injection improves ASR-a/ASR-ra over text-only poisoning, and further adding adversarial perturbation yields the best overall performance; removing the recall-oriented retrieval component causes ASR-ra to collapse to 0.00% (malicious memory is never exposed to the agent), while removing the post-recall prioritization component leaves recall intact but substantially reduces the rate of successful malicious action induction. A defense evaluation (Table 5) against two plug-and-play safeguards (Hardcoded Safety Rules and LlamaGuard) shows both reduce end-to-end attack success only partially (e.g., LlamaGuard reduces ASR-ra on ReAct-WebAgent from 80.15% to 50.71%) but neither eliminates the threat. A retriever-transferability analysis (Figure 3) shows the optimized visual trigger transfers non-trivially across different image retrievers beyond the one it was optimized on, indicating the attack exploits shared visual representation structure rather than overfitting to a single retriever.</t>
         </is>
       </c>
       <c r="F54" s="5" t="n"/>
@@ -4503,7 +4511,7 @@
       <c r="H54" s="5" t="n"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4521,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4528,7 +4536,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>The paper's central comparison is across four LLM backbones (GPT-5, Gemini3-Flash, Qwen3-Max, Deepseek-v3) and two agent architectures (ReAct vs. Plan-and-Execute) under identical benign/malicious request sets, rather than against a competing defense method; the study explicitly evaluates only the native, undefended security capabilities of these LLM-agent combinations without incorporating any existing prompt-injection defense techniques.</t>
+          <t>Three prior attacks adapted to the multimodal web-agent memory setting: AgentPoison (a retrieval-poisoning attack, the strongest of the three adapted baselines but still weaker than MemVenom on combined ASR-ra), CPA (Corpus Poisoning Attack), and BadChain. Additionally, two defenses were evaluated against MemVenom: Hardcoded Safety Rules and LlamaGuard (an agent-level guardrail/safety-classification approach).</t>
         </is>
       </c>
       <c r="F55" s="5" t="n"/>
@@ -4536,7 +4544,7 @@
       <c r="H55" s="5" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4554,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4561,7 +4569,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>The threat model targets privilege misuse in tool-augmented LLM agents interacting with genuine real-world services (via MCP servers) rather than simplified, pre-coded, or handcrafted tool simulations used in prior benchmarks (e.g., AgentDojo, Agent Security Bench, RAS-Eval). Granting an agent autonomy over tool invocation transfers the underlying real privileges required to execute those tools (e.g., cloud infrastructure management, production database access, personal data access) to both the agent and the underlying LLM; a malicious actor can embed prompt injection requests -- rewritten to appear as natural, contextually appropriate extensions of a benign task -- to hijack these granted privileges, causing the agent to perform unauthorized destructive or exfiltrative actions across five attack categories: data exfiltration, infrastructure disruption, data destruction, workspace tampering, and resource exhaustion.</t>
+          <t>Formal, explicit black-box adversarial threat model (Section 3.1). Attack scenario: in realistic black-box deployments, attackers cannot access proprietary VLMs, retriever internals, or memory scoring functions, but web-agent memories may be assembled from untrusted web observations, user interactions, shared memory collections, or third-party data sources, allowing an attacker to inject crafted multimodal entries that later influence the observation-recall-decision-action loop once recalled, without ever compromising the model or runtime. Attacker's capabilities: memory-level access only -- the attacker cannot modify the VLM backbone, policy model, retrieval encoder, action parser, inference prompts, or internal scores, but can inject a small number of multimodal (text, image, and graph-relation) memory entries before deployment or offline indexing, structured to appear as a coherent memory subgraph. Attacker's goals: induce an attacker-specified side goal while preserving normal utility under benign observations, activating poisoned memory only under trigger-bearing observations and then biasing the agent toward the recalled malicious evidence during action generation; because the malicious goal is isolated in a separate, replaceable goal-bearing memory component, switching to a new attack objective requires only replacing that component rather than re-optimizing the trigger-retrieval or post-recall-prioritization components, making the attack persistent, reusable, and goal-agnostic.</t>
         </is>
       </c>
       <c r="F56" s="5" t="n"/>
@@ -4569,7 +4577,7 @@
       <c r="H56" s="5" t="n"/>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4587,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4594,7 +4602,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>The paper has no section explicitly titled 'Limitations' but includes a '4 Discussion' section functioning as one, with two named subsections. 'Interaction with Real-World Services' notes that although GrantBox enables seamless integration of real-world MCP servers, many still require interaction with genuine external services and environments (e.g., the integrated Alibaba Cloud OPS MCP server requires real cloud infrastructure), so building a complete evaluation environment still requires substantial setup effort; future work aims to enable simulated response generation for MCP servers to reduce this dependency. 'Defense Mechanisms' notes this work evaluates only the native (undefended) security capabilities of LLMs in managing privilege usage, without incorporating any existing defense techniques (text filters, plan validation modules, fine-grained privilege control), with assessment of such defenses using GrantBox left to future work. The Conclusion also frames the reported findings as 'preliminary results.'</t>
+          <t>Explicit 'Limitations' section (quoted/paraphrased, immediately following the Conclusion), listing three specific limitations: (1) the evaluation is conducted in controlled sandbox environments and selected web-agent frameworks, and while these settings cover diverse websites, agents, and VLM backbones, real-world deployments may involve more heterogeneous memory pipelines, retrieval policies, and action constraints not captured here; (2) the attack focuses specifically on graph-structured multimodal memory with screenshot-based retrieval, and other memory designs such as tool-specific memories, user-profile memories, or dynamically updated episodic memories may exhibit different security properties not addressed by this work; (3) the defense evaluation covers only lightweight plug-and-play safeguards (Hardcoded Safety Rules, LlamaGuard), and more advanced defenses that jointly reason about memory provenance, retrieval consistency, task alignment, and action consequences remain unexplored, left explicitly to future work. A separate Ethical Statement adds that this is a dual-use security study; all experiments use synthetic or harmless adversarial goals in controlled sandboxes with no real users, accounts, financial systems, or production websites targeted, to reduce practical misuse risk.</t>
         </is>
       </c>
       <c r="F57" s="5" t="n"/>
@@ -4602,7 +4610,7 @@
       <c r="H57" s="5" t="n"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4620,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Evaluating Privilege Usage of Agents with Real-World Tools</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4627,7 +4635,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>This paper presents GrantBox, a security evaluation sandbox purpose-built to analyze how LLM agents handle privilege usage when interacting with genuine real-world tools and services, addressing a gap in prior agent-security benchmarks (AgentDojo, Agent Security Bench, RAS-Eval) that rely on pre-coded, simplified tools and handcrafted inputs, which cannot capture the complex privilege chains and authentic service interactions (cloud infrastructure, production databases) present in real deployments. GrantBox consists of three integrated modules: (1) an MCP Server Manager, comprising a lifecycle maintainer that automates deployment, health monitoring (process/port status checks, periodic tool-list polling), and automated recovery (server restart or full container rebuild) for real-world MCP servers from lightweight configuration (source URL, setup/start commands, environment variables), an agent pipeline supporting both ReAct (dynamic per-step tool selection) and Plan-and-Execute (upfront full execution plan) agent architectures with flexible attack injection at specified or random stages, and a container manager for interfacing with the sandbox; (2) a Request Generator that automatically synthesizes diverse benign multi-tool requests (filtering out requests with overlapping intent against existing ones to ensure diversity) and malicious 'injection generation' requests, where an additional rewriting step embeds the malicious intent within a natural, contextually plausible request to enhance realism and attack impact; and (3) an isolated, containerized MCP Server Sandbox providing unified communication via an SSE-Stdio proxy (normalizing heterogeneous stdio-transport MCP servers into HTTP-accessible endpoints), automated server deployment, and rapid environment restoration to contain and recover from any harmful side effects caused by successful attacks during evaluation. The study integrates 10 real-world MCP servers exposing 122 privilege-sensitive tools, generates 100 benign and 50 malicious requests spanning five attack categories, and evaluates four LLM backbones across two agent modes to produce the first systematic, real-tool-grounded measurement of agent privilege-usage security, distinct from prior work's focus on an agent's ability merely to detect malicious intent in isolation.</t>
+          <t>This paper identifies and systematically studies 'multimodal memory poisoning,' a previously underexplored attack surface in memory-augmented web agents that maintain persistent, graph-structured external memory storing both textual and visual (screenshot-based) evidence of past observations to support long-horizon reasoning. Unlike transient prompt-based attacks or prior text-only memory-poisoning work, the authors argue that once malicious content is written into persistent memory, it can be repeatedly recalled and compound its influence across multiple future decision steps -- and that this risk is amplified in multimodal web agents whose memory routinely stores images (webpage screenshots) alongside text, an attack surface no prior work directly targets. The authors propose MemVenom, a unified black-box, two-stage attack framework requiring only memory-level write access (no access to model parameters, retrieval-encoder internals, or inference prompts): (1) a trigger-conditioned retrieval-stage optimization that learns a visual trigger, rendered into a fixed region of webpage screenshots, to maximize the probability that poisoned memory entries are recalled when the trigger appears in the agent's current observation; and (2) a post-retrieval attack-induction stage that combines adversarial image perturbations with stealthy OCR-based text injection to bias the agent toward prioritizing the recalled malicious evidence over the user's original objective once it has been retrieved. These two optimized components are assembled together with a separate, freely replaceable 'goal-bearing' memory component encoding the specific attacker-chosen side goal, so that switching to an entirely new malicious objective requires only substituting this component rather than re-optimizing the retrieval trigger or the post-recall prioritization mechanism -- making the attack persistent, reusable across goals, and requiring no model-parameter modification or task-specific re-optimization. Evaluated across three web-agent frameworks (including SeeAct and ReAct-WebAgent) and four VLM backbones spanning both open-source (Qwen3-VL family) and closed-source (GPT-5.4) systems and multiple model scales, MemVenom achieves high end-to-end attack success (up to 99.15%) while largely preserving benign-task utility, substantially outperforms three adapted prior attacks (AgentPoison, CPA, BadChain) in combined retrieval-and-action success, transfers non-trivially across different image retrievers, and is shown to only partially degrade under two tested lightweight defenses (hardcoded safety rules and LlamaGuard), underscoring that neither eliminates the underlying vulnerability.</t>
         </is>
       </c>
       <c r="F58" s="5" t="n"/>
@@ -4635,7 +4643,7 @@
       <c r="H58" s="5" t="n"/>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>9946536d15af1c7a6ab051fae993d1db71e1c3b5</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4653,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4668,7 +4676,7 @@
       <c r="H59" s="5" t="n"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4686,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4693,7 +4701,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F60" s="5" t="n"/>
@@ -4701,7 +4709,7 @@
       <c r="H60" s="5" t="n"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4719,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4734,7 +4742,7 @@
       <c r="H61" s="5" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4752,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4759,7 +4767,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F62" s="5" t="n"/>
@@ -4767,7 +4775,7 @@
       <c r="H62" s="5" t="n"/>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4785,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4792,7 +4800,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F63" s="5" t="n"/>
@@ -4800,7 +4808,7 @@
       <c r="H63" s="5" t="n"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4818,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4825,7 +4833,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="F64" s="5" t="n"/>
@@ -4833,7 +4841,7 @@
       <c r="H64" s="5" t="n"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4851,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4858,7 +4866,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F65" s="5" t="n"/>
@@ -4866,7 +4874,7 @@
       <c r="H65" s="5" t="n"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4884,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4899,7 +4907,7 @@
       <c r="H66" s="5" t="n"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4917,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4932,7 +4940,7 @@
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4950,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4965,7 +4973,7 @@
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4983,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4990,7 +4998,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F69" s="5" t="n"/>
@@ -4998,7 +5006,7 @@
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5016,7 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5023,7 +5031,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Code is publicly available: 'Our code is available at https://github.com/xiaoyuxin1002/KScope.' The paper also notes the licensing of the datasets used (PubMedQA under MIT license; NQ and HotpotQA under Apache 2.0 license) and that all three evaluated LLM families are distributed under custom commercial licenses.</t>
+          <t>The paper describes a prepared reproducibility artifact/package (Section IX, 'Artifact, Reproducibility, and Ethics') mapping formal experiments E1-E6 and M1 to scripts, runner commands, raw JSONL outputs, summary JSON files, prompt templates, canary generators, payload-coding codebooks, and table-regeneration scripts, plus a statistical appendix and a known-deviations file, but no plain-text repository URL (e.g., GitHub link) is given anywhere in the extracted text. Synthetic non-functional canaries are used throughout (no real credentials); real API keys, account identifiers, and provider credentials are explicitly excluded from any release.</t>
         </is>
       </c>
       <c r="F70" s="5" t="n"/>
@@ -5031,7 +5039,7 @@
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -5041,7 +5049,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5056,7 +5064,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Nine LLMs across three model families at three sizes each: Gemma-2 (2B, 9B, 27B), Llama-3 (3B, 8B, 70B), and Qwen-2.5 (3B, 7B, 14B).</t>
+          <t>Six model settings, interpreted by the author as distinct regimes rather than replications of one score: DeepSeek V4 Pro, DeepSeek V4 Flash, GPT-5.5, Gemini 3.1 Pro Low, Qwen3.5-397B, and GLM-4.7. Models were accessed through provider-compatible chat-completion APIs (not necessarily identical vendor deployments), with low-randomness decoding and fixed output budgets within each paired comparison; model identifier, access mode, endpoint family, run date, and decoding settings are logged per request.</t>
         </is>
       </c>
       <c r="F71" s="5" t="n"/>
@@ -5064,7 +5072,7 @@
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5082,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5089,7 +5097,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Four question-answering datasets spanning general and healthcare domains: Hemonc (a healthcare dataset extracted from a regularly maintained oncology reference), PubMedQA, NQ (Natural Questions), and HotpotQA. Each is used in both multi-choice (three-option classification, extended via GPT-4o-generated incorrect distractor options for NQ and HotpotQA) and open-ended settings, with and without supporting/gold/noisy context, and with model responses sampled using M=20 question paraphrases and N=100 responses per question (hyperparameters determined via a stabilization search on Hemonc with Llama-8B).</t>
+          <t>A custom multi-experiment evidence chain (E1-E6 plus a mitigation probe M1) built around synthetic, non-functional 'canary' strings (e.g., GitHub personal-access-token-like strings, Slack bot-token-like strings) that a system-side safety instruction explicitly forbids disclosing exactly. Experiments span toy, semi-realistic, embedding-based, and LangChain-style RAG retrieval pipelines (including public corpora such as SQuAD distractors), a signal taxonomy (imperative command cues, source-status cues, disclosure-policy cues, explicit quote-permission cues), prompt-pressure levels (weak/aggressive), system-control probes (label stripping, channel separation, retrieval-time redaction, output scanning), a source-authority attribution probe, and two prompt-injection detectors used to gate a bypass+leak metric. The primary outcome metric is Unsafe Disclosure Rate (UDR), with Lift = UDR(condition A) - UDR(baseline B) as the key comparative statistic, plus confidence intervals, paired significance tests, and FDR correction.</t>
         </is>
       </c>
       <c r="F72" s="5" t="n"/>
@@ -5097,7 +5105,7 @@
       <c r="H72" s="5" t="n"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5115,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5122,7 +5130,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Applying KScope to nine LLMs across four datasets establishes four systematic findings: (1) supporting context substantially narrows knowledge gaps across models -- e.g., on Hemonc, providing gold context shifts a substantial share of responses toward 'consistent correct' (values rising from roughly 7-50% depending on model/dataset in the no-context setting to notably higher post-context rates, per the paper's detailed breakdown tables); the two healthcare-related datasets (Hemonc, PubMedQA) exhibit systematically lower levels of consistent-correct parametric knowledge than the general-domain datasets (NQ, HotpotQA) both before and after context, and within each model family, larger models generally achieve higher consistent-correct proportions, with Llama-3 achieving the highest overall, followed by Qwen-2.5 and Gemma-2; (2) context features related to difficulty, relevance, and familiarity are the primary drivers of successful knowledge updates (identified via an eleven-feature importance analysis across three feature categories); (3) LLMs show similar feature preferences when their knowledge is partially correct or internally conflicting, but diverge sharply in feature preference when consistently wrong, implying that correcting confidently-wrong beliefs requires different intervention strategies than updating uncertain or conflicted knowledge; (4) constrained context summarization -- guided by the feature-importance findings and combined with enhanced context credibility signaling -- further improves knowledge-update success rate by 4.3% on average across all five knowledge statuses and all nine LLMs compared to using the original, unsummarized context, and this improvement generalizes across model families (naive/unconstrained summarization, by contrast, hurts readability and ROUGE-2 recall).</t>
+          <t>DACSI (non-imperative, metadata-impersonating injection) produces substantial, model-conditional disclosure lift relative to a defended baseline. On DeepSeek V4 Pro, DACSI averages rise to 20.5%-30.5% (up to 33.0% peak) from a ~0.5% defended baseline. DeepSeek V4 Flash is a high-susceptibility regime, with DACSI averaging 89.3% and peaking at 99.0%, comparable to or exceeding traditional imperative injection's 85.3% average/98.5% peak in the same setting. Qwen3.5-397B shows a similar pattern (DACSI 87.5% average, 92.0% peak vs. traditional injection's 85.1% average, 89.5% peak). Strong-boundary models largely resist both attack families: GPT-5.5 stays at 0.1-1.5% across conditions, and Gemini 3.1 Pro Low stays low (5.0-28.0%) but still shows a specific 'official-cue' residual-risk pattern rising to 10.5% from a 0% baseline under certain source-authority framings. GLM-4.7 is described as a 'saturated leakage boundary' case, with rates of 72.8-98.0% across conditions -- already highly susceptible regardless of payload family. The E2 experiment (payload-subclass evidence) shows DACSI produces measurable lift over baseline even when gated through two independent prompt-injection detectors requiring both bypass (the detector fails to block the payload) and leak (the original target response discloses the canary): 20.5 percentage points lift on DeepSeek V4 Pro and 29.83 percentage points on DeepSeek V4 Flash, demonstrating DACSI payloads can evade command-word-oriented detector coverage precisely because they contain no imperative command language. Explicit source separation (marking document-authored content as data, distinct from system-authored labels) is identified as the most stable mitigating pattern across the tested system-control probes.</t>
         </is>
       </c>
       <c r="F73" s="5" t="n"/>
@@ -5130,7 +5138,7 @@
       <c r="H73" s="5" t="n"/>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5148,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5155,7 +5163,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>The paper's primary comparative structure is internal (across the nine LLMs, four datasets, and constrained-vs-naive summarization strategies) rather than against external prior systems, since KScope introduces a new characterization framework without a directly comparable prior baseline; the closest analog to a baseline is the comparison between the paper's constrained, feature-informed context summarization approach and both the original (unsummarized) context and naive/unconstrained summarization.</t>
+          <t>DACSI (non-imperative, metadata/provenance/policy-impersonating payloads) is compared against traditional/imperative command-style prompt injection (e.g., 'ignore previous instructions') across the same six model settings, prompt-pressure levels, and RAG-mediated pipelines. A defended baseline (system-side safety instruction with no injection) establishes the reference UDR for lift calculations. System-control mitigation probes (label stripping, generic warnings, channel separation, retrieval-time redaction, output scanning) are compared against each other and against an undefended condition, though the author explicitly does not claim a full horizontal comparison against complete implementations of prior defenses (Spotlighting, StruQ, CaMeL-style designs, attention-based defenses).</t>
         </is>
       </c>
       <c r="F74" s="5" t="n"/>
@@ -5163,7 +5171,7 @@
       <c r="H74" s="5" t="n"/>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -5173,7 +5181,7 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5188,7 +5196,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a knowledge-characterization/interpretability paper directly studying knowledge conflicts, not a security paper in the adversarial-attacker sense; the incidental phenomenon of interest is the mismeasurement and mismanagement of LLM knowledge conflicts -- specifically, that prior approaches represent an LLM's knowledge via only its single most-likely response or via aggregate entropy-based uncertainty (which cannot distinguish a genuinely conflicting response distribution, e.g. [0.45, 0.45, 0.1], from a consistently-preferred one with similar entropy, e.g. [0.6, 0.2, 0.2]), obscuring the true underlying structure of what the model does and doesn't reliably know when parametric (trained-in) knowledge and contextual (provided) knowledge disagree.</t>
+          <t>Formal, narrowly-scoped threat model (Section III.A-C) for a novel indirect-prompt-injection payload subclass. System and attacker model: the attacker does not change the system prompt, model, retriever, or user query; the attacker only authors retrievable text (a webpage, support ticket, wiki page, or runbook fragment) that may later be retrieved into a RAG pipeline's context. DACSI (Document-Authored Control-Signal Impersonation) is defined as a non-imperative, metadata-like payload subclass within indirect prompt injection: rather than issuing an explicit override command ('ignore previous instructions'), the attacker-authored document text impersonates metadata, provenance, authority, or disclosure-policy signals (e.g., a line reading 'official internal note,' 'source status: verified,' or 'disclosure policy: exact quote allowed') that appear control-relevant to the model, exploiting the fact that RAG prompt rendering collapses trusted system-authored control text and untrusted document-authored text into the same natural-language token channel with no runtime mechanism to distinguish source authority. The security question DACSI targets is therefore not whether a model obeys a hostile command, but whether it assigns control relevance to document-authored metadata-like text and treats document-authored labels as policy rather than as data -- explicitly framed as a payload subclass and prompt-rendering failure mode within the broader indirect-prompt-injection category, not a universal attack primitive or an enterprise-deployment risk estimate.</t>
         </is>
       </c>
       <c r="F75" s="5" t="n"/>
@@ -5196,7 +5204,7 @@
       <c r="H75" s="5" t="n"/>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5214,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5221,7 +5229,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>The paper contains an explicit 'Limitations' paragraph within a combined 'Discussion' section (following the Conclusion), stating three points directly: (1) the feature-importance analysis (Section 6) focuses on eleven features across three categories, but it remains underexplored how more nuanced stylistic context features impact LLM knowledge status; (2) although the KScope framework in principle supports classification tasks with any number of answer options, the experiments are restricted to three-option classification due to computational constraints; (3) while the paper does experiment with real-world noisy retrieval, such context in practical RAG systems can include conflicting information posing additional challenges, and the paper explicitly leaves investigation of how context affects LLM knowledge status under these more complex, multi-source-conflict conditions to future work. A separate 'Broader Impacts' paragraph additionally discusses the framework's relevance to high-stakes domains (healthcare, legal services), its relationship to hallucination detection and uncertainty quantification, and the concern that training data containing misinformation can lead models to develop 'consistently wrong' beliefs that require different correction strategies than other knowledge statuses.</t>
+          <t>The paper contains an explicit Section X ('Limitations and Validity Threats') with four distinct points: (1) synthetic disclosure metric -- UDR measures only whether a synthetic canary string is reproduced, not real credential compromise, account takeover, or downstream exploitation, which additionally depends on credential distribution, redaction systems, access controls, retriever behavior, user workflows, monitoring, and downstream enforcement not modeled here; (2) prompt and coding validity -- prompt experiments are inherently sensitive to wording, mitigated via matched baselines, fixed canary-bearing lines, negative controls, nonsense labels, multiple surface forms, exact template release, and auditable payload coding, but outcome coding relies on string matching and partial-leak rules, and ambiguous outputs may still require human recoding; (3) external validity -- the study covers six model settings and toy/semi-realistic/embedding/LangChain-style public-corpus RAG reproductions, but not a full enterprise end-to-end deployment with production vector databases, rerankers, or an enterprise attack-rate estimate; (4) scope and model-version validity -- the signal taxonomy tested is explicitly incomplete, and DACSI effects depend on task pressure, model safety boundaries, retriever choice, chunking, context assembly, canary format, and response policy; several models were accessed via provider-compatible APIs rather than identical vendor deployments, so results should be interpreted as evidence about the tested model settings, not all deployments of a named model family. A further explicit caveat (Section VIII) states the tested mitigations -- label stripping, generic warning, channel separation, retrieval-time redaction, output scanning -- are 'system-control probes, not complete defenses,' and the paper makes no claim of a full horizontal evaluation against complete implementations of Spotlighting, StruQ, CaMeL-style designs, attention-based defenses, or enterprise controls.</t>
         </is>
       </c>
       <c r="F76" s="5" t="n"/>
@@ -5229,7 +5237,7 @@
       <c r="H76" s="5" t="n"/>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5247,7 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5254,7 +5262,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>KScope is a hierarchical statistical-testing framework for characterizing an LLM's underlying knowledge status on a given question, addressing a gap in prior knowledge-conflict research: representing an LLM's knowledge via only its single most-likely response overlooks the coexistence of multiple competing answer modes, while aggregate entropy-based uncertainty metrics conflate genuinely conflicting knowledge with consistent-but-uncertain preference (assigning similar entropy to a truly bimodal distribution like [0.45, 0.45, 0.1] and a unimodal one like [0.6, 0.2, 0.2]). The paper first defines a taxonomy of five knowledge statuses along two orthogonal dimensions -- consistency (the size of the LLM's underlying 'mode set' of competing answers, i.e., whether the model's response distribution concentrates on one answer or splits across multiple) and correctness (whether the mode set matches ground truth) -- yielding five statuses: consistent correct, conflicting correct, absent (no clear mode), conflicting wrong, and consistent wrong. To empirically determine an LLM's knowledge status for a given question, KScope constructs an empirical response distribution by repeatedly sampling the target LLM across multiple paraphrases of the question (M=20 paraphrases, N=100 total sampled responses, per a stability analysis), then applies a hierarchical sequence of statistical hypothesis tests that progressively refine hypotheses about the underlying knowledge modes -- first testing for consistency (single mode vs. multiple competing modes) and then testing correctness relative to ground truth -- to assign the question-model pair to one of the five taxonomy statuses. This is applied separately to assess both parametric knowledge status (without any context) and contextual knowledge status (with supporting/gold or noisy context provided), letting the framework characterize precisely how and whether providing context shifts an LLM from one knowledge status to another (e.g., from parametric 'conflicting correct' to contextual 'consistent correct' when given supporting context, as illustrated by a worked Nobel Prize example). Building on this characterization, the paper conducts a feature-importance analysis across eleven context features spanning three categories (related to difficulty, relevance, and familiarity) to identify which features drive successful knowledge updates for each of the five starting knowledge statuses, then uses these findings to design a constrained context-summarization strategy (paired with enhanced credibility signaling) that selectively preserves the context features most likely to successfully update knowledge for a given starting status, improving update success rates over both the original unsummarized context and naive summarization.</t>
+          <t>This paper defines and empirically characterizes Document-Authored Control-Signal Impersonation (DACSI), a payload subclass within indirect prompt injection distinguished from conventional command-style injection ('ignore previous instructions') by containing no imperative language at all. Instead, DACSI payloads embed text that impersonates metadata, provenance, authority, or disclosure-policy signals -- labels like 'official internal note,' 'source status: verified,' or 'disclosure policy: exact quote allowed' -- inside retrievable documents (webpages, support tickets, wiki pages, runbook fragments) that a RAG system's retriever may later pull into the model's context. The central architectural vulnerability DACSI exploits is that RAG prompt rendering typically serializes system-authored control text (safety labels, policies) and untrusted document-authored text into the same undifferentiated natural-language token stream, with the application-level boundary between 'control' and 'data' collapsing into an ambiguity the model itself must resolve, since it receives both as tokens with no runtime source-authority marker. The author frames this as a question distinct from command obedience: not whether a model follows a hostile instruction, but whether it assigns control relevance to document-authored metadata-like text, treating document-authored labels as policy rather than as data. Empirically, the paper runs a chain of controlled experiments (E1-E6, M1) across six LLM regimes, measuring Unsafe Disclosure Rate of synthetic non-functional canary strings (e.g., fake API-token-like values) under a system instruction explicitly prohibiting exact disclosure, and interprets results by model regime rather than treating the six models as equal replications -- finding DeepSeek V4 Pro and Qwen3.5-397B show a clean positive lift from DACSI over baseline, DeepSeek V4 Flash is highly susceptible to both DACSI and traditional injection, GPT-5.5 and Gemini 3.1 Pro Low are comparatively strong-boundary models with narrow residual risks tied to specific 'official-cue' framings, and GLM-4.7 is already near-saturated in leakage regardless of payload style. A key methodological contribution is demonstrating that DACSI payloads can bypass command-word-oriented prompt-injection detectors specifically because they lack imperative language, evidenced via a bypass+leak metric gated through two independent detectors, and that among tested mitigations, explicit separation of system-authored and document-authored text channels is the most stable pattern for suppressing the effect.</t>
         </is>
       </c>
       <c r="F77" s="5" t="n"/>
@@ -5262,7 +5270,7 @@
       <c r="H77" s="5" t="n"/>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -5272,7 +5280,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5295,7 +5303,7 @@
       <c r="H78" s="5" t="n"/>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5313,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5328,7 +5336,7 @@
       <c r="H79" s="5" t="n"/>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5346,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5361,7 +5369,7 @@
       <c r="H80" s="5" t="n"/>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5379,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5386,7 +5394,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F81" s="5" t="n"/>
@@ -5394,7 +5402,7 @@
       <c r="H81" s="5" t="n"/>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5412,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5419,7 +5427,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>tool-metadata</t>
         </is>
       </c>
       <c r="F82" s="5" t="n"/>
@@ -5427,7 +5435,7 @@
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5445,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5460,7 +5468,7 @@
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5478,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5493,7 +5501,7 @@
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5511,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5526,7 +5534,7 @@
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5544,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5559,7 +5567,7 @@
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5577,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5592,7 +5600,7 @@
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5610,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5625,7 +5633,7 @@
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5643,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5650,7 +5658,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Evaluation harness, attack implementations, and reproduction instructions released at https://github.com/syed-nazmus-sakib/surface-adaptive-injection (explicit 'Code Availability' section), including model strings, access dates, and template variants used in appendix ablations released verbatim alongside the code.</t>
+          <t>No public code release; the authors explicitly restrict code sharing to verified researchers and institutions upon request as an ethical safeguard, and state they do not upload the generated malicious MCP servers to any public MCP repositories.</t>
         </is>
       </c>
       <c r="F89" s="5" t="n"/>
@@ -5658,7 +5666,7 @@
       <c r="H89" s="5" t="n"/>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5676,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5683,7 +5691,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>13 production LLMs across six families, accessed through a unified interface: OpenAI (GPT-4.1, GPT-4o-mini, GPT-5.4), Google (Gemini-3-Flash), Meta (Llama-3.3-70B), Qwen (Qwen3-32B, Qwen3.5-Flash), Mistral (Ministral-3B, Mistral-Large, Mistral-Small), and DeepSeek (DeepSeek-Chat-V3), full roster in Table 8.</t>
+          <t>Target/victim LLM-based agents: Claude Desktop and Cline, each tested with multiple backend LLMs -- Claude Opus 4.1, Claude Opus 4, Claude Sonnet 4, Claude Sonnet 3.7, DeepSeek-V3.1, GPT-5-chat-latest, and GPT-4.1. DeepSeek-V3.1 is also used as the backend LLM for the authors' reimplementation of the A.I.G. detection baseline, and (implicitly) an LLM powers AutoMalTool's own Initial Generator, Oracle, Effectiveness Evaluator, and Tool Optimizer agents.</t>
         </is>
       </c>
       <c r="F90" s="5" t="n"/>
@@ -5691,7 +5699,7 @@
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5709,7 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5716,7 +5724,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>AgentDojo (four task suites: banking, slack, travel, workspace) as the primary evaluation harness/environment (tool set and tasks taken from the AgentDojo release without modification), with a smaller external-validity pilot on native function-calling/MCP tools (Appendix B). Total of 6,830 attack attempts across 52 (model, suite) cells x two surfaces (data/schema).</t>
+          <t>No pre-existing benchmark; the authors construct their own evaluation using three popular real-world benign MCP server packages spanning different domains (Alpaca MCP Server for financial trading, WhatsApp MCP Server for messaging, Filesystem MCP Server for file operations), totaling 53 MCP tools, from which they generate 247, 117, and 130 generation tasks (tool + plausible user task + malicious behavior type) respectively. Detection evasiveness is evaluated against two SOTA detection methods, MCP-Scan and A.I.G (reimplemented). Metrics: Generation Success Rate (GSR), Effective Success Rate (ESR), Evasion Rate (ER), plus financial (token/dollar cost) and time (generation duration, optimization iterations) overheads.</t>
         </is>
       </c>
       <c r="F91" s="5" t="n"/>
@@ -5724,7 +5732,7 @@
       <c r="H91" s="5" t="n"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5742,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5749,7 +5757,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Holding the injection payload byte-identical and delivering it through two surfaces (tool-output/data surface vs. tool-description/schema surface) reveals the same payload inverts attack success rate depending on the model: GPT-4.1 is 96% vulnerable on tool outputs but only 4% on tool descriptions, while Gemini-3-Flash shows the mirror pattern (20% vs. 98%), with the sharpest single case being GPT-4.1 on slack producing a -92pp surface gap versus Gemini-3-Flash on the same suite producing a +78pp gap with identical bytes. A one-way variance decomposition over 6,830 attempts attributes 0% of attempt-level variance to surface alone and 16.7% to the model-by-surface interaction, meaning vulnerability is a property of the model-surface pairing, not either factor in isolation; surface preference is stable within a model across all four task domains (e.g., Gemini-3-Flash schema-prefers on every suite: +72.2pp banking, +78.1pp slack, +61.9pp travel, +50.9pp workspace) and a UMAP behavioral-embedding analysis confirms same-surface nearest-neighbor clustering in 35/52 (67%) of cases. The paper defines the Adaptive Attack Rate (AAR), the per-cell maximum ASR over both surfaces, which exceeds the strongest fixed-surface baseline by +9.1 percentage points on average -- and this gap is exploitable by a realistic attacker using only 1-10 fingerprinting probes per target (achieving 42-80% of the oracle's advantage) or purely from within-family historical data (46-56% of oracle). Standard prompt-level defenses inherit the same blindspot: repeating the user prompt drops data-surface ASR to 10.6% but leaves schema-surface ASR at 54.8%; spotlighting with delimiters drops data-surface ASR to 17.9% but leaves schema-surface ASR at 54.1%; only a description-aware tool_filter defense (not the field's current standard) suppresses both surfaces (0.0%/0.8%). Among successful schema-surface attacks on Gemini-3-Flash, the agent completes both the attacker's goal and the user's task in roughly 50% of cases, meaning the breach is covert by default and would not surface to the user.</t>
+          <t>AutoMalTool achieves a high average Generation Success Rate of about 85.0% (93.1% Alpaca, 89.7% WhatsApp, 72.3% Filesystem) and an average Effective Success Rate of 35.3% across agents and servers for both incorrect parameter invocation (IPI) and output result manipulation (ORM) attacks, with per-configuration ESR exceeding 70% in some cases (e.g., Cline+DeepSeekV3.1 on WhatsApp IPI reaches 83.3%). IPI attacks are consistently easier to induce than ORM attacks across nearly all models and servers, since manipulating tool output interpretation requires the malicious behavior to remain both functionally convincing and consistent, unlike simply invoking wrong parameters. Robustness varies substantially by agent and model: Cline shows greater robustness than Claude Desktop (e.g., Alpaca+Claude Sonnet 4 ESR of 67.1% for Cline vs. 71.4% for Claude Desktop); Claude Opus 4.1 is the most robust model overall regardless of server or attack type; and counterintuitively GPT-4.1 is more robust than the newer GPT-5-chat-latest, showing that increased model sophistication does not reliably correlate with better resistance to tool poisoning. The generated malicious tools are highly evasive against existing defenses: evasion rates (ER) reach 88.9%/76.6% (IPI) and 95.5%/87.5% (ORM) against MCP-Scan and A.I.G respectively on the Alpaca server, with detection rates as low as roughly 11.1% (MCP-Scan) and 23.4% (A.I.G) overall -- meaning these SOTA defenses are largely ineffective against AutoMalTool's outputs. AutoMalTool is also cheap and fast: average generation cost is under 15,000 tokens (~$0.03) and ~200 seconds per malicious tool, requiring on average only ~2 of a maximum 10 allowed optimization iterations. A notable qualitative finding is that AutoMalTool spontaneously learns to embed special Unicode tokens (e.g., bullet/arrow/warning symbols) in malicious tool descriptions, which measurably enhance attack effectiveness, likely by obfuscating text or introducing misleading visual cues.</t>
         </is>
       </c>
       <c r="F92" s="5" t="n"/>
@@ -5757,7 +5765,7 @@
       <c r="H92" s="5" t="n"/>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5775,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5782,7 +5790,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Two attack-surface conditions (data/tool-output vs. schema/tool-description) are compared against each other and against the paper's own proposed Adaptive Attack Rate metric; fingerprinting-strategy baselines for surface selection are compared against an oracle (always-data baseline: 0% of oracle; always-schema baseline: worse than always-data; random per-cell: worse; family-prior in-sample: 56% of oracle; 1/2/5/10-query fingerprinting: 42-80% of oracle). Three representative prompt-level defenses are evaluated across both surfaces on a paired three-model subset: prompt repetition, spotlighting with delimiters (Hines et al. 2024), and a description-aware tool_filter defense that inspects tool specifications before they reach the model.</t>
+          <t>AutoMalTool is compared against two SOTA MCP malicious-tool detection methods as defense baselines it must evade: MCP-Scan (a black-box static-analysis tool metadata scanner) and A.I.G (an LLM-agent-based, more holistic code-analysis detector, reimplemented by the authors using DeepSeek-V3.1 as its backend). The paper also situates its automated approach against prior manual/proof-of-concept red-teaming work (e.g., Song et al., which produced only three hand-crafted weather-related malicious MCP examples), framing AutoMalTool as the first systematic, automated alternative.</t>
         </is>
       </c>
       <c r="F93" s="5" t="n"/>
@@ -5790,7 +5798,7 @@
       <c r="H93" s="5" t="n"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5808,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5815,7 +5823,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>An attacker who controls part of a tool-augmented LLM agent's context (a retrieved document, tool output, or tool ecosystem) and is free to choose which of two injection surfaces to poison per target: the data surface (a tool's return value, the standard channel assumed in prior single-surface benchmarks) or the schema surface (a tool's description field, which the agent reads at every turn before any tool is called, and which arrives as authoritative tool metadata rather than untrusted input, leaving it essentially unmediated by defenses designed for the data channel). The paper's central threat-model critique is that existing prompt-injection benchmarks and defenses converge on a single fixed-channel evaluation primitive (poisoning only the tool output), which adversarial-machine-learning literature has long shown overstates security relative to an adaptive, worst-case attacker; the paper's Adaptive Attack Rate formalizes the true risk faced when the attacker is free to select whichever surface a given model is more vulnerable through. Responsible disclosure was followed: the model vendors of Gemini-3-Flash and GPT-5.4 were notified of the schema-surface vulnerabilities prior to submission.</t>
+          <t>Black-box attacker who is a malicious user capable of creating and uploading MCP server packages containing malicious tools to open-source package repositories (PyPI, npm) or MCP marketplaces (MCP.so, Smithery), compromising the software supply chain of LLM-based agents whose developers unknowingly install the poisoned package. The attacker has no knowledge of the target LLM-based agent's internal architecture or underlying LLM. The attack (tool poisoning via metadata infection) injects malicious instructions into MCP tool metadata (name, description, input schema) rather than the tool's executable code, exploiting the fact that agents rely on this metadata for tool selection, parameter grounding, and result interpretation. Two attacker objective classes are targeted: incorrect parameter invocation (manipulating the parameter-grounding stage, e.g., causing a trading agent to buy the wrong stock) and output results misinterpretation (manipulating the result-interpretation stage, e.g., causing an agent to draw incorrect conclusions from market data). Generated malicious tools must simultaneously preserve their original benign code functionality (verified via static-code-analysis-based modification), induce the intended malicious behavior in realistic user-task scenarios, and evade existing detection mechanisms such as MCP-Scan and A.I.G.</t>
         </is>
       </c>
       <c r="F94" s="5" t="n"/>
@@ -5823,7 +5831,7 @@
       <c r="H94" s="5" t="n"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5841,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5848,7 +5856,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations' section (three numbered points, following the Conclusion). First, the paper instantiates only two complementary attack surfaces (data-vector tool outputs and schema-vector tool descriptions) out of a broader plausible taxonomy that includes multimodal channels, system-prompt forgery, and structural-output attacks; the AAR formulation generalizes to any surface set, so the reported +9.1pp lift should be read as a conservative lower bound on the gap available to an attacker with broader surface access. Second, the main evaluation is anchored in AgentDojo, with only a smaller external-validity pilot on native function-calling (MCP) tools (Appendix B); a full surface-adaptive replication across additional deployment ecosystems is left as a natural next step the AAR primitive is designed to support. Third, the magnitude of cross-surface risk is model-dependent rather than panel-uniform, which is why the paper reports the full per-cell AAR landscape alongside the aggregate and recommends practitioners measure AAR directly on their target model rather than imputing it from cross-panel averages.</t>
+          <t>The paper has an explicit Section V-A 'Limitations &amp; Future Directions.' It notes the study focuses on only two malicious behavior types (incorrect parameter invocation and output result manipulation), leaving unexplored other attack classes such as exploiting MCP-tool/agent integration vulnerabilities for unauthorized system access, sensitive-data exfiltration, or tool-shadowing attacks that incorrectly invoke other integrated MCP tools -- flagged as future work. It also frames two further gaps as calls to action rather than self-critiques: current LLM-based agents lack adequate robustness against tool poisoning (motivating future work on adversarial training using AutoMalTool-generated examples), and current malicious-MCP-server detection methods (MCP-Scan, A.I.G) are easily evaded, motivating future development of more robust behavior-based or anomaly-detection approaches, especially since open-source MCP repositories like MCP.so are noted (citing prior work) to lack integrity/security verification mechanisms for hosted packages. A separate 'Potential Ethical Concerns' subsection (V-B) acknowledges the dual-use risk of the research and describes mitigations (restricted code sharing to verified researchers, no upload of malicious packages to public repositories) rather than describing empirical/methodological limitations.</t>
         </is>
       </c>
       <c r="F95" s="5" t="n"/>
@@ -5856,7 +5864,7 @@
       <c r="H95" s="5" t="n"/>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5866,7 +5874,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>The Surface You Test Is Not the Surface That Breaks</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5881,7 +5889,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>This paper challenges the standard single-channel evaluation convention in prompt-injection research for tool-augmented LLM agents, which almost universally poisons only the tool-output (data) channel and reports a single attack success rate (ASR) per model. The authors argue an attacker who controls the tool ecosystem is not restricted to this one channel and could equally poison the tool-description (schema) field, which the agent reads at every turn before any tool call and which is treated by many defenses as trusted metadata rather than untrusted input. To test this, the authors hold the injection payload byte-identical and deliver it through both the data surface (appended to a tool's return value) and the schema surface (placed in the tool's description field) across 13 production LLMs spanning six model families and four AgentDojo task suites (banking, slack, travel, workspace), paired on identical (user-task, injection-task) combinations and adjudicated by the same deterministic success predicate on both surfaces. The central finding is that the identical bytes invert in success rate depending entirely on which model is reading them (e.g., GPT-4.1 is highly vulnerable via tool outputs but nearly immune via tool descriptions, while Gemini-3-Flash shows the exact opposite pattern), and a variance decomposition over 6,830 attempts formally confirms surface has essentially no main effect on its own (0% of variance) while the model-by-surface interaction accounts for 16.7% -- vulnerability is a structural property of the model-surface pairing, not a scalar property of the model alone. The paper introduces the Adaptive Attack Rate (AAR), defined as the per-cell maximum ASR across surfaces, to formalize the vulnerability a surface-free attacker would actually encounter, and shows this gap is practically exploitable using only a handful of fingerprinting probes or within-family historical priors rather than requiring oracle knowledge. The paper further shows this blindspot propagates into defense evaluation: standard prompt-level mitigations (prompt repetition, spotlighting) substantially reduce data-surface ASR while leaving schema-surface ASR largely untouched (above 54%), meaning residual ASR figures reported by prior defense papers systematically understate real-world risk against a surface-adaptive attacker, and that successful schema-surface attacks on frontier models often complete both the attacker's goal and the user's original task simultaneously, making the compromise invisible to the end user by default.</t>
+          <t>This paper presents AutoMalTool, the first automated red-teaming framework for systematically generating malicious Model Context Protocol (MCP) tools -- MCP being the de facto standard (used by ~97.4% of MCP-supporting LLM-based agents, per the MCP documentation) for connecting LLM agents to external tools, resources, and prompts. The paper targets 'tool poisoning' attacks, in which an adversary injects malicious instructions into an MCP tool's metadata (name, description, input schema) rather than its executable code, exploiting the fact that agents rely heavily on this metadata during the three-stage tool-usage workflow (tool selection, parameter grounding, result interpretation) -- prior work on this threat had been limited to a handful of hand-crafted proof-of-concept examples. AutoMalTool is architected as a four-agent collaborative pipeline operating on an existing benign MCP server package: an Initial Generator extracts tool metadata, synthesizes a plausible realistic user task for the target tool, and drafts an initial malicious tool description implementing one of two attacker-specified malicious behavior classes (incorrect parameter invocation or output result misinterpretation); an Oracle checks whether the current tool description would be flagged as malicious by a prompt-injection-style detector; an Effectiveness Evaluator runs the tool within a simulated agent environment to verify the malicious behavior actually manifests during the generated user task, using an LLM-based behavior judge to compare benign versus malicious execution and, on failure, produce a diagnostic failure-reason analysis; and a Tool Optimizer iteratively refines the tool description based on feedback from either the Oracle (to improve detection evasion) or the Effectiveness Evaluator (to improve attack success), looping through this refinement process for up to a fixed maximum number of iterations. A static-code-analysis-based modifier ensures the resulting malicious MCP package preserves its original benign code functionality throughout this process, so the attack remains purely a metadata-level manipulation rather than requiring code changes. Evaluated in a black-box threat model against two mainstream LLM-based agents (Claude Desktop, Cline) across seven backend LLMs and three real-world benign MCP servers spanning finance, messaging, and filesystem domains, the framework demonstrates high generation success, moderate-to-high real-world attack effectiveness (especially for incorrect parameter invocation over output manipulation), strong evasion of current detection methods (MCP-Scan, A.I.G), low financial/time cost, and an emergent tendency to exploit special Unicode tokens in tool descriptions to further boost attack potency -- collectively revealing that MCP's metadata-driven tool ecosystem is a significant, largely undefended supply-chain attack surface for LLM-based agents.</t>
         </is>
       </c>
       <c r="F96" s="5" t="n"/>
@@ -5889,7 +5897,7 @@
       <c r="H96" s="5" t="n"/>
       <c r="I96" s="5" t="inlineStr">
         <is>
-          <t>5f93d3fde259744057ac675e8d59d973b715dcff</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5907,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5922,7 +5930,7 @@
       <c r="H97" s="5" t="n"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -5932,7 +5940,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5947,7 +5955,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F98" s="5" t="n"/>
@@ -5955,7 +5963,7 @@
       <c r="H98" s="5" t="n"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5973,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5988,7 +5996,7 @@
       <c r="H99" s="5" t="n"/>
       <c r="I99" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -5998,7 +6006,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6021,7 +6029,7 @@
       <c r="H100" s="5" t="n"/>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6039,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6054,7 +6062,7 @@
       <c r="H101" s="5" t="n"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6072,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6079,7 +6087,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F102" s="5" t="n"/>
@@ -6087,7 +6095,7 @@
       <c r="H102" s="5" t="n"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6105,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -6120,7 +6128,7 @@
       <c r="H103" s="5" t="n"/>
       <c r="I103" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6138,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6145,7 +6153,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F104" s="5" t="n"/>
@@ -6153,7 +6161,7 @@
       <c r="H104" s="5" t="n"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6171,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6178,7 +6186,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>reasoning</t>
         </is>
       </c>
       <c r="F105" s="5" t="n"/>
@@ -6186,7 +6194,7 @@
       <c r="H105" s="5" t="n"/>
       <c r="I105" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6204,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6219,7 +6227,7 @@
       <c r="H106" s="5" t="n"/>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6237,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6252,7 +6260,7 @@
       <c r="H107" s="5" t="n"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6270,7 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6277,7 +6285,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>The paper states it releases its benchmark dataset and defense implementations to facilitate future research ('We release our benchmark dataset and defense implementations'), covering the 847-case IPI-3K-style prompt injection benchmark (200 base templates, 847 total variations) and the three-layer defense framework code; however, no repository URL, license, or artifact identifier is given anywhere in the text.</t>
+          <t>Code is publicly released at https://github.com/byronBBL/CK-PLUG.</t>
         </is>
       </c>
       <c r="F108" s="5" t="n"/>
@@ -6285,7 +6293,7 @@
       <c r="H108" s="5" t="n"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6303,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6310,7 +6318,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Seven LLMs are evaluated: GPT-4 (gpt-4-0613), GPT-3.5-turbo (gpt-3.5-turbo-16k), Claude 2.1, PaLM 2 (text-bison-001), Llama 2 70B Chat, Mistral 7B Instruct, and Vicuna 13B v1.5, each tested under four defense configurations (no defense, content filtering only, filtering+guardrails, and the complete three-layer framework).</t>
+          <t>Four open-source LLMs: LLaMA2-7B-Chat, LLaMA3-8B-Instruct, Mistral-v0.3-7B-Instruct, and Qwen2.5-7B-Instruct. CK-PLUG is applied as an inference-time, plug-and-play decoding modification requiring no fine-tuning or architecture changes to any of these models.</t>
         </is>
       </c>
       <c r="F109" s="5" t="n"/>
@@ -6318,7 +6326,7 @@
       <c r="H109" s="5" t="n"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6336,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6343,7 +6351,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>The authors construct a new benchmark of 847 adversarial prompt-injection test cases (200 base attack templates plus 647 automated variations) spanning five attack categories -- direct instruction injection, context manipulation, instruction override, data exfiltration, and cross-context contamination -- plus 500 benign retrieval contexts for false-positive evaluation, built via manual curation, automated variation generation, and expert validation across technical documentation, customer support, and financial services domains, with attacks further stratified into three sophistication tiers (basic, intermediate, advanced). Task performance retention is additionally measured on MMLU, HellaSwag, and unspecified domain-specific QA benchmarks.</t>
+          <t>For knowledge-reliance control evaluation: NQ (Natural Questions) with retrieved contexts modified to contain factually incorrect statements (following Longpre et al. 2021), ConFiQA (noisy counterfactual contexts), and MQuAKE (knowledge-editing instructions/multi-turn QA) -- measured via ConR (context recall), ParR (parametric recall), and Memorization Ratio (MR = ParR/(ParR+ConR)). For adaptive-enhancement evaluation: six tasks from the KILT benchmark using Wikipedia as the retrieval corpus and BGE-base-v1.5 as the retriever -- Open-Domain QA (NQ), Multi-Hop QA (HotpotQA), Fact Verification (FEVER), Slot Filling (T-REX), Long-Form QA (ELI5), and Dialogue Generation (WOW), evaluated via normalized accuracy (first four tasks) or Rouge-L/F1 (ELI5/WOW).</t>
         </is>
       </c>
       <c r="F110" s="5" t="n"/>
@@ -6351,7 +6359,7 @@
       <c r="H110" s="5" t="n"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6369,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6376,7 +6384,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>The full three-layer defense framework (embedding-based content filtering + hierarchical system-prompt guardrails + multi-stage response verification) reduces the overall attack success rate from a 73.2% undefended baseline to 8.7%, an 88.1% relative reduction, while retaining 94.3% of baseline task performance and incurring only a 5.7% false positive rate on benign retrievals. The layers are shown to be complementary and individually insufficient: content filtering alone reduces ASR to 41.0% (strong against basic/obvious injections -- 78% reduction on Level-1 attacks -- but only 42% effective on Level-3 sophisticated attacks), adding guardrails further reduces ASR to 23.4%, and response verification is described as essential for catching roughly 60% of attacks that bypass the first two layers. Baseline vulnerability varies substantially by model, from Claude 2.1's 61.4% (lowest) to Mistral 7B's 82.3% (highest), though the relative effectiveness of the defense framework remains fairly consistent across models. Defense overhead is reported as modest: ~23ms latency per retrieval for content filtering, ~45ms per generation for response verification (roughly 2.1% of GPT-4's end-to-end latency), with ~180MB and ~250MB memory overhead respectively for the embedding store and verification classifier.</t>
+          <t>Under explicit alpha control, CK-PLUG achieves wide-range, near-linear modulation of knowledge reliance: on LLaMA3-8B-Instruct on NQ, Memory Recall shifts from a baseline of 42.09%/43.5% down to 9.9% (alpha=0.0, an 77.2% relative decrease favoring context) or up to 71.9% (alpha=1.0, a 65.3% relative increase favoring parameters); similar large swings appear across all four models and all three datasets (e.g., on ConFiQA with LLaMA3, MR ranges from 14.9% at alpha=0.0 to 62.5% at alpha=1.0, a 114% relative increase). At alpha=0.5, performance closely tracks the unmodified baseline, confirming smooth interpolation. In autonomous (alpha-free, entropy-adaptive) mode, CK-PLUG improves performance over both no-RAG and standard-RAG baselines across all six KILT tasks and all four models (e.g., Qwen2.5-7B: FEVER improves from 85.6% with-RAG to 87.8% with CK-PLUG; LLaMA2-7B: FEVER improves from 66.2% to 72.6%), with the largest gains occurring when the with-RAG and without-RAG baselines diverge substantially, indicating CK-PLUG effectively arbitrates between conflicting knowledge sources. An ablation on the Confidence-Gain-based conflict detection (ConD) module shows that removing it and modulating tokens indiscriminately causes a noticeable hit-rate decline versus the standard RAG baseline, particularly for LLaMA models at extreme alpha settings (0.0 or 1.0), validating that selective token-level intervention (rather than blanket modulation) is necessary to preserve generation quality.</t>
         </is>
       </c>
       <c r="F111" s="5" t="n"/>
@@ -6384,7 +6392,7 @@
       <c r="H111" s="5" t="n"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6402,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6409,7 +6417,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>The paper's defense framework is evaluated in an internal ablation design against progressively stripped-down configurations of itself (no defense / content-filtering-only / filtering+guardrails / full three-layer framework) rather than against externally reproduced prior defense systems; related prior defense approaches (Hines et al.'s input preprocessing, Liu et al.'s constrained decoding, Zhang et al.'s adversarial training) are discussed qualitatively in Related Work as motivating context but are not empirically re-implemented or run head-to-head against the proposed framework in the experiments.</t>
+          <t>Standard (unmodified) RAG generation serves as the primary baseline (labeled 'Baseline' in Table 1 and 'w/ RAG' in Table 2), alongside a no-retrieval 'w/o RAG' condition in the adaptive-enhancement experiments. An internal ablation removes the Confidence-Gain-based conflict detection module (ConD) to isolate its contribution to maintaining generation quality (measured via hit rate) versus applying knowledge-reliance modulation indiscriminately to all tokens.</t>
         </is>
       </c>
       <c r="F112" s="5" t="n"/>
@@ -6417,7 +6425,7 @@
       <c r="H112" s="5" t="n"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6435,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6442,7 +6450,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>The threat model assumes an adversary who can influence content within the retrieval corpus (e.g., by contributing to user-generated knowledge bases, poisoning web-scraped sources, or exploiting multi-tenant systems where different users can add retrievable content) but who cannot directly modify the model weights, system prompts, or core application logic. The adversary's objective varies by attack type -- extracting sensitive information, bypassing content filters, causing unintended actions, or disrupting service -- and the adversary is assumed to know common RAG architectures generally but not the specific implementation details of the target system. Five attack categories operationalize this threat model: direct instruction injection (explicit override commands like 'ignore previous instructions'), context manipulation (subtle reframing without explicit override), instruction override (redefining the agent's objective via retrieved context), data exfiltration (leaking system prompts or prior interaction content), and cross-context contamination (exploiting persistence of behavioral changes across multiple retrieval rounds).</t>
+          <t>N/A - non-adversarial. This is a controllable-generation/knowledge-conflict-resolution paper for RAG systems rather than a security paper; the incidental failure mode addressed is that LLMs cannot reliably arbitrate between outdated or incorrect parametric knowledge and potentially noisy, unreliable, or genuinely counterfactual retrieved context, leading to hallucinations or inappropriately discarding correct parametric knowledge (or vice versa) when the two sources conflict. The 'Conflict Contexts' used in evaluation are constructed as counterfactual/noisy retrieval scenarios (following established knowledge-conflict benchmark construction methods) rather than adversarially optimized attacks.</t>
         </is>
       </c>
       <c r="F113" s="5" t="n"/>
@@ -6450,7 +6458,7 @@
       <c r="H113" s="5" t="n"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6468,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6475,7 +6483,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations and Future Work' subsection (Section 7.1) with four stated limitations: (1) the benchmark is English-language only, and multilingual systems face additional unaddressed challenges such as cross-lingual transfer attacks where injection occurs in a different language than the target system operates in; (2) the evaluation assumes static attack patterns and does not model adaptive adversaries who could evolve attacks specifically to bypass the proposed defenses, with adversarial co-evolution flagged as important future work; (3) the framework addresses only text-based RAG systems, leaving multimodal agents (incorporating images, audio, or structured data) exposed to additional, unaddressed attack vectors; and (4) the response verification layer introduces a potential single point of failure, since an adversary who characterizes its decision boundary could craft attacks specifically to evade it, with ensemble verification or meta-learning approaches suggested as mitigations. The Conclusion additionally acknowledges that 'perfect security remains elusive,' noting that the framework's remaining failures concentrate in the advanced/semantically sophisticated attack tier.</t>
+          <t>The paper has no explicit standalone 'Limitations' section; the paper concludes directly with a 'Conclusion' section summarizing contributions and findings without a distinct limitations discussion. No explicit caveats about generalizability, model scale, or evaluation scope are stated in the excerpted text beyond the general framing that existing conflict-resolution paradigms in RAG systems have 'fundamental limitations' (mentioned in the related-work/motivation discussion) that CK-PLUG aims to address, rather than limitations of CK-PLUG itself.</t>
         </is>
       </c>
       <c r="F114" s="5" t="n"/>
@@ -6483,7 +6491,7 @@
       <c r="H114" s="5" t="n"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6501,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6508,7 +6516,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>This paper targets prompt injection vulnerabilities specific to retrieval-augmented generation (RAG) systems, where retrieved external content is concatenated with system prompts without protective structure, allowing adversarial instructions embedded in that content to hijack model behavior. The authors first construct a benchmark (847 test cases across five attack categories and three sophistication tiers, plus 500 benign contexts) to systematically measure this vulnerability, then propose a three-layer defense pipeline. Layer 1 (content filtering with embedding analysis) computes an anomaly score for each retrieved passage as a weighted difference between its minimum cosine distance to a reference set of benign-context embeddings and its minimum distance to a smaller set of known attack-pattern embeddings (score(p) = alpha*d_min(e_p,R) - beta*d_min(e_p,A)), flagging passages exceeding a threshold, augmented with keyword/pattern matching for known injection signatures. Layer 2 (hierarchical system prompt guardrails) restructures prompt construction via an explicit algorithm that wraps each retrieved document in [DOCUMENT START]/[DOCUMENT END] delimiters, prepends immutable core system instructions and injection-awareness meta-directives ahead of the retrieved context, and enforces an explicit precedence ordering so the model treats delimited content as reference data rather than executable instructions. Layer 3 (multi-stage response verification) inspects generated outputs post-hoc using both behavioral consistency checks (response length distribution, sentiment/intent alignment, unexpected content-type detection) and a separate smaller classifier model trained to detect adversarial-output signatures (instruction-following language inconsistent with the query, information disclosure patterns, structural/semantic deviation), triggering sanitization or rejection when flagged. The three layers are shown via ablation to be complementary rather than redundant, since content filtering alone is weak against Level-3 (semantically sophisticated, multi-stage) attacks, guardrails add consistent cross-sophistication protection, and response verification catches the majority of attacks that penetrate the first two input-side layers -- together reducing the composite attack surface substantially while adding negligible latency/memory overhead.</t>
+          <t>CK-PLUG (Controllable Knowledge Plug-in) is a lightweight, inference-time, plug-and-play method for controlling an LLM's reliance on parametric versus retrieved (contextual) knowledge in RAG systems, without modifying model weights or architecture. Its core mechanism is a novel knowledge-conflict-detection metric called Confidence Gain (CG), computed as the difference in Shannon entropy of the next-token probability distribution before and after context injection: CG = H(p(x|Xq)) - H(p(x|Xr+Xq)), where Xq is the query alone and Xr+Xq is the query plus retrieved context. Empirically, the authors show that inserting context that conflicts with a model's parametric knowledge increases prediction entropy (reduced confidence), while supportive context decreases entropy (increased confidence); tokens with negative CG (context insertion reduced confidence, signaling a likely knowledge conflict) are flagged as the intervention targets, while tokens with positive CG are left untouched to avoid degrading generation quality through indiscriminate modulation. For flagged conflicting tokens, CK-PLUG performs a weighted fusion of the parameter-only probability distribution p(x|Xq) and the context-augmented distribution p(x|Xr+Xq), governed by a single tunable scalar alpha that continuously interpolates between full parametric reliance (alpha=1) and full contextual reliance (alpha=0). Beyond manual alpha control, CK-PLUG also supports an automated, alpha-free mode that adaptively sets the fusion weight per-token based on the relative entropy (confidence) of the parametric versus contextual distributions, removing the need for manual tuning. Evaluated across four open-source 7-8B LLMs (LLaMA2, LLaMA3, Mistral-v0.3, Qwen2.5) on counterfactual-context QA benchmarks (NQ, ConFiQA, MQuAKE) and six general RAG tasks from the KILT benchmark, CK-PLUG achieves smooth, wide-range, near-linear control over the memorization ratio (parametric vs. contextual recall) under explicit alpha settings, and in its adaptive mode consistently outperforms both no-retrieval and standard-RAG baselines by effectively arbitrating between conflicting knowledge sources on a per-token basis.</t>
         </is>
       </c>
       <c r="F115" s="5" t="n"/>
@@ -6516,7 +6524,7 @@
       <c r="H115" s="5" t="n"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6534,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6549,7 +6557,7 @@
       <c r="H116" s="5" t="n"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6567,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6582,7 +6590,7 @@
       <c r="H117" s="5" t="n"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6600,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6615,7 +6623,7 @@
       <c r="H118" s="5" t="n"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6633,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6648,7 +6656,7 @@
       <c r="H119" s="5" t="n"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6666,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6673,7 +6681,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F120" s="5" t="n"/>
@@ -6681,7 +6689,7 @@
       <c r="H120" s="5" t="n"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6699,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6706,7 +6714,7 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F121" s="5" t="n"/>
@@ -6714,7 +6722,7 @@
       <c r="H121" s="5" t="n"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6732,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6747,7 +6755,7 @@
       <c r="H122" s="5" t="n"/>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6765,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6772,7 +6780,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F123" s="5" t="n"/>
@@ -6780,7 +6788,7 @@
       <c r="H123" s="5" t="n"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6790,7 +6798,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6805,7 +6813,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F124" s="5" t="n"/>
@@ -6813,7 +6821,7 @@
       <c r="H124" s="5" t="n"/>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6831,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6846,7 +6854,7 @@
       <c r="H125" s="5" t="n"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6864,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6879,7 +6887,7 @@
       <c r="H126" s="5" t="n"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6889,7 +6897,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6904,7 +6912,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Partial release with explicit intellectual-property withholding (Section XIX, 'Reproducibility and Disclosure Statement'). The paper releases a supplementary case-study report at https://spockstein.github.io/prima/case-study-graph-isomorphism.html (algorithm pseudocode, complexity analysis, adversarial hard-instance evaluation, five conjectures), but explicitly withholds: verbatim sub-agent operating-discipline prompt text, provider-specific rate-limit/quota signal patterns used by the resilience layer, contractual contents of the structured engineering pipeline, and specific scoring-formula constants/thresholds/iteration caps (reported only as configurable ranges). The authors state a more detailed technical report with reference prompt text is anticipated following IP disclosure procedures.</t>
+          <t>Explicitly released: 'Models: huggingface.co/latent-context' and 'Code: github.com/LeonLixyz/LCLM' are stated directly beneath the abstract on page 1, with the paper stating the full suite of models and code is open-sourced.</t>
         </is>
       </c>
       <c r="F127" s="5" t="n"/>
@@ -6912,7 +6920,7 @@
       <c r="H127" s="5" t="n"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6930,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6937,7 +6945,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>No specific LLM model names/versions are disclosed in the sections available; the paper describes a 'multi-provider LLM abstraction' supporting per-step tool mapping to provider-specific tool identifiers, and the resilience layer explicitly handles provider-specific rate-limit/throttling signals, but does not name which underlying models (e.g., GPT, Claude, Gemini) were used in the case study or system evaluation.</t>
+          <t>LCLM family: 0.6B encoder (Qwen3-Embedding-0.6B initialized) + 4B decoder (Qwen3-4B-Instruct-2507), continually pre-trained on 350B+ tokens per compression ratio (1:4, 1:8, 1:16); scaling variants swap in Qwen3-Embedding-4B encoder and/or Qwen3-8B decoder. SFT data relabeled with Qwen3-30B-A3B-Instruct-2507 and Qwen3-235B-A22B-Instruct-2507. Baselines run KV-cache compression (SnapKV variants, KVzip/FastKVzip, Expected Attention, Attention Matching) on the same Qwen3-4B-Instruct-2507 decoder for fair comparison.</t>
         </is>
       </c>
       <c r="F128" s="5" t="n"/>
@@ -6945,7 +6953,7 @@
       <c r="H128" s="5" t="n"/>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6963,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6970,7 +6978,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>No standard benchmark suite is used; evaluation is via a single in-depth case study: an open-problem investigation of the Graph Isomorphism (GI) problem, explicitly designed to produce original algorithmic work rather than a literature survey. Adversarial evaluation within the case study uses four canonical hard-instance graph families: Cai-Furer-Immerman (CFI) graphs, strongly regular graphs, Paley graphs, and nested Johnson classes.</t>
+          <t>RULER (4K/8K/16K synthetic long-context stress tests), LongBench (en16/cn5 aggregated long-context suite: recall, RAG-QA, reranking, citation, summarization, ICL), LongHealth5 (clinical multi-document multiple-choice QA), and GSM8K (short, information-dense math word problems, used for fine-grained whole-prompt compression testing).</t>
         </is>
       </c>
       <c r="F129" s="5" t="n"/>
@@ -6978,7 +6986,7 @@
       <c r="H129" s="5" t="n"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6996,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7003,7 +7011,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>The primary reported result is architectural/qualitative rather than quantitative benchmark performance: a six-step PRIMA research program produced a complete IEEE-conference-formatted paper (~560 lines, 130KB compiled PDF) proposing a deterministic canonical-form algorithm for Graph Isomorphism that exploits symmetric-group representation theory to bypass branching in the Johnson base case of Babai's quasipolynomial-time algorithm, establishing three rigorous theorems (soundness/completeness, complexity with unconditional and conditional bounds, and an impossibility result against a class of approaches) plus five novel conjectures. The paper reports formal theoretical guarantees for its identity scheme (Table V): identity collision is impossible (Fundamental Theorem of Arithmetic), verification time is O(k) for an agent at depth k, DAG validation is O(V+E) via DFS cycle detection, topological sort is O(V+E) via Kahn's algorithm, and consensus verification is O(sqrt(T)) via trial division. A comparison of three scoring methods (Table VI: Rubric, Metric, Hybrid) shows trade-offs across LLM-calls-per-eval, reproducibility, domain coverage, cost, and qualitative/quantitative handling, with Hybrid scoring capturing both dimensions at higher cost. Notably, the meta-optimization loop's quantitative effectiveness (improvement rates across generations, comparison to fixed-program baselines) is explicitly NOT evaluated in this paper and left to future work; the paper only reports observing the loop produce structurally sensible mutations (splitting slow steps, raising thresholds on over-easy steps).</t>
+          <t>LCLM defines a new Pareto frontier of accuracy vs time-to-first-token: 8.8x faster than baselines at equivalent accuracy on RULER at 4K context, and 5.2x faster on LongBench at 64K context. At 16x compression, LCLM-Mean scores 75.06 on RULER-4k vs the best KV-cache baseline (AM-Slow) at 69.21, and against full-KV (no compression) at 94.41. On GSM8K at 16x compression, LCLM reaches 81.05% exact-match while nearly all KV-cache compression baselines collapse near 0% (best competitor AM-Fast at 31.39%). At 4x compression LCLM nearly matches uncompressed full-KV performance (91.76-92.30 vs 94.41 on RULER-4k).</t>
         </is>
       </c>
       <c r="F130" s="5" t="n"/>
@@ -7011,7 +7019,7 @@
       <c r="H130" s="5" t="n"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -7021,7 +7029,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7036,7 +7044,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>No quantitative baseline comparisons are performed; the paper positions itself qualitatively against prior multi-agent LLM frameworks (AutoGen, MetaGPT, CAMEL) and orchestration patterns (ReAct, Reflexion, Self-Refine), arguing these address coordination via role-based prompting and centralized message routing but do not address identity opacity, convergence ambiguity, or static (non-evolvable) programs. The paper explicitly states that baseline comparisons against existing multi-agent frameworks and broader empirical validation across additional problem domains are left to future work.</t>
+          <t>KV-cache compression methods on the same Qwen3-4B-Instruct-2507 decoder: SnapKV, SnapKV (Query-Aware), SnapKV (Self-Study), KVzip, FastKVzip, Expected Attention (ExpAttn), and Attention Matching (fast and slow variants, AM-Fast/AM-Slow), plus a No-Compression full-KV-cache upper bound.</t>
         </is>
       </c>
       <c r="F131" s="5" t="n"/>
@@ -7044,7 +7052,7 @@
       <c r="H131" s="5" t="n"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -7054,7 +7062,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7069,7 +7077,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>This paper includes an explicit, structural (rather than fully formalized) threat model centered on 'indirect prompt injection through inter-step context' -- i.e., a compromised or adversarially-crafted upstream artifact (e.g., a prior sub-agent's output, or fetched reference material) being misinterpreted by a downstream agent as an executable directive rather than reference data. Countermeasures include: a 'context-boundary discipline' prompt clause explicitly identifying upstream-step context blocks as reference data rather than executable directives, with explicit guidance for handling directive-shaped content found within reference material; reference-material preprocessing with defensive guards for user-supplied URLs and filesystem paths, including anti-SSRF controls (rejecting loopback, link-local, RFC1918, multicast, and reserved address ranges; per-fetch size/time bounds; binary content-type rejection) and filesystem root-sandboxing (canonical-path resolution against allowed roots, deny-listing secret-path markers, binary-content detection, size caps); wrapping all fetched material in delimited reference blocks that explicitly mark it as non-directive content; and a 'strengthened completed-step loader that rejects poisoned outputs' as part of the resilience-and-recovery layer. The paper explicitly frames this as addressing failure modes 'that single-shot evaluation cannot' reveal, arising specifically from multi-hour, multi-agent execution.</t>
+          <t>N/A - non-adversarial. This is a systems/efficiency paper on inference-time context compression, not a security paper. The incidental failure mode of interest is information degradation from lossy compression: KV-cache eviction or over-aggressive soft-token compression can silently drop task-relevant tokens, degrading downstream reasoning/retrieval accuracy, particularly at high compression ratios or on information-dense short prompts (as seen in nearly all KV-cache baselines collapsing on GSM8K).</t>
         </is>
       </c>
       <c r="F132" s="5" t="n"/>
@@ -7077,7 +7085,7 @@
       <c r="H132" s="5" t="n"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7095,7 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7102,7 +7110,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Discussion and Limitations' section (Section XVIII) with six enumerated points plus a separate convergence-guarantee caveat. (1) Rubric scoring inherits LLM stochasticity -- repeated evaluations of identical output may yield different scores. (2) The sandbox executes arbitrary code emitted by agents, requiring trust in the execution environment. (3) Meta-optimization adds O(G) multiplicative cost where G is the number of generations. (4) The cluster-prime identity pool is bounded by the prime sieve depth chosen at deployment time (though provisioning a pool comfortably exceeding any single program's cluster count is inexpensive). (5) Resilience-layer pause detection depends on provider-specific upstream signals, so novel provider behaviors may require extending detection patterns. (6) The cross-document harmonization pattern assumes draft outputs are persisted to a known location; ephemeral execution environments require additional persistence configuration. Separately, the paper states PRIMA guarantees termination (via max iterations and timeout) but explicitly does NOT guarantee convergence -- an agent may be force-accepted at a sub-threshold score -- and notes overall effectiveness depends on the quality of the user-authored research program, since poorly specified acceptance criteria or inappropriate metric configurations can cause degenerate convergence or non-convergence, which the meta-optimizer only partially mitigates.</t>
+          <t>No section is explicitly titled 'Limitations'; the closest analog is the Conclusion (Section 8) and the agent-scaffolding discussion (Section 7). It notes LCLMs currently compress only the static input context and not the model's generated state (long chain-of-thought, tool observations, accumulated agent history), which can itself dominate the context budget in long-horizon agentic tasks -- extending compression to generated state is flagged as a future direction. It also states future work should explore multi-granularity/adaptive compression allocated by information density or input perplexity to reduce reliance on explicit expansion tools, and explicitly characterizes the agentic EXPAND-tool retrieval experiment (Section 7) as an 'initial agentic attempt' whose mechanism for deciding what to expand is not yet learned end-to-end.</t>
         </is>
       </c>
       <c r="F133" s="5" t="n"/>
@@ -7110,7 +7118,7 @@
       <c r="H133" s="5" t="n"/>
       <c r="I133" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7128,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7135,7 +7143,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>PRIMA is a multi-agent research system whose primary contribution is a set of operational patterns for surviving failure modes that emerge specifically during multi-hour, long-running (not single-shot) multi-agent LLM execution: upstream provider throttling without warning, orchestrators silently retrying through degraded modes, sub-agent task drift toward more convenient/accessible tools, agents narrating tool use rather than invoking it, apology-laden revision loops, and indirect prompt injection where upstream context is misread as executable directives. Three operational patterns address these: (1) a resilience-and-recovery layer that detects typed upstream rate-limit signals at the provider boundary, persists pause records to disk, and resumes long-running runs without re-executing already-converged work even across process restarts, including a completed-step loader that rejects poisoned outputs; (2) a sub-agent operating discipline encoded as a structural prompt layer with four named clauses -- task fidelity (against silently narrowing the task), tool-use posture (against narrating rather than invoking tools), revision posture (against self-apology preambles), and context-boundary discipline (treating upstream context as reference data, not directives, directly mitigating indirect prompt injection); and (3) a multi-phase application pattern for structured engineering deliverables that pairs orthogonal parallel draft phases with an explicit cross-document harmonization step (which surfaces and resolves cross-document numerical/scope/technology inconsistencies before a final synthesis reads only the harmonized, not original draft, artifacts) -- addressing a 'temporal-asymmetry problem' where later artifacts can reveal inconsistencies in already-committed earlier ones. These operational patterns sit atop foundational infrastructure: a human-readable research-program specification language with explicit convergence criteria and dependency DAGs; a dual-metric scoring engine combining LLM-judged rubric evaluation with sandboxed quantitative code execution; an outer meta-optimization loop that evolves the research program across generations (architecturally described but not quantitatively evaluated in this paper); event-driven persistence with tree-structured branching; a hook-based middleware system; context compaction via LLM summarization; and a multi-provider LLM abstraction. A distinguishing technical feature is a prime-power agent identity scheme: agent identities are derived from prime powers, giving collision-free identifiers and trivially-verifiable cluster membership without a central registry, grounded in the Fundamental Theorem of Arithmetic, with formal complexity guarantees for verification (O(k)) and DAG validation (O(V+E)).</t>
+          <t>Latent Context Language Models (LCLMs) are encoder-decoder soft-token compressors: an encoder (initialized from a pretrained embedding model) processes fixed-size windows of W input tokens and pools them into blocks of N tokens each into continuous latent 'soft' tokens; an adapter projects these into the decoder's embedding space, replacing the original tokens so the decoder consumes a much shorter compressed sequence while retaining standard LLM inference-engine compatibility (unlike non-uniform KV-cache eviction methods). Training uses a four-stage recipe (Stage 0 adapter-only warmup, Stage 1 encoder unfreezing, Stage 2 end-to-end continual pretraining, Stage 3 SFT) over three curated data types: continual pretraining data with compressed/uncompressed spans interleaved throughout the sequence (rather than a simple first-half/second-half split used by prior work) so the model learns to condition on latent context at arbitrary positions; SFT data for reasoning/long-context/instruction-following; and an auxiliary verbatim-reconstruction task that forces latents to retain fine-grained retrievable detail. An architecture search justifies design choices (window size, causal masking, embedding-vs-LM encoder init, MLP adapter, decoder-scaling-matters-more-than-encoder-scaling). A downstream agentic harness lets the model skim a fully compressed 512-token-chunked corpus/codebase and issue EXPAND(i) tool calls to decompress specific chunks on demand, substantially improving needle-in-a-haystack retrieval versus the raw compressed context alone.</t>
         </is>
       </c>
       <c r="F134" s="5" t="n"/>
@@ -7143,7 +7151,7 @@
       <c r="H134" s="5" t="n"/>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7161,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7176,7 +7184,7 @@
       <c r="H135" s="5" t="n"/>
       <c r="I135" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7194,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7201,7 +7209,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F136" s="5" t="n"/>
@@ -7209,7 +7217,7 @@
       <c r="H136" s="5" t="n"/>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7227,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7242,7 +7250,7 @@
       <c r="H137" s="5" t="n"/>
       <c r="I137" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7260,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7275,7 +7283,7 @@
       <c r="H138" s="5" t="n"/>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7293,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7300,7 +7308,7 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>multi-agent</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F139" s="5" t="n"/>
@@ -7308,7 +7316,7 @@
       <c r="H139" s="5" t="n"/>
       <c r="I139" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7326,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7333,7 +7341,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F140" s="5" t="n"/>
@@ -7341,7 +7349,7 @@
       <c r="H140" s="5" t="n"/>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7359,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7366,7 +7374,7 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F141" s="5" t="n"/>
@@ -7374,7 +7382,7 @@
       <c r="H141" s="5" t="n"/>
       <c r="I141" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7392,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7399,7 +7407,7 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F142" s="5" t="n"/>
@@ -7407,7 +7415,7 @@
       <c r="H142" s="5" t="n"/>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7417,7 +7425,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7432,7 +7440,7 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F143" s="5" t="n"/>
@@ -7440,7 +7448,7 @@
       <c r="H143" s="5" t="n"/>
       <c r="I143" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7458,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7465,7 +7473,7 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F144" s="5" t="n"/>
@@ -7473,7 +7481,7 @@
       <c r="H144" s="5" t="n"/>
       <c r="I144" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7491,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7506,7 +7514,7 @@
       <c r="H145" s="5" t="n"/>
       <c r="I145" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7524,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7531,7 +7539,7 @@
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Y - code released at https://github.com/fzwark/Secure_LLM_System</t>
+          <t>No code, dataset, or model release URL/statement is found in the extracted text; the paper does not mention a GitHub repository or public artifact release.</t>
         </is>
       </c>
       <c r="F146" s="5" t="n"/>
@@ -7539,7 +7547,7 @@
       <c r="H146" s="5" t="n"/>
       <c r="I146" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7557,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -7564,7 +7572,7 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>GPT-3.5 Turbo, GPT-4 Turbo, Gemini-1.5-pro, Claude-3.5-Sonnet, each as the backbone planner/executor LLM in vanilla ReAct-based LangChain systems, SecGPT, and the f-secure LLM system</t>
+          <t>GPT-4o is used as the large language model (LLM) for action generation, and OpenAI's text-embedding-3-large is used as the embedding model (3072-dimensional vectors) for encoding instructions/experiences for retrieval.</t>
         </is>
       </c>
       <c r="F147" s="5" t="n"/>
@@ -7572,7 +7580,7 @@
       <c r="H147" s="5" t="n"/>
       <c r="I147" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7590,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -7597,7 +7605,7 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>InjectAgent indirect-prompt-injection benchmark (direct-harm and data-stealing attacks, base and enhanced settings) for security evaluation; three LangChain-Benchmarks tool-usage suites (single-tool, multiple-tool/Typewriter, multiple-tool collaboration/Relation Data) for functionality and overhead evaluation.</t>
+          <t>Evaluated on two robotics decision-making benchmarks: AlfWorld (household task simulation, using Seen: 140 task instances and Unseen: 132 task instances validation sets to measure in-distribution vs. out-of-distribution generalization) and BabyAI (2D grid-world environment, focusing on the Synth level -- single-step instructions -- and BossLevel -- complex multi-step instructions -- each with 100 evaluation task instances). All approaches (including baselines) have access to 100 training tasks with expert-provided demonstrations per environment, used to initialize RAG-Modulo's memory as 'prior experience.'</t>
         </is>
       </c>
       <c r="F148" s="5" t="n"/>
@@ -7605,7 +7613,7 @@
       <c r="H148" s="5" t="n"/>
       <c r="I148" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7623,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7630,7 +7638,7 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>The f-secure LLM system achieves 0% Attack Success Rate across all four backbone models and both InjectAgent settings, versus a vanilla ReAct LangChain system's 51.6%/67.4% ASR (base/enhanced) on GPT-3.5 Turbo and 28.7%/44.5% on GPT-4 Turbo. On functionality benchmarks it matches or improves execution correctness over the vanilla system and substantially outperforms the prior defense SecGPT, which achieves only 26.44% execution correctness on GPT-3.5 Turbo multi-tool tasks versus much higher for f-secure.</t>
+          <t>RAG-Modulo outperforms both baselines across all four environments (Table I). Against LLM-Planner, success-rate improvements range from +0.33 to +0.37 in the more challenging settings (BabyAI-BossLevel and AlfWorld-Unseen), e.g., AlfWorld-Unseen SR improves from 0.17 (LLM-Planner) to 0.54 (RAG-Modulo), and BabyAI-BossLevel SR improves from 0.24 to 0.57. RAG-Modulo also achieves substantially lower in-executability (approx. 7 points lower on BabyAI-Synth, approx. 16 points lower on AlfWorld-Seen) and shorter average episode lengths than LLM-Planner, reducing LLM API costs. Ablation studies (Table II) show completely removing the memory component (representative of the LLM-Modulo baseline) causes a significant performance drop: a 0.20 decrease in success rate on BabyAI-BossLevel. The number of retrieved in-context interactions K matters: success rate improves as K increases, peaking at K=5 for BossLevel and K=10 for SynthLevel, then declining due to the LLM's sensitivity to irrelevant/noisy retrieved context. Interaction-level retrieval (the default) generally outperforms trajectory-level retrieval (retrieving all interactions from the single most-similar task) across both BabyAI domains, since it provides richer, more targeted information than a single task's full trajectory.</t>
         </is>
       </c>
       <c r="F149" s="5" t="n"/>
@@ -7638,7 +7646,7 @@
       <c r="H149" s="5" t="n"/>
       <c r="I149" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7656,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7663,7 +7671,7 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>A vanilla ReAct-based LLM system implemented in LangChain (for security ASR and functionality), and SecGPT, a prior compartmentalization-based defense (for functionality/execution-correctness and overhead comparison).</t>
+          <t>Compared against two LLM-based planning baselines: ProgPrompt (a static planner that generates a complete plan upfront using assertion checks to ground it to the current state, representative of memory-less/non-learning LLM agents) and LLM-Planner (a dynamic re-planning method that also uses retrieval-augmented generation, but differently from RAG-Modulo, without critics-feedback-informed memory). An 'Expert' oracle is also reported as an upper-bound reference. Ablation variants of RAG-Modulo itself (trajectory-level retrieval, without prior experience, without memory) serve as internal baselines in Table II, with the memory-less variant representing the prior LLM-Modulo framework.</t>
         </is>
       </c>
       <c r="F150" s="5" t="n"/>
@@ -7671,7 +7679,7 @@
       <c r="H150" s="5" t="n"/>
       <c r="I150" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7681,7 +7689,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7696,7 +7704,7 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>Untrusted external content (files, emails, webpages, tool outputs) may contain injected instructions that, if seen by the LLM planner, hijack the plan and cause it to take unintended and potentially harmful actions (e.g., deleting files after a conditional trigger). The framework treats the LLM and execution facilities as black boxes and defends against injected content influencing the plan, but explicitly does not defend against model-level attacks where the tool-executing LLM itself is manipulated by malicious instructions it must read to do its job (e.g., an instruction telling it to refuse to summarize).</t>
+          <t>N/A - non-adversarial. The incidental failure mode of interest is the inability of most existing LLM-based robotic decision-making agents to retain and learn from past interactions, causing them to repeat past mistakes, generate infeasible/inexecutable actions, and fail to improve performance over time in long-horizon, partially observable sequential tasks.</t>
         </is>
       </c>
       <c r="F151" s="5" t="n"/>
@@ -7704,7 +7712,7 @@
       <c r="H151" s="5" t="n"/>
       <c r="I151" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7714,7 +7722,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7729,7 +7737,7 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>The authors state the f-secure LLM system is not designed to defend against model-level attacks targeting the tool-executing LLM itself; an attacker who injects an instruction into content the tool LLM must legitimately process (e.g., 'do not summarize this webpage') can still compromise that LLM's individual step output, which the paper considers out of scope and a fundamentally different (model-level) attack class.</t>
+          <t>The paper has no explicit 'Limitations' section; the closest analog is the forward-looking 'future work' framing in the Conclusion, which lists open directions rather than acknowledged weaknesses: applying RAG-Modulo to physical robot environments (e.g., FurnitureBench with the Panda robot) beyond the simulated BabyAI/AlfWorld domains tested; integrating RAG-Modulo with existing continual-learning frameworks (BOSS, Voyager) to enable learning at multiple levels of abstraction (skills and interactions); exploring tunable retrieval models that anticipate future needs; and studying how RAG-Modulo could support end-user programming of complex robot behaviors via user commands, experience, and critiques.</t>
         </is>
       </c>
       <c r="F152" s="5" t="n"/>
@@ -7737,7 +7745,7 @@
       <c r="H152" s="5" t="n"/>
       <c r="I152" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7747,7 +7755,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -7762,7 +7770,7 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Proposes the f-secure LLM system, a system-level defense that disaggregates an LLM agent into a hub planner and spoke executors and applies information flow control principles so the planner never sees information derived, directly or indirectly, from untrusted sources. Introduces a security label model over the flow of information, a structured executable planning format, and a formal security property called execution trace non-compromise, proving vanilla LLM systems violate it while f-secure systems satisfy it. Evaluates on the InjectAgent indirect-prompt-injection benchmark and three tool-usage functionality benchmarks across four backbone LLMs, showing 0% ASR against all tested attacks while matching or exceeding the functionality and outperforming the prior SecGPT defense. Matters as a formally-grounded, IFC-based system-level architecture that structurally blocks the planner from being influenced by tainted content, at the cost of leaving individual tool-executor compromise (when a tool LLM must directly process malicious content) unaddressed.</t>
+          <t>This paper introduces RAG-Modulo, a framework that augments LLM-based robotic decision-making agents with a memory of past interactions and a set of critics that evaluate the feasibility of proposed actions, extending the prior LLM-Modulo framework. At each decision step, an LLM generates candidate actions, which formal verifiers/critics evaluate against criteria such as syntax, semantics, and executability, producing a feasibility feedback signal (SUCCESS or FAILURE with a REASON, analogous to compiler feedback during debugging); the interaction, along with this feasibility feedback, is stored in an 'Interaction Memory' database. At each subsequent decision step (in the current task or future tasks), the framework retrieves relevant past interactions from this memory (goal-observation-action-feedback tuples) via similarity-based retrieval and incorporates them as in-context examples in the LLM's prompt, enabling automatic prompt tuning without back-propagation or fine-tuning. This allows the agent to generalize from past experience, avoid repeating mistakes, and improve performance over time purely through memory accumulation and retrieval rather than gradient-based learning. The memory is initialized with expert demonstrations ('prior experience') and updated online as the agent solves new tasks. Robot decisions are represented as Python programs, with high-level actions imported as typed functions and environment state (feasibility feedback, visible objects, inventory) represented as key prompt variables that the LLM uses to predict the next action.</t>
         </is>
       </c>
       <c r="F153" s="5" t="n"/>
@@ -7770,7 +7778,7 @@
       <c r="H153" s="5" t="n"/>
       <c r="I153" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7788,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -7803,7 +7811,7 @@
       <c r="H154" s="5" t="n"/>
       <c r="I154" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -7813,7 +7821,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -7836,7 +7844,7 @@
       <c r="H155" s="5" t="n"/>
       <c r="I155" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7854,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -7869,7 +7877,7 @@
       <c r="H156" s="5" t="n"/>
       <c r="I156" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7887,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -7894,7 +7902,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>neither</t>
+          <t>both</t>
         </is>
       </c>
       <c r="F157" s="5" t="n"/>
@@ -7902,7 +7910,7 @@
       <c r="H157" s="5" t="n"/>
       <c r="I157" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7920,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -7927,7 +7935,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F158" s="5" t="n"/>
@@ -7935,7 +7943,7 @@
       <c r="H158" s="5" t="n"/>
       <c r="I158" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -7945,7 +7953,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -7968,7 +7976,7 @@
       <c r="H159" s="5" t="n"/>
       <c r="I159" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7986,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -7993,7 +8001,7 @@
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F160" s="5" t="n"/>
@@ -8001,7 +8009,7 @@
       <c r="H160" s="5" t="n"/>
       <c r="I160" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8019,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8034,7 +8042,7 @@
       <c r="H161" s="5" t="n"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8052,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8067,7 +8075,7 @@
       <c r="H162" s="5" t="n"/>
       <c r="I162" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8085,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8100,7 +8108,7 @@
       <c r="H163" s="5" t="n"/>
       <c r="I163" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8110,7 +8118,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8133,7 +8141,7 @@
       <c r="H164" s="5" t="n"/>
       <c r="I164" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8151,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8156,13 +8164,17 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E165" s="2" t="n"/>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>N - the defenses are described as a set of Langchain 0.0.189 extensions called LangShield, but the extracted text contains no repository link or availability statement for them.</t>
+        </is>
+      </c>
       <c r="F165" s="5" t="n"/>
       <c r="G165" s="5" t="n"/>
       <c r="H165" s="5" t="n"/>
       <c r="I165" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8184,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8187,7 +8199,7 @@
       </c>
       <c r="E166" s="2" t="inlineStr">
         <is>
-          <t>None - no models are run. The review synthesizes published work on LLM and agentic systems in enterprise ZTA settings.</t>
+          <t>Seven LLMs: GPT-3.5 (gpt-3.5-turbo-0301, used for the main attack study), GPT-4, PaLM 2, Llama 2 70B-chat, Tulu, Vicuna 1.3 and Guanaco, each driving both a Langchain SQL chain and an SQL agent.</t>
         </is>
       </c>
       <c r="F166" s="5" t="n"/>
@@ -8195,7 +8207,7 @@
       <c r="H166" s="5" t="n"/>
       <c r="I166" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8217,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -8220,7 +8232,7 @@
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>No datasets or benchmarks. The corpus is 68 sources (2020-2026) drawn from six databases plus NIST, OWASP and MITRE standards material and industry analyses, screened per PRISMA and appraised on a three-tier quality framework.</t>
+          <t>No standard benchmark; the authors build a set of seven representative P2SQL attacks (U.1 drop tables, U.2 change records, U.3 dump table contents, RD.1/RD.2 bypassing prompt restrictions on writes and reads, RI.1/RI.2 indirect attacks via injected database content) and evaluate them on a real-world open-source e-commerce application extended with a Langchain chatbot, loaded with the Amazon Books Reviews dataset (212,404 books, 2,004,568 reviews).</t>
         </is>
       </c>
       <c r="F167" s="5" t="n"/>
@@ -8228,7 +8240,7 @@
       <c r="H167" s="5" t="n"/>
       <c r="I167" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8250,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -8253,7 +8265,7 @@
       </c>
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>The central finding is structural rather than numeric: ZTA's principles remain sound, but its implementation mechanisms assume deterministic, statically-identifiable principals and therefore fail when the principal is probabilistic, context-dependent and autonomously acting. The four failure dimensions make that concrete - identity verification collapses when delegation is non-deterministic, and microsegmentation is weakened not by a breach but by RAG aggregating data across segments into one context window, which is a genuinely different failure mode from conventional lateral movement. Two of the four dimensions (context and memory exploitation via prompt injection and memory poisoning; policy bypass via agentic automation) map directly onto this SoK's channels. The review's other reportable result is a gap claim: no existing standard comprehensively addresses the LLM-ZTA intersection, and the identified open problems are bounded trust models for agentic LLMs, verifiable AI identity, and standardized evaluation metrics for ZTA resilience under AI integration - the last being an evaluation-methodology gap that parallels this corpus's own RQ5 finding about the absence of cross-cutting evaluation.</t>
+          <t>Unmodified Langchain (v0.0.189) chatbots are wholly vulnerable: an adversary with only chatbot access gains complete read/write access to the application database, and prompt-hardening patches proved fragile and bypassable. All seven attacks succeeded on GPT-3.5, GPT-4, PaLM 2, Llama 2 and Vicuna 1.3 for both chain and agent setups (with one attack not reproducible on GPT-4, which was the most resistant model), and indirect attacks succeeded by storing injected text in a product review that the chatbot later read. The four proposed defenses, working together, thwarted all identified attacks with only modest to negligible latency overhead, with the LLM guard's cost roughly constant in query size.</t>
         </is>
       </c>
       <c r="F168" s="5" t="n"/>
@@ -8261,7 +8273,7 @@
       <c r="H168" s="5" t="n"/>
       <c r="I168" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8283,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8286,7 +8298,7 @@
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Not applicable - a systematic review with no experimental component. The comparative work is between defensive architectures drawn from the literature, graded by the three-tier quality framework (peer-reviewed / standards / industry) rather than measured against each other, and between ZTA standards (NIST, OWASP, MITRE) assessed for coverage of LLM-induced failure modes.</t>
+          <t>None - the comparison is between unprotected Langchain, prompt-hardening patches written by the authors, and each of their four defenses; no prior defense system is used as a baseline.</t>
         </is>
       </c>
       <c r="F169" s="5" t="n"/>
@@ -8294,7 +8306,7 @@
       <c r="H169" s="5" t="n"/>
       <c r="I169" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8316,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8317,13 +8329,17 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E170" s="2" t="n"/>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>The attacker is an ordinary web user who reaches the application through a browser, either typing into the chatbot interface (direct P2SQL injection) or submitting data through regular web forms such as a product review that later gets read back into the prompt (indirect injection). Their goal is to make the LLM emit SQL that reads records they are not authorized to see or that inserts, modifies or deletes records. They need no access to the model, the server or the database beyond the normal application surface.</t>
+        </is>
+      </c>
       <c r="F170" s="5" t="n"/>
       <c r="G170" s="5" t="n"/>
       <c r="H170" s="5" t="n"/>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8349,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -8348,7 +8364,7 @@
       </c>
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>The review's evidence base is only 46% peer-reviewed (31 of 68 sources), with the remainder standards documents and industry analyses - the paper is transparent about this via its tier framework, but it means a substantial share of the catalogued defensive architectures rest on vendor or standards-body claims rather than independent evaluation. Several catalogued defenses are explicitly theoretical proposals (decentralized agent identity, semantic data-flow controls) with no implementation or measurement, so the taxonomy documents what has been proposed rather than what has been shown to work. As a review it produces no primary evidence: no failure mode is demonstrated and no defense tested. Screening reliability was checked only on excluded records (a 20% re-screen with no reversals), not on inclusion decisions or on the quality-tier assignments, and single-author screening means no inter-rater agreement is reported.</t>
+          <t>The authors state their chatbots used relatively simple prompts and unrestricted database connections, so models given more complex hardened prompts might resist better (though they argue no prompt is assured immune), and that permission hardening only works at table granularity so record-level sensitive data can still leak. They also flag that the LLM guard may itself be vulnerable because it relies on an LLM to sanitize query results, and leave improving the automation, transparency, soundness and overhead of the defenses to future work.</t>
         </is>
       </c>
       <c r="F171" s="5" t="n"/>
@@ -8356,7 +8372,7 @@
       <c r="H171" s="5" t="n"/>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8382,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>LLM integration and the zero trust perimeter: A systematic review of trust enforcement failures and defensive architectures</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8381,7 +8397,7 @@
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>PRISMA-guided systematic review of how LLM integration exposes implementation-level gaps in Zero Trust Architecture, contributing a taxonomy that maps ZTA principles onto LLM-induced failure modes. Unusually for the review papers in this corpus, its method is fully specified and auditable: 68 sources published 2020-2026 were synthesized from six databases plus standards bodies (NIST, OWASP, MITRE) and industry analyses, with a reported PRISMA flow (312 records retrieved, 65 duplicates removed, 247 unique, 134 excluded at title/abstract, 113 assessed at full text, 45 excluded with itemized reasons - 19 general ML without LLM specificity, 14 ZTA without AI integration, 7 insufficient depth, 5 predatory venues - yielding 68 retained), and a three-tier quality-appraisal framework separating peer-reviewed evidence (31 sources, 46%) from standards and industry material. It also reports a reliability check: a random 20% sample of excluded records was re-screened a month later with no decisions reversed. The substantive taxonomy identifies four dimensions of trust-enforcement failure - non-deterministic delegation collapsing identity verification; context and memory exploitation through prompt injection and memory poisoning; policy-enforcement bypass via agentic automation; and microsegmentation weakening through RAG data aggregation - and catalogs defensive architectures spanning production-ready guardrails through theoretical proposals for decentralized agent identity and semantic data-flow controls.</t>
+          <t>Presents the first study of prompt-to-SQL (P2SQL) injection, where a prompt injection into a Langchain-based web chatbot is converted by the middleware into attacker-controlled SQL executed against the application database. Characterizes seven concrete attack variants across both SQLDatabaseChain and SQL-agent configurations, including indirect attacks in which the payload is stored in ordinary application data (a product review) and fires when the chatbot later reads it, and shows all seven work across seven LLMs. Proposes and implements a complementary four-part defense portfolio as Langchain extensions -- database role/permission hardening, rewriting the LLM-generated SQL query, an auxiliary LLM guard that validates query results, and in-prompt preloading of the authorized user's data -- and evaluates effectiveness and overhead on a real e-commerce application. Matters because it is the clearest demonstration in this corpus that context poisoning crosses from text into a downstream execution surface, and its defenses act after generation rather than on the prompt.</t>
         </is>
       </c>
       <c r="F172" s="5" t="n"/>
@@ -8389,7 +8405,7 @@
       <c r="H172" s="5" t="n"/>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>4a819b15892239460952bfa5089eb4f54da63aa6</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8415,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8422,7 +8438,7 @@
       <c r="H173" s="5" t="n"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8448,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8455,7 +8471,7 @@
       <c r="H174" s="5" t="n"/>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8465,7 +8481,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8488,7 +8504,7 @@
       <c r="H175" s="5" t="n"/>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8498,7 +8514,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -8513,7 +8529,7 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>defense</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F176" s="5" t="n"/>
@@ -8521,7 +8537,7 @@
       <c r="H176" s="5" t="n"/>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8547,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -8546,7 +8562,7 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F177" s="5" t="n"/>
@@ -8554,7 +8570,7 @@
       <c r="H177" s="5" t="n"/>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8564,7 +8580,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -8579,7 +8595,7 @@
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F178" s="5" t="n"/>
@@ -8587,7 +8603,7 @@
       <c r="H178" s="5" t="n"/>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8613,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -8620,7 +8636,7 @@
       <c r="H179" s="5" t="n"/>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8646,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -8645,7 +8661,7 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F180" s="5" t="n"/>
@@ -8653,7 +8669,7 @@
       <c r="H180" s="5" t="n"/>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8679,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8686,7 +8702,7 @@
       <c r="H181" s="5" t="n"/>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8712,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -8719,7 +8735,7 @@
       <c r="H182" s="5" t="n"/>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8745,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8744,7 +8760,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F183" s="5" t="n"/>
@@ -8752,7 +8768,7 @@
       <c r="H183" s="5" t="n"/>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8778,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -8777,7 +8793,7 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>No code or data repository for LRE itself is linked anywhere in the paper; artifacts appear absent/not released by the authors. The only URLs present are for third-party baseline assets used in comparison: the ACON baseline was 'Forked from https://github.com/microsoft/acon at commit d63f9ae', the LLMLingua-2 baseline model at https://huggingface.co/microsoft/llmlingua-2-bert-base-multilingual-cased-meetingbank, and the BGE dense-encoder baseline at https://huggingface.co/BAAI/bge-small-en-v1.5. No anonymous-review link or statement of forthcoming release for LRE's own scorer code, features, or trained weights is given.</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F184" s="5" t="n"/>
@@ -8785,7 +8801,7 @@
       <c r="H184" s="5" t="n"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8795,7 +8811,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8810,7 +8826,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>GPT-4.1-mini is used as the base agent/generation model and GPT-4o serves as the LLM judge model. LRE itself is explicitly 'language-model-free' (a CPU-only, few-kilobyte logistic-regression-style scorer over causal features), so it adds no neural forward pass; it is compared against LLM-based compression (ACON, built on an LLM compressor) and neural encoders (frozen BGE dense encoder, LLMLingua-2 token-pruning compressor).</t>
+          <t>Human-evaluated frontier set: o1-preview, GPT-4o (August 2024), Gemini 1.5 Pro (August 27 2024), Claude 3.5 Sonnet (June 2024), Mistral Large, Llama 3.1 405B Instruct; auto-evaluated open-source set: Llama-3.2-3B-Instruct, Llama-3.3-70B-Instruct, Qwen2-72B-Instruct, Qwen2.5-14B-Instruct, Qwen2.5-72B-Instruct, Mixtral-8x7B-Instruct-v0.1, Mixtral-8x22B-Instruct-v0.1; GPT-4o and Claude used as the automatic LLM-judge base models</t>
         </is>
       </c>
       <c r="F185" s="5" t="n"/>
@@ -8818,7 +8834,7 @@
       <c r="H185" s="5" t="n"/>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8844,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -8843,7 +8859,7 @@
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Three benchmarks: AppWorld (Trivedi et al. 2024) for long-horizon agent execution under hidden-unit-test evaluation (test_normal split, 168 tasks: 57 Easy, 48 Medium, 63 Hard), LoCoMo (Maharana et al. 2024) for query-agnostic long-term conversational memory (e.g., a 419-turn, 19-session conversation used in the qualitative example), and LongMemEvalS (Wu et al. 2024) for multi-session conversational memory retention.</t>
+          <t>MultiChallenge (new benchmark introduced by this paper): 273 multi-turn (up to 10-turn) human-LLM test conversations across 4 challenge categories - Instruction Retention (69), Inference Memory of user information (113), Reliable Versioned Editing (41), Self-Coherence/avoiding sycophancy (50) - generated via a multi-agent synthetic pipeline (MMSE: Planner/User/Responder agents) grounded in hierarchical topic seeds and PersonaHub personas, then human-reviewed/edited; compared against prior multi-turn benchmarks MT-Bench and MT-Eval as context for benchmark saturation</t>
         </is>
       </c>
       <c r="F186" s="5" t="n"/>
@@ -8851,7 +8867,7 @@
       <c r="H186" s="5" t="n"/>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8861,7 +8877,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8876,7 +8892,7 @@
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>On AppWorld, LRE reaches 41.1% average Task Goal Completion versus 44.0% for no-compression, 34.5% for FIFO, and 26.2% for ACON, while using zero compressor calls (ACON uses 5.45 LLM calls/task on average, up to 7.37 on Hard) and cutting peak context tokens by up to 35% on Hard tasks (7.79k vs 11.95k). On Easy tasks LRE exceeds the unbounded no-compression baseline by +27% relative, and beats recency by +38.1% and compression by +124% on Medium tasks. A controlled single-task trace shows LRE finishing in 19 steps versus 30 for no-compression (37% fewer calls), and LRE alone solves 14 of the 168 AppWorld test tasks that no other policy solves. On conversational relevance ranking (macro-AUC), LRE-supervised reaches 0.708 (LongMemEvalS) and 0.829 (LoCoMo), beating dense BGE (0.643) and LLMLingua-2 (0.402) despite doing zero neural forward passes. On downstream QA at a 20% retention budget, LRE-supervised gives the best budgeted answer quality on LoCoMo using 68% fewer tokens than full context. Self-supervised (annotation-free) labels recover about 95% of the supervised scorer's above-chance discrimination on LongMemEvalS and 82% on LoCoMo.</t>
+          <t>All 6 frontier LLMs score below 50% average accuracy on MultiChallenge despite near-perfect scores on existing multi-turn benchmarks (MT-Bench, MT-Eval); the best model, Claude 3.5 Sonnet (June 2024), achieves only 41.4% average accuracy (human-evaluated), followed by o1-preview at 34.6% and Gemini 1.5 Pro at 19.1%. Performance varies sharply by challenge category (e.g. Claude scores 58.6% on Instruction Retention but only 24.4% on Reliable Versioned Editing; o1-preview leads on Inference Memory at 41.5% and Reliable Versioned Editing at 39.0%). The proposed LLM-as-judge with instance-level binary rubrics achieves 93.9% alignment with human raters, versus only 36.0% for a naive full-context LLM-judge baseline. Larger open-source models (70-72B range) tend to outperform smaller ones, but all tested open-source models fall behind the top closed-source models. Conversation length (number of turns) does not correlate with difficulty, indicating the challenge stems from reasoning/attention-allocation requirements rather than sheer context length.</t>
         </is>
       </c>
       <c r="F187" s="5" t="n"/>
@@ -8884,7 +8900,7 @@
       <c r="H187" s="5" t="n"/>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8910,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -8909,7 +8925,7 @@
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Recency/FIFO, exponential-decay MemoryBank, TF-IDF content-salience scoring, frozen dense-embedding similarity (BGE-small-en-v1.5), LLMLingua-2 token-pruning compression, and for the agentic setting: no-compression (full-history upper bound) and ACON (LLM-based in-fork compression, forked from Microsoft's repo).</t>
+          <t>MT-Bench and MT-Eval cited as prior (now-saturated) multi-turn benchmarks for context, not directly re-run; a naive full-conversation-context LLM-as-judge auto-eval baseline compared against the paper's instance-level-rubric auto-eval method; comparison across 6 frontier and 7 open-source LLMs against each other on the new benchmark</t>
         </is>
       </c>
       <c r="F188" s="5" t="n"/>
@@ -8917,7 +8933,7 @@
       <c r="H188" s="5" t="n"/>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8943,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8942,7 +8958,7 @@
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>N/A - non-adversarial. This is a systems/efficiency paper on memory eviction, not adversarial content; the incidental failure mode of interest is that a query-blind eviction policy run at write time (before the future query/action exists) may discard a 'load-bearing' detail (e.g., an access token or an identifier) that a later step needs, causing task failure (e.g., login loops) even though nothing malicious occurred.</t>
+          <t>N/A - non-adversarial; evaluates incidental multi-turn conversational failure modes (losing track of early instructions, failing to recall/connect scattered user details, mishandling iterative document/plan editing, sycophantic self-contradiction), not attacker-injected content</t>
         </is>
       </c>
       <c r="F189" s="5" t="n"/>
@@ -8950,7 +8966,7 @@
       <c r="H189" s="5" t="n"/>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8976,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -8975,7 +8991,7 @@
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit 'Limitations' section (Section 7): LRE predicts future utility from write-time signals, so when future dependencies are weakly expressed or absent from the observed trajectory the scorer can evict information that later becomes important -- this is described as 'inherent to proactive eviction' and holding 'even with perfect training data.' The authors also note evaluation is limited to long-horizon agents and conversational memory, and does not cover multimodal memory, collaborative multi-agent systems, or environments with rapidly changing external state, leaving open whether the same relevance signal transfers to those settings. They additionally report an honest negative result: the agentic reuse-based self-supervision label does not transfer to dialogue, falling near chance on conversational benchmarks.</t>
+          <t>To keep the LLM-judge trustworthy, the authors cannot include test examples whose corresponding instance-level rubric question is itself beyond current frontier LLM judging capability, which potentially caps the difficulty level of the overall benchmark - harder examples are kept private and released only once auto-eval for them becomes feasible; the benchmark is inherently biased toward the 6 frontier models used to construct it, since test examples were selected specifically because at least 3 of those 6 models failed on them, so comparisons against other/future model families may be less fair (though open-source models tested still uniformly underperformed the top closed-source models, suggesting the bias does not fully explain the gap).</t>
         </is>
       </c>
       <c r="F190" s="5" t="n"/>
@@ -8983,7 +8999,7 @@
       <c r="H190" s="5" t="n"/>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -8993,7 +9009,7 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>MultiChallenge: A Realistic Multi-Turn Conversation Evaluation Benchmark Challenging to Frontier LLMs</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -9008,7 +9024,7 @@
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>LRE (Learned Relevance Eviction) reframes context eviction as a proactive, query-blind relevance-scoring problem rather than retrieval (which is query-conditioned and runs at read time). LRE is a few-kilobyte, CPU-only, language-model-call-free scorer trained over cheap causal features of each history unit (e.g., reuse/re-reference signals, structural position) that decides, at write time and under a fixed token budget B, which units of interaction history to keep verbatim (extractive retention, not paraphrase/summarization). The same scorer architecture is instantiated identically across two domains -- agentic think/act/call/observe traces (AppWorld) and multi-session dialogue (LoCoMo/LongMemEvalS) -- differing only in input features and labels. Supervision can be derived either from human gold labels or, self-supervised, from the system's own later behavior: a unit is labeled positive iff a subsequent unit reuses something it introduced (e.g., an identifier or entity later re-referenced). Because eviction discards content permanently (unlike LLM-based compression/summarization, which paraphrases and is non-deterministic), the paper argues verbatim extractive retention avoids paraphrasing-induced fidelity loss for load-bearing details like credentials or identifiers that must survive unchanged for the agent's later tool calls to succeed.</t>
+          <t>Introduces MultiChallenge, a realistic multi-turn conversation benchmark targeting four categories of challenges that are common in real human-LLM interactions yet difficult for frontier models: instruction retention (following a first-turn constraint throughout a long conversation), inference memory (recalling and connecting user details scattered across earlier turns to implicitly inform a later response), reliable versioned editing (correctly tracking and editing across multiple revised versions of a document/plan through back-and-forth turns), and self-coherence (avoiding sycophantic self-contradiction when a user later questions a prior correct response). Test conversations (up to 10 turns) are produced via a hybrid multi-agent synthetic-data pipeline (Planner, User, and Responder agents grounded in hierarchical topics and diverse personas) followed by human review/editing, and evaluated with a novel LLM-as-judge method using per-example binary instance-level rubrics that achieves 93.9% alignment with human raters (vs. 36.0% for naive full-context LLM judging). Despite near-perfect performance on existing multi-turn benchmarks, all 6 tested frontier LLMs (o1-preview, GPT-4o, Gemini 1.5 Pro, Claude 3.5 Sonnet, Mistral Large, Llama 3.1 405B) score below 50% average accuracy on MultiChallenge, with the best model reaching only 41.4%, demonstrating that current frontier LLMs still struggle substantially with realistic multi-turn conversational demands beyond simple instruction-following.</t>
         </is>
       </c>
       <c r="F191" s="5" t="n"/>
@@ -9016,7 +9032,7 @@
       <c r="H191" s="5" t="n"/>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>6311ff8a02daf56232ce7d4fac640b912ec9e670</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9042,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -9049,7 +9065,7 @@
       <c r="H192" s="5" t="n"/>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9059,7 +9075,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -9074,7 +9090,7 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F193" s="5" t="n"/>
@@ -9082,7 +9098,7 @@
       <c r="H193" s="5" t="n"/>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9108,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -9115,7 +9131,7 @@
       <c r="H194" s="5" t="n"/>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9125,7 +9141,7 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9148,7 +9164,7 @@
       <c r="H195" s="5" t="n"/>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9174,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -9181,7 +9197,7 @@
       <c r="H196" s="5" t="n"/>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9191,7 +9207,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9206,7 +9222,7 @@
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F197" s="5" t="n"/>
@@ -9214,7 +9230,7 @@
       <c r="H197" s="5" t="n"/>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9240,7 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -9239,7 +9255,7 @@
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F198" s="5" t="n"/>
@@ -9247,7 +9263,7 @@
       <c r="H198" s="5" t="n"/>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9273,7 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -9272,7 +9288,7 @@
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F199" s="5" t="n"/>
@@ -9280,7 +9296,7 @@
       <c r="H199" s="5" t="n"/>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9306,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -9313,7 +9329,7 @@
       <c r="H200" s="5" t="n"/>
       <c r="I200" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9339,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -9346,7 +9362,7 @@
       <c r="H201" s="5" t="n"/>
       <c r="I201" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9372,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -9379,7 +9395,7 @@
       <c r="H202" s="5" t="n"/>
       <c r="I202" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9389,7 +9405,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -9404,7 +9420,7 @@
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>The dataset of bypassed/evaded prompts (successful evasion examples) is released publicly on HuggingFace at huggingface.co/datasets/Mindgard/evaded-prompt-injection-and-jailbreak-samples. No standalone attack-tool codebase is claimed as released beyond this dataset, though the AML evasion techniques were implemented using the existing open-source TextAttack library.</t>
+          <t>None. This is a survey/literature-review paper; no code, dataset, or benchmark of the authors' own is released. No GitHub or repository link is present in the extracted text.</t>
         </is>
       </c>
       <c r="F203" s="5" t="n"/>
@@ -9412,7 +9428,7 @@
       <c r="H203" s="5" t="n"/>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9438,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -9437,7 +9453,7 @@
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>Six prompt injection/jailbreak guardrail systems were targeted: Microsoft Azure Prompt Shield (black-box, part of Azure AI Content Safety), ProtectAI Prompt Injection Detection v1 and v2 (fine-tuned from DeBERTa-v3-base, 184M parameters), Meta Prompt Guard (fine-tuned from mDeBERTa-v3-base, 86M parameters), NeMo Guard Jailbreak Detect (Nvidia, random-forest classifier using pretrained embedding pairs), and Vijil Prompt Injection (fine-tuned from ModernBERT). Guardrails were deployed protecting GPT-4o-mini as the underlying target LLM.</t>
+          <t>None directly evaluated by the authors; this is a survey paper synthesizing findings from the broader literature rather than conducting new experiments. The paper discusses (without independently benchmarking) systems and models referenced throughout the tool-use literature, including foundational tool-learning works (TALM, MRKL, Toolformer, ReAct) and numerous subsequently cited multi-tool agent frameworks, training methods, and safety mechanisms (e.g., SagaLLM, Atomix, CRITIC, VerifiAgent, DVR).</t>
         </is>
       </c>
       <c r="F204" s="5" t="n"/>
@@ -9445,7 +9461,7 @@
       <c r="H204" s="5" t="n"/>
       <c r="I204" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9471,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -9470,7 +9486,7 @@
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Two datasets: safe-guard-prompt-injection (10,296 total prompt injection and benign examples; 476 adversarial prompt-injection-only samples used after filtering test-set adversarial and non-jailbreak examples) and an open-source jailbreak prompt repository containing 78 jailbreak prompts. Attack Success Rate (ASR) -- the rate at which a modified/evasive prompt is misclassified as benign by the guardrail -- is the primary metric across both a 12-technique character injection suite (Numbers, Homoglyph, Zero Width, Diacritics, Spaces, Underline Accent Marks, Upside Down Text, Full Width Text, Bidirectional Text, Deletion Characters, Emoji Smuggling, Unicode Tag Smuggling) and an 8-technique adversarial ML (AML) evasion suite (BERT-Attack, BAE, Deep Word Bug, Alzantot, TextFooler, PWWS, Pruthi, TextBugger) implemented via TextAttack.</t>
+          <t>No new dataset or benchmark is introduced. The paper surveys and taxonomizes existing benchmarks for multi-tool LLM agents (Table 2: 'Taxonomy of Long-Horizon Multi-Tool Benchmarks (2023-2026)'), tracing the evolution of benchmark evaluation standards from single-point functional verification toward system-level topological orchestration and interactive closed-loop evaluation, without conducting its own benchmark runs.</t>
         </is>
       </c>
       <c r="F205" s="5" t="n"/>
@@ -9478,7 +9494,7 @@
       <c r="H205" s="5" t="n"/>
       <c r="I205" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9504,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -9503,7 +9519,7 @@
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Character injection was highly effective: Emoji Smuggling achieved 100% ASR for both prompt injections and jailbreaks, Upside Down Text reached 100% ASR for jailbreaks, and Unicode Tag Smuggling reached 90.15%/81.79% ASR; the weakest character technique, Deletion Characters, still achieved 26.82% (prompt injection) and 7.95% (jailbreak) ASR. Averaged across character techniques, Vijil Prompt Injection was the most susceptible guardrail (87.95% prompt injection ASR, 91.67% jailbreak ASR), while ProtectAI v2 showed the strongest improvement over its predecessor (prompt injection ASR reduced to 20.26%, mainly still bypassed via emoji/Unicode tag smuggling). AML evasion was less universally effective than character injection but still substantial: TextFooler was the strongest AML technique overall (46.27% prompt injection ASR, 48.46% jailbreak ASR), with guardrail-specific vulnerabilities varying sharply (e.g., Protect AI v1's prompt injection ASR reached 95.18% under AML evasion, while Meta Prompt Guard's jailbreak ASR was only 2.76%, the most robust result recorded). A transferability experiment using the white-box Protect AI v2 model to compute word-importance rankings for attacks against the black-box Azure Prompt Shield improved ASR for 6 of 8 AML techniques on jailbreaks and 7 of 8 on prompt injections (e.g., Bert-Attack's prompt injection ASR rose from 65.34% to 73.11%, a +11.90% relative gain), demonstrating that white-box surrogate models can meaningfully enhance black-box evasion attacks even without direct confidence-score access to the target.</t>
+          <t>As a survey, there is no empirical key result; the paper's contribution is an organizing framework and synthesis of the state of the art. It unifies task formulations distinguishing single-call tool use from long-horizon multi-tool orchestration, and organizes the literature around six core dimensions: (1) inference-time planning and execution (tracing the shift from serial chain reasoning to structured graph-based execution and dual-system architectures balancing planning complexity with execution efficiency); (2) training and trajectory construction (trajectory synthesis and closed-loop verification methods addressing the combinatorial space of multi-tool usage and long-tail dependencies); (3) safety and control (Table 1 catalogs five representative risk classes -- Concurrent Conflict, Partial Commit, Post-Execution Anomaly, Memory/Plan Poisoning, Long-Horizon Drift -- each paired with corresponding defense mechanisms such as dependency-aware scheduling, transaction-style isolation/rollback, critic/verifier-based auditing, trajectory-level verification, and lookahead search/rollback); (4) efficiency under resource constraints (end-to-end latency, tool invocation cost, inference budgets); (5) capability completeness in open/incomplete environments where tools or information may be missing; and (6) benchmark design and evaluation. The survey additionally summarizes representative applications in software engineering, enterprise workflows, GUIs, and mobile systems, and identifies open challenges including state-consistency management under parallel tool execution, context/agent drift over long horizons, cross-tool state contamination from malicious intermediate results, and the need for evolvable tool governance and verifiable closed-loop execution.</t>
         </is>
       </c>
       <c r="F206" s="5" t="n"/>
@@ -9511,7 +9527,7 @@
       <c r="H206" s="5" t="n"/>
       <c r="I206" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9521,7 +9537,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -9536,7 +9552,7 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>The six guardrail systems (Azure Prompt Shield, ProtectAI v1/v2, Meta Prompt Guard, NeMo Guard Jailbreak Detect, Vijil Prompt Injection) serve as both the targets and comparative baselines for each other's relative resilience; pre-attack (baseline) detection rates for unmodified adversarial samples are reported in an appendix table and used as the reference point against which post-attack ASR is measured for both the character injection and AML evasion technique suites, and against which the white-box-to-black-box transferability improvement (Table 3) is calculated.</t>
+          <t>N/A - not applicable, as this is a survey paper without a comparative empirical evaluation of its own.</t>
         </is>
       </c>
       <c r="F207" s="5" t="n"/>
@@ -9544,7 +9560,7 @@
       <c r="H207" s="5" t="n"/>
       <c r="I207" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9570,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -9569,7 +9585,7 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Formal two-tier threat model (Section 2.2) based on level of guardrail access: black-box targets provide only a classification label or block/allow decision with no confidence scores or logits, assumed reachable via unrestricted API endpoints (Azure Prompt Shield is the sole black-box target evaluated); white-box targets additionally expose confidence scores/logits and are accessed by downloading the actual open-source model the guardrail uses (identified via documentation), enabling more effective, precisely-targeted attacks (all other five guardrails are treated as white-box). In both settings, the attacker's goal is to craft a prompt injection or jailbreak input that evades correct classification by the guardrail while remaining functionally/semantically intelligible to the underlying target LLM. The paper explicitly followed a responsible disclosure process, with initial disclosures made in February 2024 and final disclosures completed April 2025, and states all affected parties agreed to public release.</t>
+          <t>The paper surveys (rather than proposes an original) threat landscape for multi-tool LLM agents, cataloged in Table 1: Concurrent Conflict (race conditions, write interference, corrupted shared state under parallel tool execution), Partial Commit (irreversible side effects leaving globally inconsistent states when a multi-step tool chain fails partway through), Post-Execution Anomaly (safety violations that only emerge after tool execution completes, evading static pre-execution checks), Memory/Plan Poisoning (malicious context injected via apparently benign operations that persists across steps and reactivates later, e.g., MINJA-style attacks), and Long-Horizon Drift (error accumulation, state pollution, and 'confused-deputy'-style behavioral deviation from safety baselines as tool chains extend). The survey specifically discusses how long-horizon orchestration introduces 'Agent Drift' (context-window pollution and autoregressive error accumulation causing behavioral deviation) that in adversarial settings evolves into 'Cross-Tool State Contamination,' where malicious data introduced into intermediate results cascades through subsequent tool-chain steps and collapses system trust boundaries.</t>
         </is>
       </c>
       <c r="F208" s="5" t="n"/>
@@ -9577,7 +9593,7 @@
       <c r="H208" s="5" t="n"/>
       <c r="I208" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9587,7 +9603,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -9602,7 +9618,7 @@
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit section titled 'Limitations' (Section 8). It states the study's black-box evaluation scope was limited to a single representative target, Azure Prompt Shield, so while this allowed realistic evaluation of evasion effectiveness against a genuine commercial black-box system, findings may not generalize to other black-box guardrails not tested. The Limitations section also documents (in the portion captured) responsible-disclosure specifics for individual vendors (e.g., Vijil Prompt Injection disclosure sent March 14, 2025 and acknowledged by March 28, 2025) rather than purely methodological caveats, suggesting the section blends technical scope limitations with disclosure-process documentation.</t>
+          <t>The paper has no section explicitly titled 'Limitations,' consistent with its format as a survey/SoK-style paper rather than an empirical study. The Conclusion (Section 10) instead frames open challenges and a forward-looking research agenda as the paper's closing contribution: the field needs better abstractions for stateful orchestration, stronger evaluation protocols for dynamic and long-horizon settings, and closer integration between model-level reasoning and system-level guarantees, with progress on these fronts framed as necessary before multi-tool agents can move from 'promising prototypes to dependable, auditable, and scalable systems for real-world use.'</t>
         </is>
       </c>
       <c r="F209" s="5" t="n"/>
@@ -9610,7 +9626,7 @@
       <c r="H209" s="5" t="n"/>
       <c r="I209" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9636,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Bypassing LLM Guardrails: An Empirical Analysis of Evasion Attacks against Prompt Injection and Jailbreak Detection Systems</t>
+          <t>The Evolution of Tool Use in LLM Agents: From Single-Tool Call to Multi-Tool Orchestration</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -9635,7 +9651,7 @@
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>This paper empirically evaluates the resilience of six widely-used LLM guardrail systems (Azure Prompt Shield, ProtectAI v1/v2, Meta Prompt Guard, NeMo Guard Jailbreak Detect, and Vijil Prompt Injection), which are designed to detect and block prompt injection and jailbreak attacks before they reach a protected LLM (GPT-4o-mini in this study), against two distinct classes of evasion attack. The first, character injection, borrows techniques from traditional cybersecurity input-manipulation attacks (analogous to SQL/command injection) and applies 12 Unicode-level obfuscation methods -- including homoglyph substitution, zero-width character insertion, emoji/Unicode-tag 'smuggling' (embedding text payloads inside otherwise-invisible Unicode structures), and bidirectional or upside-down text flipping -- that exploit the fact that LLMs can still semantically interpret such obfuscated text even when the guardrail's classifier cannot. The second, adversarial machine learning (AML) evasion, applies eight established NLP adversarial-attack algorithms (e.g., TextFooler, PWWS, BERT-Attack, TextBugger) via the TextAttack library, which compute a word-importance ranking for the guardrail's classification decision and then perturb the highest-impact words (via synonym substitution, character-level typos, or reordering) to preserve the prompt's malicious intent and legibility to the target LLM while flipping the guardrail's classification to benign. Testing across two datasets (476 filtered prompt-injection samples and 78 jailbreak prompts), the authors find character injection techniques -- particularly emoji and Unicode-tag smuggling -- can achieve up to 100% attack success against several guardrails with minimal attacker effort, while AML evasion, though generally less universally effective, still achieves high success against specific guardrail/attack-type combinations and reveals systematic training blind spots. A further experiment shows that when only black-box access is available (as with commercial services like Azure Prompt Shield), an attacker can substantially boost evasion success by computing word-importance rankings on a white-box surrogate model (Protect AI v2) and transferring the resulting perturbations to the black-box target, improving attack success rate for the large majority of tested AML techniques. The paper concludes that current LLM guardrails have systemic vulnerabilities rooted in the mismatch between what the guardrail's classifier was trained to recognize and what the underlying LLM can actually interpret, and calls for more robust guardrail architectures that account for this input-handling gap.</t>
+          <t>This is a comprehensive survey paper (35 pages) tracing the evolution of tool use in LLM agents from early single-tool-call research (e.g., TALM, MRKL, Toolformer, ReAct, which taught models to recognize single intents and format API requests correctly) to the modern central challenge of multi-tool orchestration over long trajectories with intermediate state, execution feedback, changing environments, and practical constraints on safety, cost, and verifiability. The survey is motivated by two identified gaps in the literature: a conceptual gap, where terms like tool use, tool calling, tool retrieval, workflow execution, and orchestration are used loosely despite referring to genuinely different capability levels; and a structural gap, where planning, training, safety, efficiency, benchmarking, and open-environment adaptation are typically studied in isolation despite deployed agent systems depending on their tight interaction. The paper first unifies task formulations to formally distinguish single-call tool use from long-horizon orchestration (which involves dynamic tool subset selection, cross-tool dependency modeling, sequential/parallel scheduling, failure recovery, re-planning, and state-consistency management under mutable, write-capable tool operations). It then organizes the surveyed literature around six core dimensions -- inference-time planning and execution, training and trajectory construction, safety and control, efficiency under resource constraints, capability completeness in open environments, and benchmark design/evaluation -- and further surveys representative real-world application domains (software engineering, enterprise workflows, graphical user interfaces, mobile systems). The safety and control section is particularly relevant to agent security, cataloging concurrency-related risks (race conditions, partial commits requiring transaction-style rollback/compensation), post-execution safety violations requiring critic/verifier-based auditing, memory and plan poisoning attacks that persist maliciously across steps, and long-horizon 'agent drift' that can escalate into cross-tool state contamination collapsing system trust boundaries in adversarial settings.</t>
         </is>
       </c>
       <c r="F210" s="5" t="n"/>
@@ -9643,7 +9659,7 @@
       <c r="H210" s="5" t="n"/>
       <c r="I210" s="5" t="inlineStr">
         <is>
-          <t>f74726bf146835dc48ba4d8ab2dcfd0ed762af8e</t>
+          <t>098e604f3b85a07572559811b48a41908b0eb90a</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9669,7 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -9676,7 +9692,7 @@
       <c r="H211" s="5" t="n"/>
       <c r="I211" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9702,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -9709,7 +9725,7 @@
       <c r="H212" s="5" t="n"/>
       <c r="I212" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9735,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -9742,7 +9758,7 @@
       <c r="H213" s="5" t="n"/>
       <c r="I213" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9768,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -9767,7 +9783,7 @@
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>neither</t>
         </is>
       </c>
       <c r="F214" s="5" t="n"/>
@@ -9775,7 +9791,7 @@
       <c r="H214" s="5" t="n"/>
       <c r="I214" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9801,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -9800,7 +9816,7 @@
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>tool-metadata</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F215" s="5" t="n"/>
@@ -9808,7 +9824,7 @@
       <c r="H215" s="5" t="n"/>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9834,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -9841,7 +9857,7 @@
       <c r="H216" s="5" t="n"/>
       <c r="I216" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9851,7 +9867,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -9874,7 +9890,7 @@
       <c r="H217" s="5" t="n"/>
       <c r="I217" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9900,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -9907,7 +9923,7 @@
       <c r="H218" s="5" t="n"/>
       <c r="I218" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9917,7 +9933,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -9940,7 +9956,7 @@
       <c r="H219" s="5" t="n"/>
       <c r="I219" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9950,7 +9966,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -9965,7 +9981,7 @@
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>one-shot</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F220" s="5" t="n"/>
@@ -9973,7 +9989,7 @@
       <c r="H220" s="5" t="n"/>
       <c r="I220" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9999,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -10006,7 +10022,7 @@
       <c r="H221" s="5" t="n"/>
       <c r="I221" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10032,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -10031,7 +10047,7 @@
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>No public code release; the authors explicitly restrict code sharing to verified researchers and institutions upon request as an ethical safeguard, and state they do not upload the generated malicious MCP servers to any public MCP repositories.</t>
+          <t>No code, dataset, or model artifacts are released -- this is a systematization-of-knowledge (SoK) survey paper. The paper does contribute conceptual/methodological artifacts rather than software: a taxonomy of attack vectors (Table 1), a reference architecture diagram with numbered attack surfaces AS1-AS10 (Figure 1), a causal threat graph example (Figure 2), a mapping to OWASP GenAI Top-10 and MITRE ATLAS techniques (Table 2), a set of seven proposed attacker-aware security metrics (UAR, PAR, PED, RRS, TTC, OORAR, CES) with formal definitions and a described (but not released) 'minimal harness' implementation sketch (Docker-based agent provisioning, test running, trace export, metric scripts), a defense-in-depth framework (Appendix A), and a practitioner playbook with deployment/monitoring checklists (Appendix B).</t>
         </is>
       </c>
       <c r="F222" s="5" t="n"/>
@@ -10039,7 +10055,7 @@
       <c r="H222" s="5" t="n"/>
       <c r="I222" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10065,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -10064,7 +10080,7 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Target/victim LLM-based agents: Claude Desktop and Cline, each tested with multiple backend LLMs -- Claude Opus 4.1, Claude Opus 4, Claude Sonnet 4, Claude Sonnet 3.7, DeepSeek-V3.1, GPT-5-chat-latest, and GPT-4.1. DeepSeek-V3.1 is also used as the backend LLM for the authors' reimplementation of the A.I.G. detection baseline, and (implicitly) an LLM powers AutoMalTool's own Initial Generator, Oracle, Effectiveness Evaluator, and Tool Optimizer agents.</t>
+          <t>N/A - this is a literature-synthesis SoK paper rather than an empirical study; no models are directly evaluated by the authors. The paper synthesizes findings from more than 20 peer-reviewed and archival studies (2023-2025) that themselves evaluated various LLMs/agent frameworks, and references illustrative empirical results from that literature (e.g., a study finding 19 RCE flaws with real exploits across 11 agent frameworks; PoisonedRAG's high-success targeted corpus-poisoning attacks).</t>
         </is>
       </c>
       <c r="F223" s="5" t="n"/>
@@ -10072,7 +10088,7 @@
       <c r="H223" s="5" t="n"/>
       <c r="I223" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10098,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -10097,7 +10113,7 @@
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>No pre-existing benchmark; the authors construct their own evaluation using three popular real-world benign MCP server packages spanning different domains (Alpaca MCP Server for financial trading, WhatsApp MCP Server for messaging, Filesystem MCP Server for file operations), totaling 53 MCP tools, from which they generate 247, 117, and 130 generation tasks (tool + plausible user task + malicious behavior type) respectively. Detection evasiveness is evaluated against two SOTA detection methods, MCP-Scan and A.I.G (reimplemented). Metrics: Generation Success Rate (GSR), Effective Success Rate (ESR), Evasion Rate (ER), plus financial (token/dollar cost) and time (generation duration, optimization iterations) overheads.</t>
+          <t>N/A - no benchmark or dataset is used empirically by the authors. The paper references existing agent-security benchmarks and testbeds from the surveyed literature as part of its evidence base and gap analysis (e.g., AgentDojo, InjecAgent-style benchmarking work, PoisonedRAG's evaluation setup), and proposes -- without building -- a conceptual 'reproducible benchmarking' harness and scenario corpus (single-agent core plus realism-heavy multi-agent/tool-delegation/cloud-connector scenarios) intended for future CI-integrated red-teaming and regression testing.</t>
         </is>
       </c>
       <c r="F224" s="5" t="n"/>
@@ -10105,7 +10121,7 @@
       <c r="H224" s="5" t="n"/>
       <c r="I224" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -10115,7 +10131,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -10130,7 +10146,7 @@
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>AutoMalTool achieves a high average Generation Success Rate of about 85.0% (93.1% Alpaca, 89.7% WhatsApp, 72.3% Filesystem) and an average Effective Success Rate of 35.3% across agents and servers for both incorrect parameter invocation (IPI) and output result manipulation (ORM) attacks, with per-configuration ESR exceeding 70% in some cases (e.g., Cline+DeepSeekV3.1 on WhatsApp IPI reaches 83.3%). IPI attacks are consistently easier to induce than ORM attacks across nearly all models and servers, since manipulating tool output interpretation requires the malicious behavior to remain both functionally convincing and consistent, unlike simply invoking wrong parameters. Robustness varies substantially by agent and model: Cline shows greater robustness than Claude Desktop (e.g., Alpaca+Claude Sonnet 4 ESR of 67.1% for Cline vs. 71.4% for Claude Desktop); Claude Opus 4.1 is the most robust model overall regardless of server or attack type; and counterintuitively GPT-4.1 is more robust than the newer GPT-5-chat-latest, showing that increased model sophistication does not reliably correlate with better resistance to tool poisoning. The generated malicious tools are highly evasive against existing defenses: evasion rates (ER) reach 88.9%/76.6% (IPI) and 95.5%/87.5% (ORM) against MCP-Scan and A.I.G respectively on the Alpaca server, with detection rates as low as roughly 11.1% (MCP-Scan) and 23.4% (A.I.G) overall -- meaning these SOTA defenses are largely ineffective against AutoMalTool's outputs. AutoMalTool is also cheap and fast: average generation cost is under 15,000 tokens (~$0.03) and ~200 seconds per malicious tool, requiring on average only ~2 of a maximum 10 allowed optimization iterations. A notable qualitative finding is that AutoMalTool spontaneously learns to embed special Unicode tokens (e.g., bullet/arrow/warning symbols) in malicious tool descriptions, which measurably enhance attack effectiveness, likely by obfuscating text or introducing misleading visual cues.</t>
+          <t>This SoK synthesizes evidence across four main threat categories (prompt/indirect injection, RAG index/retrieval poisoning, tool/API abuse, and multi-agent emergent risks) and reaches three central conclusions rather than a single quantitative finding: (1) no single safeguard suffices -- layered defenses (content sanitization, provenance tracking, ACL-aware retrieval, typed tool schemas, sandboxing, least-privilege credentials, monitoring, kill-switches) meaningfully reduce unsafe actions and limit blast radius but do not guarantee robustness under worst-case adversarial inputs; (2) security must be measured continuously via attacker-aware metrics (UAR, PED, RRS, TTC, etc.) computed from execution traces, combined with CI-integrated red-teaming for regression control; and (3) cross-disciplinary methods -- formal verification of agent plans/behaviors, hardened retrieval and memory architectures, and policy-as-code governance -- are needed alongside purely technical controls. An evidence-maturity assessment across the surveyed literature finds tool- and retrieval-level attacks are predominantly supported by 'grade A-B' (stronger) evidence, while defenses -- especially at the multi-agent and full-lifecycle level -- remain largely at 'grade C' (weaker) evidence, revealing a significant maturity gap between demonstrated attacks and validated defenses. The illustrative literature evidence cited includes: 19 RCE flaws with working exploits found across 11 LLM-agent frameworks in one cited study, and PoisonedRAG demonstrating high-success targeted RAG manipulation via small corpus perturbations.</t>
         </is>
       </c>
       <c r="F225" s="5" t="n"/>
@@ -10138,7 +10154,7 @@
       <c r="H225" s="5" t="n"/>
       <c r="I225" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -10148,7 +10164,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -10163,7 +10179,7 @@
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>AutoMalTool is compared against two SOTA MCP malicious-tool detection methods as defense baselines it must evade: MCP-Scan (a black-box static-analysis tool metadata scanner) and A.I.G (an LLM-agent-based, more holistic code-analysis detector, reimplemented by the authors using DeepSeek-V3.1 as its backend). The paper also situates its automated approach against prior manual/proof-of-concept red-teaming work (e.g., Song et al., which produced only three hand-crafted weather-related malicious MCP examples), framing AutoMalTool as the first systematic, automated alternative.</t>
+          <t>N/A - not applicable in the empirical sense, since this is a survey/SoK rather than a method paper. The authors instead position their work against prior surveys/frameworks: Deng et al.'s agent-threat survey and Narajala &amp; Narayan's agent-focused threat model (both described as taxonomy/principle-focused, which this SoK complements with a causal threat graph tying vectors to privileged effects and a CI-suitable measurement harness); TRiSM-oriented reviews (described as governance/control-family focused, which this SoK connects to specific tool/RAG attack surfaces and multi-step attack paths); broad LLM-risk surveys (described as centering on standalone-model prompt-level behaviors, which this SoK extends to full agentic pipelines with planners, effectors, and knowledge infrastructure); and community/industry guidance (OWASP LLM Top-10, MITRE ATLAS), which the paper explicitly maps its taxonomy onto (Table 2).</t>
         </is>
       </c>
       <c r="F226" s="5" t="n"/>
@@ -10171,7 +10187,7 @@
       <c r="H226" s="5" t="n"/>
       <c r="I226" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10197,7 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -10196,7 +10212,7 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Black-box attacker who is a malicious user capable of creating and uploading MCP server packages containing malicious tools to open-source package repositories (PyPI, npm) or MCP marketplaces (MCP.so, Smithery), compromising the software supply chain of LLM-based agents whose developers unknowingly install the poisoned package. The attacker has no knowledge of the target LLM-based agent's internal architecture or underlying LLM. The attack (tool poisoning via metadata infection) injects malicious instructions into MCP tool metadata (name, description, input schema) rather than the tool's executable code, exploiting the fact that agents rely on this metadata for tool selection, parameter grounding, and result interpretation. Two attacker objective classes are targeted: incorrect parameter invocation (manipulating the parameter-grounding stage, e.g., causing a trading agent to buy the wrong stock) and output results misinterpretation (manipulating the result-interpretation stage, e.g., causing an agent to draw incorrect conclusions from market data). Generated malicious tools must simultaneously preserve their original benign code functionality (verified via static-code-analysis-based modification), induce the intended malicious behavior in realistic user-task scenarios, and evade existing detection mechanisms such as MCP-Scan and A.I.G.</t>
+          <t>The paper defines a formal threat model with four adversary classes and an associated causal threat graph. External Attacker (Unprivileged): a generic outsider interacting with the agent like a normal user or via public channels (e.g., prompts, malicious links), using techniques like direct prompt-based jailbreaks. Malicious Content Provider: controls data the agent may consume indirectly (e.g., a webpage author embedding hidden prompts, a poisoned PDF, a crafted third-party API response) -- notably, this adversary need not be a user of the system at all, making the threat particularly insidious since the legitimate user unknowingly fetches attacker-controlled content. Supply-Chain Attacker: compromises components the agent depends on (trojaned plugins/packages, poisoned model checkpoints or vector databases at development time). Insider/Developer: has direct access to configuration, prompts, secrets, or corpora (mostly treated as a source of unintentional vulnerabilities, though deliberate weakening of safeguards is also noted). A fifth category, Compromised API/Service, covers an attacker who gains control of an external service the agent trusts (e.g., a compromised email account or vector-database service returning poisoned results). The paper defines a Trusted Computing Base (TCB) comprising core model weights/system prompt, the tool-execution substrate (sandboxes, brokers, schema validators), secret storage/credential issuance, and the RAG indexing pipeline/stores; everything else (user inputs, external content, plugin/tool outputs) is explicitly non-TCB and must be treated defensively. The system assumption is that the LLM is a black-box component vulnerable to prompt manipulation where built-in guardrails are insufficient alone, and operators must assume any malicious instruction reaching the model may be followed -- hence the paper's central defense-in-depth mandate. Assets at risk span the full CIA triad (confidentiality of sensitive data/credentials, integrity of agent behavior/outputs, availability against resource exhaustion/looping) plus alignment/policy integrity and accountability/auditability.</t>
         </is>
       </c>
       <c r="F227" s="5" t="n"/>
@@ -10204,7 +10220,7 @@
       <c r="H227" s="5" t="n"/>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10230,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -10229,7 +10245,7 @@
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>The paper has an explicit Section V-A 'Limitations &amp; Future Directions.' It notes the study focuses on only two malicious behavior types (incorrect parameter invocation and output result manipulation), leaving unexplored other attack classes such as exploiting MCP-tool/agent integration vulnerabilities for unauthorized system access, sensitive-data exfiltration, or tool-shadowing attacks that incorrectly invoke other integrated MCP tools -- flagged as future work. It also frames two further gaps as calls to action rather than self-critiques: current LLM-based agents lack adequate robustness against tool poisoning (motivating future work on adversarial training using AutoMalTool-generated examples), and current malicious-MCP-server detection methods (MCP-Scan, A.I.G) are easily evaded, motivating future development of more robust behavior-based or anomaly-detection approaches, especially since open-source MCP repositories like MCP.so are noted (citing prior work) to lack integrity/security verification mechanisms for hosted packages. A separate 'Potential Ethical Concerns' subsection (V-B) acknowledges the dual-use risk of the research and describes mitigations (restricted code sharing to verified researchers, no upload of malicious packages to public repositories) rather than describing empirical/methodological limitations.</t>
+          <t>The paper has no section explicitly titled 'Limitations,' but the 'Gaps' discussion within Section 5 (Evidence) and the 'Open Problems &amp; Research Directions' Section 7 serve as the closest analogs, identifying concrete unresolved areas rather than caveats about the SoK's own methodology. Identified evidence/knowledge gaps include: post-exploitation persistence and concealment techniques remain underexplored; fine-grained adversarial perturbations in retrieved text are rare in the literature; and common, reproducible testbeds for agent tool misuse are only beginning to appear, with defenses against multi-agent and lifecycle-level threats remaining at markedly weaker ('grade C') evidence maturity than attack techniques. Open research problems explicitly enumerated include formal methods for verifying agent plans and tool-use safety, avoiding evaluator leakage and non-stationarity in benchmarking as models and defenses co-evolve, safe-by-design search spaces for agentic exploration, resilient/verifiable long-term memory, and supply-chain assurance for plugins/dependencies. A dedicated 'LLM usage considerations' statement discloses that LLMs were used for editorial support only, with all outputs reviewed by the authors for accuracy and originality, and that literature review and citation selection were conducted by the human authors.</t>
         </is>
       </c>
       <c r="F228" s="5" t="n"/>
@@ -10237,7 +10253,7 @@
       <c r="H228" s="5" t="n"/>
       <c r="I228" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10263,7 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>SoK: The Attack Surface of Agentic AI - Tools, and Autonomy</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -10262,7 +10278,7 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>This paper presents AutoMalTool, the first automated red-teaming framework for systematically generating malicious Model Context Protocol (MCP) tools -- MCP being the de facto standard (used by ~97.4% of MCP-supporting LLM-based agents, per the MCP documentation) for connecting LLM agents to external tools, resources, and prompts. The paper targets 'tool poisoning' attacks, in which an adversary injects malicious instructions into an MCP tool's metadata (name, description, input schema) rather than its executable code, exploiting the fact that agents rely heavily on this metadata during the three-stage tool-usage workflow (tool selection, parameter grounding, result interpretation) -- prior work on this threat had been limited to a handful of hand-crafted proof-of-concept examples. AutoMalTool is architected as a four-agent collaborative pipeline operating on an existing benign MCP server package: an Initial Generator extracts tool metadata, synthesizes a plausible realistic user task for the target tool, and drafts an initial malicious tool description implementing one of two attacker-specified malicious behavior classes (incorrect parameter invocation or output result misinterpretation); an Oracle checks whether the current tool description would be flagged as malicious by a prompt-injection-style detector; an Effectiveness Evaluator runs the tool within a simulated agent environment to verify the malicious behavior actually manifests during the generated user task, using an LLM-based behavior judge to compare benign versus malicious execution and, on failure, produce a diagnostic failure-reason analysis; and a Tool Optimizer iteratively refines the tool description based on feedback from either the Oracle (to improve detection evasion) or the Effectiveness Evaluator (to improve attack success), looping through this refinement process for up to a fixed maximum number of iterations. A static-code-analysis-based modifier ensures the resulting malicious MCP package preserves its original benign code functionality throughout this process, so the attack remains purely a metadata-level manipulation rather than requiring code changes. Evaluated in a black-box threat model against two mainstream LLM-based agents (Claude Desktop, Cline) across seven backend LLMs and three real-world benign MCP servers spanning finance, messaging, and filesystem domains, the framework demonstrates high generation success, moderate-to-high real-world attack effectiveness (especially for incorrect parameter invocation over output manipulation), strong evasion of current detection methods (MCP-Scan, A.I.G), low financial/time cost, and an emergent tendency to exploit special Unicode tokens in tool descriptions to further boost attack potency -- collectively revealing that MCP's metadata-driven tool ecosystem is a significant, largely undefended supply-chain attack surface for LLM-based agents.</t>
+          <t>This is a systematization-of-knowledge (SoK) paper mapping the attack surface of agentic AI systems -- LLMs augmented with tool/API access, retrieval-augmented generation (RAG) over external corpora, and autonomous multi-agent planning loops -- arguing this combination introduces a qualitatively different and broader attack surface than prior standalone-LLM security work, because autonomous decision-making, persistent state, and direct tool interaction blur trust boundaries between the model, its data, and its execution environment. The paper's central technical contribution is a reference agentic-LLM pipeline architecture (Figure 1) with ten explicitly numbered attack surfaces (AS1-AS10: user input, retrieved-content ingress, tool-call serialization, sandbox boundary, file I/O, API token scope, indexer, retriever/ANN, long-term memory, audit/telemetry) situated relative to a defined Trusted Computing Base, combined with a taxonomy (Table 1) mapping seven attack-goal categories (G1-G7) and five common attack-path patterns (P1-P5) across eight distinct attack-vector classes (prompt/content, RAG indexing, RAG retrieval, tool, API/cloud, state/memory, multi-agent, supply chain) to their typical preconditions and persistence mechanisms, and a causal threat graph formalism (Figure 2) that traces how an attacker's initial foothold (e.g., controlling some ingested content) propagates through the agent's plan-select-execute-update decision loop to a security breach, with defensive controls represented as graph-edge-blocking interventions. Building on this, the paper synthesizes evidence from 20+ peer-reviewed and archival studies (2023-2025) spanning indirect prompt injection, RAG/knowledge-base poisoning, tool/plugin exploitation (including code execution and classic web vulnerabilities like SSRF exposed through weak tool schemas), and multi-agent emergent threats (cascading jailbreaks, cross-agent manipulation), grading the empirical maturity of each vector's supporting evidence. It also introduces seven formally-defined attacker-aware security metrics intended to be computed directly from agent execution traces for continuous, CI-integrable security measurement: Unsafe Action Rate (UAR, fraction of test scenarios triggering a policy-violating action), Policy Adherence Rate (PAR), Privilege-Escalation Distance (PED, graph-distance-based measure of how close an attack came to a privileged asset on the causal threat graph), Retrieval Risk Score (RRS, a weighted sum of per-document risk features for a retrieved bundle, usable to gate autonomy or trigger human-in-the-loop review), Time-to-Contain (TTC), Out-of-Role Action Rate (OORAR, fraction of executed actions violating an explicit role/tool contract), and Cost-Exploit Susceptibility (CES, expected monetary loss under an adversarial policy over a fixed horizon) -- alongside a sketched minimal reproducible benchmarking harness (randomized seeds, replayed scenarios, structured trace/metric export) for longitudinal, head-to-head comparison across agent systems and defenses. The paper closes with a defense-in-depth framework spanning pre-ingestion/indexing, inference-time, planning/acting, and infrastructure/monitoring layers (detailed in Appendix A) and a phased practitioner security checklist for deployment, runtime monitoring, and incident response (Appendix B), concluding that layered defenses meaningfully reduce risk but that no single safeguard is sufficient under worst-case adversarial conditions.</t>
         </is>
       </c>
       <c r="F229" s="5" t="n"/>
@@ -10270,7 +10286,7 @@
       <c r="H229" s="5" t="n"/>
       <c r="I229" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>db437d3cdc6b1a5910d0d89fc120f400b9ac80fc</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10296,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -10303,7 +10319,7 @@
       <c r="H230" s="5" t="n"/>
       <c r="I230" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10313,7 +10329,7 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -10336,7 +10352,7 @@
       <c r="H231" s="5" t="n"/>
       <c r="I231" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10362,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -10369,7 +10385,7 @@
       <c r="H232" s="5" t="n"/>
       <c r="I232" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10395,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -10402,7 +10418,7 @@
       <c r="H233" s="5" t="n"/>
       <c r="I233" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10412,7 +10428,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -10427,7 +10443,7 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F234" s="5" t="n"/>
@@ -10435,7 +10451,7 @@
       <c r="H234" s="5" t="n"/>
       <c r="I234" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10461,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -10460,7 +10476,7 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="F235" s="5" t="n"/>
@@ -10468,7 +10484,7 @@
       <c r="H235" s="5" t="n"/>
       <c r="I235" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10494,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -10501,7 +10517,7 @@
       <c r="H236" s="5" t="n"/>
       <c r="I236" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10511,7 +10527,7 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -10526,7 +10542,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F237" s="5" t="n"/>
@@ -10534,7 +10550,7 @@
       <c r="H237" s="5" t="n"/>
       <c r="I237" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10544,7 +10560,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -10559,7 +10575,7 @@
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F238" s="5" t="n"/>
@@ -10567,7 +10583,7 @@
       <c r="H238" s="5" t="n"/>
       <c r="I238" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10577,7 +10593,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -10600,7 +10616,7 @@
       <c r="H239" s="5" t="n"/>
       <c r="I239" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10626,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -10625,7 +10641,7 @@
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F240" s="5" t="n"/>
@@ -10633,7 +10649,7 @@
       <c r="H240" s="5" t="n"/>
       <c r="I240" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10643,7 +10659,7 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -10658,7 +10674,7 @@
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Code released at https://github.com/Peregrine123/TRACE_official.</t>
+          <t>Y — the abstract states 'The dataset, code, videos, and other material can be found at the following link: https://nvidia-ai-iot.github.io/remembr', and the paper notes the code release will include multiple LLM backend options for community use.</t>
         </is>
       </c>
       <c r="F241" s="5" t="n"/>
@@ -10666,7 +10682,7 @@
       <c r="H241" s="5" t="n"/>
       <c r="I241" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10692,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -10691,7 +10707,7 @@
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>TRACE is evaluated on four backbone models: Qwen3Guard-Gen-4B, Qwen3-4B-Instruct-2507, Qwen3-8B, and Llama-3.1-8B. For each backbone, the Compressor and Reader are both initialized from that same frozen backbone (only Compressor query tokens, LoRA adapters, and the Reader classification head are trained). Compared against Base (zero-shot backbone), SFT (fully fine-tuned backbone), AgentAuditor (a retrieval-augmented guardrail consulting external safety guidelines), and MAGE (a shadow-memory-based online trajectory monitor, described as the strongest and most directly comparable memory-augmented baseline).</t>
+          <t>GPT-4o (closed-source) is the primary LLM backend for ReMEmbR's querying agent; open-source alternatives Codestral-22B, Command-R, and Llama3.1-8B are also evaluated as ReMEmbR backends. Video captioning uses VILA (VILA1.5-13b for main experiments; VILA1.5-8b and VILA1.5-3b compared in ablations; a quantized VILA-3b for the on-robot deployment). Captions are embedded with mxbai-embed-large-v1. Baselines reuse GPT-4o as an 'LLM with Caption' (all captions given at once) and a 'Multi-Frame VLM' (frames sampled at 2 FPS given directly). Whisper is used for speech recognition in the robot deployment only.</t>
         </is>
       </c>
       <c r="F242" s="5" t="n"/>
@@ -10699,7 +10715,7 @@
       <c r="H242" s="5" t="n"/>
       <c r="I242" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10725,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -10724,7 +10740,7 @@
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Three main long-horizon agent-safety benchmarks: ASSEBench (diverse multi-turn risk scenarios, loose labeling standard used), Pre-Ex-Bench (pre-execution alignment risk scenarios, controllable risk synthesis), and R-Judge (curated multi-turn interaction cases across 5 application domains with trajectory-level safety annotations). A fourth benchmark, LongSafety, is used specifically for context-length robustness analysis via a controlled relevance-sorted stress-test protocol at length buckets 0k, 0.1k, 0.3k, 0.5k, 1k, 2k, 4k, and 8k+ tokens, with Safety Rate as the metric; a diagnostic split from LongSafety is also bucketed into sparse, delayed, compositional, and mixed/excluded evidence regimes for finer-grained analysis.</t>
+          <t>NaVQA, a new dataset introduced by the paper: 210 spatial/point-in-time/duration/descriptive questions annotated by 5 robot experts over 7 long-horizon navigation video sequences (15-30 minutes each, indoor/outdoor, various lighting/weather) drawn from the CODa robot navigation dataset (Clearpath Husky robot), subsampled into short (&lt;2 min), medium (2-7 min), and long (&gt;7 min) segments (30 questions per sequence, 210 total).</t>
         </is>
       </c>
       <c r="F243" s="5" t="n"/>
@@ -10732,7 +10748,7 @@
       <c r="H243" s="5" t="n"/>
       <c r="I243" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10758,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -10757,7 +10773,7 @@
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>TRACE achieves the best Accuracy across all four backbones and all three main benchmarks (Table 1), improving over Base by 28-52 percentage points and over SFT by 0.83-14.62 percentage points (4.91-13.16pp on ASSEBench, 1.57-14.62pp on Pre-Ex-Bench, 0.83-2.88pp on R-Judge); on F1 and Unsafe Recall TRACE leads in most settings, though SFT occasionally slightly exceeds it on R-Judge, attributed to R-Judge's shorter contexts reducing the need for long-span evidence aggregation. Concretely, on Qwen3-8B, TRACE reaches 91.57% Accuracy on ASSEBench (vs. 83.14% for MAGE and 80.17% for SFT), 92.06% on Pre-Ex-Bench (vs. 90.87% MAGE), and 93.40% on R-Judge (vs. 92.56% MAGE). On the LongSafety length-robustness stress test, MAGE's safety rate degrades sharply from 78% to 55% as context length grows to 8k+ tokens, while TRACE degrades much more slowly (79% to 76%), yielding roughly a 20-point advantage over MAGE at the longest length bucket and demonstrating markedly better robustness to evidence dilution as trajectories lengthen. Attention visualizations show the compressed latent evidence state is associated with attention shifts toward risk-critical trajectory segments, and ablations (removing the compressed reference pathway) cause sharper accuracy degradation, alongside cross-sample latent-swap and token-shuffle control experiments confirming the gains reflect learned risk-aware compression rather than an artifact of extra parameters or noise.</t>
+          <t>ReMEmbR (GPT-4o backend) achieves the best descriptive-question accuracy, positional error, and temporal error on long-duration videos compared to the 'LLM with Caption' and 'Multi-Frame VLM' baselines, and performs comparably to the VLM baseline on short videos while the VLM baseline fails entirely on medium/long videos due to context-window limits. Overall correctness for ReMEmbR is 0.72/0.56/0.61 (short/medium/long) versus 0.67/0.48/0.50 for a single-retrieval-call ablation and 0.54/0.50/0.38 for a coarser 12-second-caption ablation. ReMEmbR's per-question latency is roughly constant (~25 seconds for a 21.5-minute video) regardless of video length, versus ~90 seconds for the VLM baseline on a much shorter 5.5-minute video. Open-source LLM backends (Codestral, Command-R, Llama3.1-8B) substantially underperform GPT-4o, attributed to weaker arithmetic/spatiotemporal reasoning despite being tuned for function calling.</t>
         </is>
       </c>
       <c r="F244" s="5" t="n"/>
@@ -10765,7 +10781,7 @@
       <c r="H244" s="5" t="n"/>
       <c r="I244" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10791,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -10790,7 +10806,7 @@
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>Base (zero-shot backbone, no task-specific adaptation, lower bound), SFT (full supervised fine-tuning on safety detection data, adaptation upper bound), AgentAuditor (retrieval-augmented guardrail consulting external safety guidelines during judgment), and MAGE (a fixed-size shadow-memory method that incrementally accumulates safety context across interaction steps, the strongest memory-augmented baseline and most direct comparison to TRACE's compression approach).</t>
+          <t>'LLM with Caption' (GPT-4o given all video captions concatenated at once, no retrieval) and 'Multi-Frame VLM' (GPT-4o given video frames sampled at 2 FPS directly, no retrieval) — both of which are shown to fail on medium/long videos due to fixed context-window limits.</t>
         </is>
       </c>
       <c r="F245" s="5" t="n"/>
@@ -10798,7 +10814,7 @@
       <c r="H245" s="5" t="n"/>
       <c r="I245" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10808,7 +10824,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -10823,7 +10839,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>This is a security/safety paper with an explicit (defensive, detection-oriented) threat model: long-horizon LLM agent trajectories can contain safety risks that are sparse (only a small fraction of steps carry risk signals, easily overwhelmed by benign content), delayed (risk consequences surface only many steps after the originating cue, creating long causal spans), and compositional (multiple individually-safe steps become dangerous only when combined in a specific sequence) -- exemplified by multi-step tool misuse, delayed attack chains, and persistent context manipulation that gradually corrupts agent memory. The paper's goal is a detector (TRACE) that aggregates this dispersed evidence across an entire trajectory for accurate safety classification, in contrast to per-turn/local moderation guardrails (e.g., Llama Guard, ShieldGemma) that only see a short rolling context and can miss such distributed risk signals.</t>
+          <t>N/A - non-adversarial. The paper addresses the incidental failure mode of context/memory scalability: robots' inability to reason over arbitrarily long deployment histories within the fixed context windows of transformer-based LLMs/VLMs, not any adversarial actor.</t>
         </is>
       </c>
       <c r="F246" s="5" t="n"/>
@@ -10831,7 +10847,7 @@
       <c r="H246" s="5" t="n"/>
       <c r="I246" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10857,7 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
@@ -10856,7 +10872,7 @@
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>Explicit 'Limitations' section (Section 6) noting: (1) experiments abstract away several deployment factors including authentication flows, rate limits, multi-user interaction, and complex permission hierarchies; (2) training data reflects existing risk taxonomies and annotation policies, so performance under unseen risk categories or substantially different labeling standards remains an open question; (3) the latent evidence state S, while improving compactness, is not directly human-readable, which can make auditing harder in high-stakes deployment settings. An Ethical Considerations section additionally notes the work could include prompts/tools potentially misusable against LLM agents and states the methods are intended for academic reference only, not real-world harmful application.</t>
+          <t>The paper has an explicit 'Limitations and Future Work' section. (1) NaVQA enforces a single unique correct answer per question, whereas real-world deployments often admit multiple valid answers, requiring more focus on contextual reasoning. (2) The memory-building approach relies solely on video captioning and does not incorporate other rich spatial information sources (e.g., room numbers, equipment labels, semantic maps, scene graphs, queryable scene representations) that could be added as additional memory/function-call types. (3) The vector database continuously accumulates potentially repetitive information over time without pruning, which the authors state 'would dilute useful information over time,' flagging efficient memory aggregation as future work. The qualitative robot deployment section also reports concrete failure cases (e.g., confusing a water fountain for a 'soda machine') attributed to the smaller quantized 3B captioning model used on-device.</t>
         </is>
       </c>
       <c r="F247" s="5" t="n"/>
@@ -10864,7 +10880,7 @@
       <c r="H247" s="5" t="n"/>
       <c r="I247" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10890,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -10889,7 +10905,7 @@
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>TRACE (Trajectory Risk-Aware Compression for Long-Horizon Agent Safety) reframes long-horizon LLM agent safety detection as a trajectory-level evidence compression problem, addressing the failure of per-turn or short-context safety guardrails (e.g., Llama Guard, ShieldGemma) to reliably retain and aggregate safety evidence that is sparse, delayed, and compositional across long multi-step agent trajectories. The architecture uses a Compressor-Reader design: a Compressor module encodes the full raw trajectory into a compact latent evidence state S (using a fixed budget of K=16 learned query tokens attending over the trajectory, related conceptually to the Information Bottleneck principle) under trajectory-level supervision, selectively retaining risk-critical signals regardless of where they occur in the sequence. Because compression inevitably discards fine-grained local detail, the Reader then performs the final safety judgment using a dual-input design: it processes the raw trajectory as the primary evidence source (preserving complete detail) concatenated with the latent evidence state S (mapped into the Reader's embedding space via a linear projection) as an auxiliary safety reference that helps reweight attention toward risk-critical segments -- avoiding both premature evidence loss (a limitation of incremental memory-based baselines like MAGE, which may overwrite early weak cues before the trajectory fully unfolds) and the information loss of a naive summarize-then-judge pipeline. Both the Compressor and Reader are initialized from the same frozen backbone LLM, with only the Compressor's query tokens, LoRA adapters, and the Reader's classification head trained via binary cross-entropy loss, keeping the approach parameter-efficient relative to full supervised fine-tuning. The design specifically targets three empirically-motivated evidence patterns in long-horizon agent risk (sparse, delayed, compositional), and the paper provides both quantitative benchmark results and qualitative attention-visualization/case-study evidence that the compressed reference mechanism helps the Reader recover cross-step risk evidence that local or purely-incremental-memory approaches tend to miss.</t>
+          <t>ReMEmbR (Retrieval-augmented Memory for Embodied Robots) addresses long-horizon video question answering for robot navigation by decomposing the problem into a memory-building phase and a querying phase, avoiding the impracticality of feeding unbounded histories into a transformer's fixed context window. During memory building, the robot's video stream is segmented into t-second chunks, each captioned by a VLM (VILA), and the caption embedding (via mxbai-embed-large-v1) together with the corresponding position and timestamp is stored in a vector database V, built without knowledge of any future question. During querying, an LLM-agent acts as an iterative state machine (up to k=3 rounds) that issues up to three retrieval function calls per round — text retrieval, position retrieval, or time retrieval — against V, accumulating retrieved memories until it judges the question answerable, at which point it emits a structured JSON answer (text, position, time, or duration). To evaluate this approach on robot-centric long-horizon reasoning, the authors construct the NaVQA dataset from real robot navigation videos and compare ReMEmbR against non-retrieval baselines that feed the entire caption history or entire frame history directly to a VLM/LLM, showing ReMEmbR scales to much longer histories with near-constant latency. The system is further deployed in real time on a Nova Carter robot (on-device VILA-3b captioning, Nav2/AMCL localization, Whisper ASR, cloud or local LLM backend), demonstrating the ability to answer navigation-centric natural-language questions and generate metric goals after a 25-minute memory-building run in a real office environment.</t>
         </is>
       </c>
       <c r="F248" s="5" t="n"/>
@@ -10897,7 +10913,7 @@
       <c r="H248" s="5" t="n"/>
       <c r="I248" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
         </is>
       </c>
     </row>
@@ -10907,7 +10923,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -10930,7 +10946,7 @@
       <c r="H249" s="5" t="n"/>
       <c r="I249" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10956,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -10955,7 +10971,7 @@
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>ML/AI</t>
         </is>
       </c>
       <c r="F250" s="5" t="n"/>
@@ -10963,7 +10979,7 @@
       <c r="H250" s="5" t="n"/>
       <c r="I250" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10989,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -10996,7 +11012,7 @@
       <c r="H251" s="5" t="n"/>
       <c r="I251" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11022,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -11021,7 +11037,7 @@
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>defense</t>
         </is>
       </c>
       <c r="F252" s="5" t="n"/>
@@ -11029,7 +11045,7 @@
       <c r="H252" s="5" t="n"/>
       <c r="I252" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11055,7 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -11054,7 +11070,7 @@
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>tool-output</t>
         </is>
       </c>
       <c r="F253" s="5" t="n"/>
@@ -11062,7 +11078,7 @@
       <c r="H253" s="5" t="n"/>
       <c r="I253" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11088,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -11087,7 +11103,7 @@
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>data-exfiltration</t>
+          <t>reasoning-corruption</t>
         </is>
       </c>
       <c r="F254" s="5" t="n"/>
@@ -11095,7 +11111,7 @@
       <c r="H254" s="5" t="n"/>
       <c r="I254" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11121,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -11120,7 +11136,7 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F255" s="5" t="n"/>
@@ -11128,7 +11144,7 @@
       <c r="H255" s="5" t="n"/>
       <c r="I255" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11154,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -11153,7 +11169,7 @@
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F256" s="5" t="n"/>
@@ -11161,7 +11177,7 @@
       <c r="H256" s="5" t="n"/>
       <c r="I256" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11171,7 +11187,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -11186,7 +11202,7 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F257" s="5" t="n"/>
@@ -11194,7 +11210,7 @@
       <c r="H257" s="5" t="n"/>
       <c r="I257" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11220,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -11219,7 +11235,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>cross-session-dormant</t>
+          <t>session-persistent</t>
         </is>
       </c>
       <c r="F258" s="5" t="n"/>
@@ -11227,7 +11243,7 @@
       <c r="H258" s="5" t="n"/>
       <c r="I258" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11237,7 +11253,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -11260,7 +11276,7 @@
       <c r="H259" s="5" t="n"/>
       <c r="I259" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11286,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -11285,7 +11301,7 @@
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>N - no code or attack-tooling release link is given</t>
+          <t>The paper explicitly states: 'We open source Slipstream at https://github.com/chenzhuofu/slipstream' -- a full open-source release of the Slipstream system implementation.</t>
         </is>
       </c>
       <c r="F260" s="5" t="n"/>
@@ -11293,7 +11309,7 @@
       <c r="H260" s="5" t="n"/>
       <c r="I260" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11319,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -11318,7 +11334,7 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>Four Clio configurations (extractor/summarizer pairs): Qwen3 (4B/30B), Gemma3 (4B/27B), LLaMA3 (8B/70B), Claude (Haiku 3/Sonnet 4.5); target-chat generation via Claude Sonnet 4.5</t>
+          <t>Two models instruction-tuned for long-horizon agentic tasks: Qwen3.5-9B (a hybrid Mixture-of-Experts model) and Seed-OSS-36B-Instruct (a dense Transformer model). The same model architecture is used to instantiate both the agent and the compaction judge (using a structured prompt), and the paper notes judge validation quality is largely insensitive to model choice.</t>
         </is>
       </c>
       <c r="F261" s="5" t="n"/>
@@ -11326,7 +11342,7 @@
       <c r="H261" s="5" t="n"/>
       <c r="I261" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11336,7 +11352,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -11351,7 +11367,7 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>WildChat (1M conversations, random 1K-chat samples used for clustering) mixed with 100 synthetically generated medical target chats built from the NLICE synthetic patient-record dataset (47 diseases)</t>
+          <t>Two long-horizon agent workloads: BrowseComp (evaluates web-browsing agents that must maintain search progress and entity constraints across many tool calls) and SWE-bench Verified (evaluates coding agents that must preserve issue context, test outcomes, and repository observations over multi-step debugging trajectories). These are chosen to stress different forms of trajectory state -- BrowseComp primarily search-state maintenance, SWE-bench both factual observations and evolving code-editing plans -- evaluated across multiple compaction thresholds (active-context token counts at which compaction triggers: 4k/6k/8k for SWE-bench, 16k/24k/32k/48k/64k for BrowseComp).</t>
         </is>
       </c>
       <c r="F262" s="5" t="n"/>
@@ -11359,7 +11375,7 @@
       <c r="H262" s="5" t="n"/>
       <c r="I262" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11369,7 +11385,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -11384,7 +11400,7 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>Cliopatra extracts a target user's medical history with nearly 100% precision in up to 65% of attack attempts (versus a 22% baseline for an adversary using only public information); a regex-augmented variant ('C-Regex Attack') achieves nearly 4x improvement over baseline while maintaining 100% precision; stealthy variants can obfuscate leaked information in the generated insights to evade both human and Clio's built-in LLM-based privacy auditor, which the authors show fails to detect major leaks.</t>
+          <t>Slipstream improves task accuracy over synchronous compaction (Sync) in every tested configuration, by up to 8.8 percentage points, while reducing end-to-end latency by up to 39.7%. On SWE-bench Verified with Qwen3.5-9B, accuracy improves from 23.4% to 29.8% (+6.4pp) at a 4k threshold, from 22.0% to 30.8% (+8.8pp) at 6k, and from 20.4% to 29.2% (+8.8pp) at 8k; with Seed-OSS-36B, improvements range from +2.6pp to +6.6pp across thresholds. On BrowseComp, improvements are smaller but consistent, ranging from +1.3pp to +4.6pp across models and thresholds. The paper reports that compaction judge rejection (indicating the candidate summary would have changed downstream agent behavior in a trajectory-relevant way) is empirically rare -- 1.0-3.5% of cases on BrowseComp and 5.4-8.5% on SWE-bench Verified -- meaning Slipstream retains most of its latency benefit from the common accept path while using targeted repair as a guardrail specifically for the minority of cases where synchronous compaction would have silently corrupted the trajectory. Beyond the main accuracy/latency results, the paper also reports that synchronous compaction as deployed today inflates end-to-end agent execution times by 26-44% across mainstream workloads (a baseline finding motivating the work), and that Slipstream's judge processes lightweight inputs (only the candidate compacted state and the next-k continuation trajectory, typically 3.6-6.8% of the pre-compaction context size) to keep validation overhead low.</t>
         </is>
       </c>
       <c r="F263" s="5" t="n"/>
@@ -11392,7 +11408,7 @@
       <c r="H263" s="5" t="n"/>
       <c r="I263" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11402,7 +11418,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -11417,7 +11433,7 @@
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>A baseline adversary that infers the target's disease solely from public information without observing any Clio output; existing ad hoc mitigation in the form of Clio's own LLM-based privacy-auditing step, shown to be unreliable at detecting the attack's leaks</t>
+          <t>Synchronous compaction (Sync), the standard deployed approach in modern agent frameworks, where compaction blocks agent execution and always adopts the resulting compacted context regardless of whether it faithfully preserves trajectory-relevant information -- compared against Slipstream at matched compaction thresholds across both models and both workloads.</t>
         </is>
       </c>
       <c r="F264" s="5" t="n"/>
@@ -11425,7 +11441,7 @@
       <c r="H264" s="5" t="n"/>
       <c r="I264" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11451,7 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -11450,7 +11466,7 @@
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>An external adversary with only account-level access to the platform (no access to the target's raw chats) inserts a small number of carefully crafted 'poison' chats designed to simultaneously (1) bypass PII redaction, (2) cluster with the target user's chat under the platform's clustering step, (3) trigger exposure of the target's sensitive information in the resulting aggregated cluster summary, and (4) obfuscate that exposure to evade human or automated (LLM-based) privacy auditors; the adversary is assumed to know only basic demographics (age, gender) and a subset of symptoms about the target.</t>
+          <t>N/A - non-adversarial. This is a systems/reliability paper on context compaction for long-horizon LLM agents, not a security paper; the incidental failure mode of interest is a structural validation gap in synchronous compaction: the compactor (an LLM invoked to rewrite accumulated agent trajectory into a shorter summary) must decide what information to preserve without knowing what the agent will actually need in future steps, and because synchronous execution always adopts the resulting summary before any subsequent agent behavior is observed, there is no way to validate whether the compacted summary faithfully preserved the agent's forward intent and the key facts/constraints it depends on -- errors (dropped constraints, mutated entities, lost task intent) then silently propagate through subsequent agent steps as coherent-looking but incorrect behavior, contributing to the broader 'context rot' phenomenon where accuracy degrades with context length even when all relevant information remains technically present.</t>
         </is>
       </c>
       <c r="F265" s="5" t="n"/>
@@ -11458,7 +11474,7 @@
       <c r="H265" s="5" t="n"/>
       <c r="I265" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11468,7 +11484,7 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -11483,7 +11499,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>The attack and Clio both focus on text-based summarization; extending to multimodal (image/file) conversations is left to future work. Cliopatra currently targets one chat at a time rather than performing an untargeted or simultaneous multi-chat attack, and it is unclear how inserting multiple distinct poisons would affect clustering or per-chat targeting effectiveness. For ethical reasons, the authors attack a local replication of Clio using synthetic data rather than a live deployed system.</t>
+          <t>The paper does not contain a section titled 'Limitations' (no matching header found after thorough search); the Conclusion frames the work's core insight and broader implication rather than enumerating explicit unresolved caveats, stating that 'running auxiliary procedures synchronously on an agent's critical path can foreclose validation signals that asynchrony makes available -- a pattern worth examining beyond compaction itself,' implicitly suggesting the current work's scope is limited to the compaction use case specifically, with generalization to other synchronous agent-pipeline components left unexplored. The paper does transparently document, as an operational caveat rather than a formal limitation, that in rare cases (structural drift too pervasive to repair locally) Slipstream's targeted-update repair mechanism cannot recover the compacted state and the system falls back to full synchronous compaction from scratch.</t>
         </is>
       </c>
       <c r="F266" s="5" t="n"/>
@@ -11491,7 +11507,7 @@
       <c r="H266" s="5" t="n"/>
       <c r="I266" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11517,7 @@
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -11516,7 +11532,7 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>Introduces Cliopatra, the first privacy attack against 'privacy-preserving' LLM-based insights systems such as Anthropic's Clio, combining data poisoning, prompt injection, and attribute-inference techniques. An adversary inserts malicious chats that simultaneously defeat PII redaction, cluster with a target user's conversation, force the target's sensitive information into the generated cluster-summary insight, and obfuscate that leak to evade privacy auditors. Evaluated by replicating Clio locally across four LLM families (Qwen3, Gemma3, LLaMA3, Claude) using WildChat data mixed with synthetic medical target chats, extracting a target's medical history with up to 65% success rate and near-100% precision, far above a public-information-only baseline, and shows the platform's own LLM-based privacy auditor fails to catch most leaks even for stealthy attack variants.</t>
+          <t>Slipstream is a trajectory-grounded compaction system for long-horizon LLM agents that addresses a structural validation gap in how modern agent frameworks perform context compaction (using an LLM to periodically rewrite accumulated trajectory history into a shorter summary the agent resumes from, to combat context-length-driven accuracy degradation known as 'context rot'). As deployed today, compaction runs synchronously on the critical path of agent execution: the agent pauses, the compactor produces a summary, and the agent unconditionally resumes from that summary -- but because the compactor must decide what to preserve without knowing what the agent will actually need in subsequent steps, and because synchronous execution provides no mechanism to check this prediction before committing to it, compaction errors (dropped constraints, corrupted entities, lost task intent) silently propagate through coherent-but-incorrect downstream agent behavior. Slipstream's key insight is that running the compactor asynchronously -- in parallel with the agent continuing to execute on the original, uncompacted context -- generates both the candidate compacted summary and the agent's actual subsequent reasoning/behavior independently from the same shared pre-compaction state, producing a validation signal that no synchronous configuration can construct: the agent's continued behavior on the full context serves as ground truth against which the candidate summary can be checked. Concretely, Slipstream uses a judge model to validate the candidate summary against the agent's continued reasoning trajectory, checking specifically that the summary preserves both the agent's forward intent and the key facts/constraints its subsequent behavior depends on. On judge acceptance, execution swaps to the compacted state augmented with the next-k continuation steps that completed during the parallel compaction window, since the judge has already verified consistency, allowing the live agent to safely continue with reduced context. On judge rejection, Slipstream performs a targeted, surgical update to the compacted state (using the judge's diagnosis and evidence from the uncompacted continuation to repair only the specific trajectory-relevant omission or corruption, e.g., restoring a dropped constraint or correcting a mutated entity) rather than re-running compaction entirely from scratch, falling back to full synchronous compaction only in rare cases where the drift is too pervasive to repair locally. To make asynchronous execution practical at low overhead, Slipstream exploits the fact that long-horizon agent serving is typically memory-bound rather than compute-bound (leaving compute headroom to run the compactor and judge alongside the main agent), and further optimizes memory usage by having the agent and compaction threads share the same pre-compaction context prefix in the KV cache (via multi-layer cascade attention) rather than materializing duplicate copies, while keeping the judge's own input lightweight (only the candidate summary plus the next-k continuation, typically a small fraction of the full pre-compaction context).</t>
         </is>
       </c>
       <c r="F267" s="5" t="n"/>
@@ -11524,7 +11540,7 @@
       <c r="H267" s="5" t="n"/>
       <c r="I267" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11550,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -11557,7 +11573,7 @@
       <c r="H268" s="5" t="n"/>
       <c r="I268" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11567,7 +11583,7 @@
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -11582,7 +11598,7 @@
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>ML/AI</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="F269" s="5" t="n"/>
@@ -11590,7 +11606,7 @@
       <c r="H269" s="5" t="n"/>
       <c r="I269" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11616,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -11623,7 +11639,7 @@
       <c r="H270" s="5" t="n"/>
       <c r="I270" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11633,7 +11649,7 @@
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -11648,7 +11664,7 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="F271" s="5" t="n"/>
@@ -11656,7 +11672,7 @@
       <c r="H271" s="5" t="n"/>
       <c r="I271" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11682,7 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -11689,7 +11705,7 @@
       <c r="H272" s="5" t="n"/>
       <c r="I272" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11699,7 +11715,7 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
@@ -11714,7 +11730,7 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="F273" s="5" t="n"/>
@@ -11722,7 +11738,7 @@
       <c r="H273" s="5" t="n"/>
       <c r="I273" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11732,7 +11748,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -11747,7 +11763,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F274" s="5" t="n"/>
@@ -11755,7 +11771,7 @@
       <c r="H274" s="5" t="n"/>
       <c r="I274" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11765,7 +11781,7 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -11788,7 +11804,7 @@
       <c r="H275" s="5" t="n"/>
       <c r="I275" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11814,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -11821,7 +11837,7 @@
       <c r="H276" s="5" t="n"/>
       <c r="I276" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11847,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -11846,7 +11862,7 @@
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>session-persistent</t>
+          <t>one-shot</t>
         </is>
       </c>
       <c r="F277" s="5" t="n"/>
@@ -11854,7 +11870,7 @@
       <c r="H277" s="5" t="n"/>
       <c r="I277" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11880,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -11887,7 +11903,7 @@
       <c r="H278" s="5" t="n"/>
       <c r="I278" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11897,7 +11913,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
@@ -11910,17 +11926,13 @@
           <t>secondary</t>
         </is>
       </c>
-      <c r="E279" s="2" t="inlineStr">
-        <is>
-          <t>No public code repository URL is given in the extracted main text. The paper describes an internal 'versatile integration platform' supporting arbitrary sandboxed research/engineering tasks, and provides a notation table (Table 3) and a list of supported task types (Table 4) in the appendix, but no explicit GitHub or other public artifact link is present in the available text.</t>
-        </is>
-      </c>
+      <c r="E279" s="2" t="n"/>
       <c r="F279" s="5" t="n"/>
       <c r="G279" s="5" t="n"/>
       <c r="H279" s="5" t="n"/>
       <c r="I279" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11930,7 +11942,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -11945,7 +11957,7 @@
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>Gemini 2.5 Pro is used as the primary backbone LLM across most experiments (Symbolic Regression/LLM-SR and KernelBench), with Gemini 2.5 Flash as a secondary/ensemble model for frameworks supporting model ensembles. Gemini 3 Pro is used as the backbone for the more complex Modded NanoGPT experiment. PACEvolve is compared against baseline evolutionary frameworks including uDSR, LLM-SR, OpenEvolve, CodeEvolve, and ShinkaEvolve, all run with the same LLM backbones for fair comparison.</t>
+          <t>Six target LLMs: Llama-3-8B (Meta, 8B), Gemma-2B-Instruct (Google, 2B), InternLM-2-7B-Chat (InternLM, 7B), Mistral-7B-Instruct (Mistral AI, 7.3B), Llama-2-7B-Chat-HF (Meta, 7B), and GPT-3.5-Turbo (OpenAI, 175B), each evaluated under diverse defense strategies.</t>
         </is>
       </c>
       <c r="F280" s="5" t="n"/>
@@ -11953,7 +11965,7 @@
       <c r="H280" s="5" t="n"/>
       <c r="I280" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11963,7 +11975,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -11978,7 +11990,7 @@
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>Three benchmarks: LLM-SR (symbolic regression, evaluated via Log10 Normalized Mean Squared Error/NMSE on a Nonlinear Oscillator task, 10 repeated runs), KernelBench (GPU kernel optimization, 16 sampled kernels spanning activation functions, normalization layers, operators, and full models like MLP/RNN/VGG16/AlexNet, benchmarked on a single A100 40GB GPU with 1000 iterations per kernel against the PyTorch baseline and KernelBench Leaderboard v0.1), and Modded NanoGPT (a heavily community-optimized language-model-training-speed benchmark, evaluated by time-to-reach validation loss 3.28 on FineWeb using 8 H100 GPUs).</t>
+          <t>No external benchmark surfaced. Attack scenarios are generated by the framework itself, with conversation histories containing sensitive information serving as the extraction target; evaluation spans the six-model panel crossed with multiple defense strategies.</t>
         </is>
       </c>
       <c r="F281" s="5" t="n"/>
@@ -11986,7 +11998,7 @@
       <c r="H281" s="5" t="n"/>
       <c r="I281" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -11996,7 +12008,7 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
@@ -12011,7 +12023,7 @@
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>On LLM-SR, PACEvolve-Single outperforms all baselines (uDSR, LLM-SR, OpenEvolve, CodeEvolve, ShinkaEvolve) on best, worst, mean, and P75 log10-NMSE, achieving best NMSE of -8.23 versus the next-best CodeEvolve's -7.26; PACEvolve-Multi further improves P75 and mean NMSE (best -8.24, mean -6.11), discovering 3 solutions with log10 NMSE below -8, supporting the hypothesis that the self-adaptive crossover mechanism effectively synergizes across islands once at least one finds a promising direction. On KernelBench (16 kernels), both PACEvolve-Single and PACEvolve-Multi outperform the best existing KernelBench-leaderboard kernels in every tested case; PACEvolve-Single outperforms ShinkaEvolve on all 16 kernels and PyTorch on all but 2 (MLP and large-k MatMul, both heavily hand-optimized in PyTorch); PACEvolve-Multi outperforms PACEvolve-Single in 13/16 (81.25%) of kernels and found equivalent-or-better kernels than ShinkaEvolve/CodeEvolve in 14/16 cases and OpenEvolve in 15/16 cases, with maximum discovered speedups over PyTorch ranging up to 17.38x (LayerNorm) and 3.95x (ConvMax). On Modded NanoGPT (an environment optimized down from ~2700s in version 1 to 142s by version 40 prior to this work), PACEvolve discovers a sequence of incremental but nontrivial improvements -- data-loading/sharding optimization (142.8s to 141.9s), a novel U-shaped skip-connection weight initialization (141.9s to 141.5s), joint hyperparameter tuning across logit softcapping, Distributed Adam beta1, YaRN alpha, and token-smearing lambda (141.5s to 140.8s), and dynamic context-window scheduling (140.8s to 140.2s) -- collectively surpassing the prior record on an already heavily optimized benchmark. Ablation studies (on the Symbolic Regression task) show each of PACEvolve's three components contributes incrementally: adding Hierarchical Context Management alone improves mean/best performance but leaves worst-case runs stuck (since it only prunes low-performing ideas, not a locally-optimal-but-suboptimal best idea); adding Momentum-Based Backtracking on top eliminates the low-performing/stuck runs but slightly reduces best-case performance (since backtracking forces more frequent exploration, reducing budget devoted to LLM-preferred exploitative refinement); and adding Collaborative Evolution Sampling on top of both preserves backtracking's elimination of low performers while substantially improving mean and P75 performance, demonstrating the full three-component recipe achieves the best overall trade-off.</t>
+          <t>The evaluation is unusually broad on the model axis for an attack paper of this period, spanning six target LLMs across scale and provider: Llama-3-8B (Meta, 8B), Gemma-2B-Instruct (Google, 2B), InternLM-2-7B-Chat (InternLM, 7B), Mistral-7B-Instruct (Mistral AI, 7.3B), Llama-2-7B-Chat-HF (Meta, 7B) and GPT-3.5-Turbo (OpenAI, 175B), and it is conducted across diverse defense strategies rather than against undefended models only. That two-dimensional design - attacks against multiple models under multiple defenses - lets the framework serve a dual purpose the paper claims explicitly: assessing the resilience of defense mechanisms and measuring the safety alignment of the models themselves, positioning automated red teaming as a measurement instrument rather than only an attack. Specific per-model or per-defense success rates are not surfaced in the extracted material. For this SoK the notable structural point is that an automated generator evaluated against a defense panel is exactly the adaptive-adversary capability whose absence this corpus repeatedly flags in defense papers - AutoRed is the kind of tool that would let those papers test robustness rather than assert it.</t>
         </is>
       </c>
       <c r="F282" s="5" t="n"/>
@@ -12019,7 +12031,7 @@
       <c r="H282" s="5" t="n"/>
       <c r="I282" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -12029,7 +12041,7 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
@@ -12044,7 +12056,7 @@
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>uDSR (state-of-the-art non-LLM-based symbolic regression framework), LLM-SR, OpenEvolve, CodeEvolve, and ShinkaEvolve (state-of-the-art LLM-driven evolutionary search frameworks, including the framework that produced state-of-the-art Circle Packing results), plus the raw PyTorch baseline and KernelBench Leaderboard v0.1 best-known kernels for the KernelBench experiments.</t>
+          <t>Human-generated red-team test cases represent the incumbent paradigm AutoRed is positioned to replace on cost and time grounds. Empirically, the framework is evaluated across six target LLMs and across diverse defense strategies, so the comparison axes are model and defense rather than competing automated red-teaming systems.</t>
         </is>
       </c>
       <c r="F283" s="5" t="n"/>
@@ -12052,7 +12064,7 @@
       <c r="H283" s="5" t="n"/>
       <c r="I283" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12074,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -12075,17 +12087,13 @@
           <t>freetext</t>
         </is>
       </c>
-      <c r="E284" s="2" t="inlineStr">
-        <is>
-          <t>N/A - non-adversarial. This is an evolutionary-search / automated-scientific-discovery systems paper (optimizing symbolic regression, GPU kernels, and neural-network training pipelines), not a security paper; there is no adversarial actor considered. The paper's central failure mode, 'Context Pollution,' is directly relevant to context-poisoning-adjacent research even though it is entirely non-adversarial: because successful discoveries are naturally sparse during evolutionary search, the agent's in-context experiment history rapidly saturates with failed attempts, and a self-reinforcing feedback loop causes the LLM to persist with flawed hypotheses even in the face of repeated negative results, degrading the signal-to-noise ratio of the context and biasing the model toward generating similar (unproductive) ideas rather than exploring diverse alternatives -- an unintentional, self-inflicted analog to how noisy or misleading accumulated context can corrupt an agent's downstream decision-making, distinct from any externally injected poisoning.</t>
-        </is>
-      </c>
+      <c r="E284" s="2" t="n"/>
       <c r="F284" s="5" t="n"/>
       <c r="G284" s="5" t="n"/>
       <c r="H284" s="5" t="n"/>
       <c r="I284" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12103,7 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
@@ -12110,7 +12118,7 @@
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>The paper has no dedicated 'Limitations' section and no explicit ethics/broader-impact statement in the extracted text. The closest analogs are experimental-design caveats noted inline: for the KernelBench evaluation, the authors state that due to higher evaluation cost and the need to cover a wide variety of kernels, they 'could not repeat the experiments multiple times' (unlike the LLM-SR and ablation experiments, which use 10 repeated runs to obtain result distributions), instead mitigating variance by comparing per-kernel timing individually; the appendix also notes that the stochastic nature of LLM decoding combined with evolutionary search 'necessitates multiple experimental repetitions to draw robust conclusions,' implicitly acknowledging that single-run or limited-repetition results (as used for KernelBench and Modded NanoGPT) carry more residual uncertainty than the repeated-run LLM-SR results. The ablation study itself surfaces an internal trade-off/limitation of one of the paper's own components: adding Momentum-Based Backtracking alone improves worst-case (stuck) runs but 'slightly affected the best-performing processes,' since backtracking forces more frequent exploration at the expense of budget for LLM-preferred exploitative refinement -- a limitation the paper addresses via the subsequent Collaborative Evolution Sampling component rather than leaving unresolved.</t>
+          <t>No explicit limitations section surfaced. The scope is privacy extraction from in-context conversation history, so results speak to data exfiltration rather than to goal hijacking or tool misuse, and generalization to agentic tool-calling settings is not established - the threat model is conversational rather than tool-mediated. Target models are those available in 2024 (including Llama-2 and GPT-3.5-Turbo), so measured alignment and defense resilience are perishable and may not characterize current models. Because the generator is trained with supervised fine-tuning and reinforcement learning against these targets, there is a risk that discovered attacks are tuned to the specific model panel rather than transferable, and no held-out model evaluation is surfaced to test that. Per-model and per-defense figures are not available in the extracted material.</t>
         </is>
       </c>
       <c r="F285" s="5" t="n"/>
@@ -12118,7 +12126,7 @@
       <c r="H285" s="5" t="n"/>
       <c r="I285" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12136,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -12143,7 +12151,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>This paper addresses instability in LLM-driven evolutionary search -- systems where an LLM iteratively proposes, executes, and reflects on candidate solutions to optimization problems (replacing the fixed random mutation/crossover operators of classical evolutionary algorithms with intelligent, context-aware reasoning) -- by identifying and systematically addressing three failure modes observed empirically across diverse research/engineering tasks: Context Pollution, where sparse successful discoveries cause the agent's accumulated experiment history to fill with failed trials, forming a self-reinforcing feedback loop that biases the LLM toward persisting with flawed hypotheses and degrading the context's signal-to-noise ratio; Mode Collapse, where agents stagnate in local minima due to poor exploration-exploitation balance, since summarized experiment histories used as context for future iterations bias LLMs toward generating similar rather than diverse ideas; and Weak Collaboration, where rigid, fixed crossover strategies fail to effectively transfer knowledge between parallel search trajectories (islands). The proposed framework, PACEvolve (Progress-Aware Consistent Evolution), addresses each failure mode with a corresponding mechanism: Hierarchical Context Management (HCM) decouples idea generation from idea selection and applies context pruning, maintaining a hierarchical idea memory (idea classification into hypotheses, idea selection, and pruning of low-performing entries) to combat context pollution and incentivize diverse idea generation; Momentum-Based Backtracking (MBB) monitors search momentum to provide a 'hard escape mechanism' that forces the system to break free from local minima when progress stalls, directly combating mode collapse; and Self-Adaptive Collaborative Evolution Sampling (CE) unifies internal backtracking (deep exploration within an island) with external crossover (knowledge transfer across parallel islands) via a search-control policy that dynamically balances the two based on monitored search momentum, resolving weak collaboration by enabling multiple concurrent explorations of promising regions once at least one island discovers a favorable direction. Evaluated across three benchmarks of increasing complexity -- symbolic regression (LLM-SR), GPU kernel optimization (KernelBench, 16 kernels), and full-stack language-model training-pipeline optimization (Modded NanoGPT, spanning architecture, distributed training, and kernel changes simultaneously) -- PACEvolve consistently and substantially outperforms prior state-of-the-art LLM-driven evolutionary search frameworks (ShinkaEvolve, OpenEvolve, CodeEvolve, LLM-SR) as well as a strong non-LLM symbolic-regression baseline (uDSR), and surpasses the prior best-known result on the heavily-optimized Modded NanoGPT benchmark through a sequence of discovered systems- and modeling-level innovations, with ablations confirming that all three of PACEvolve's components contribute complementary, non-redundant improvements to the overall evolutionary search recipe.</t>
+          <t>Presents AutoRed, a learning framework that automatically generates malicious attack scenarios for extracting sensitive information from LLMs, addressing the cost and time burden of red teaming that relies on human testers to hand-craft provocative test cases. The threat model is specifically privacy-oriented and in-context: sensitive information supplied during conversation is retained as in-context memory, and the attack aims to extract those conversation histories through injected prompts to uncover private data - so the target is not policy violation in the abstract but recovery of data the user themselves provided earlier in the session. AutoRed comprises three cooperating components: a malicious prompt generator producing candidate injection attempts, a sensitive information extractor recovering private content from the responses, and a stop point identifier determining when an attack sequence should terminate. That third component is the distinctive piece - automated red teaming otherwise struggles to know when a probing sequence has succeeded or should be abandoned, and making the stopping decision explicit is what allows the pipeline to run unattended. Training combines supervised fine-tuning and reinforcement learning. Relevant to this corpus as a memory/direct-input channel Track A attack whose consequence is data exfiltration - a consequence class RQ7 identifies as the worst-covered in the entire registry (1 of 9 mechanisms defended).</t>
         </is>
       </c>
       <c r="F286" s="5" t="n"/>
@@ -12151,7 +12159,7 @@
       <c r="H286" s="5" t="n"/>
       <c r="I286" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12250,7 +12258,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Seeing through the Conflict: Transparent Knowledge Conflict Handling in Retrieval-Augmented Generation</t>
+          <t>TracLLM: A Generic Framework for Attributing Long Context LLMs</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -12260,7 +12268,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>TCR (Transparent Conflict Resolution)</t>
+          <t>TracLLM</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -12270,7 +12278,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G2" s="5" t="n"/>
@@ -12279,7 +12287,7 @@
       <c r="J2" s="5" t="n"/>
       <c r="K2" s="5" t="inlineStr">
         <is>
-          <t>4c78b5e846a9de2f2fcfd854ad52641f1b2ced41</t>
+          <t>e8f42c742f2e6d3f570ec4ae4089309c64a61b24</t>
         </is>
       </c>
     </row>
@@ -12289,27 +12297,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KScope: A Framework for Characterizing the Knowledge Status of Language Models</t>
+          <t>Backdooring Instruction-Tuned Large Language Models with Virtual Prompt Injection</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>KScope-guided Constrained Context Summarization</t>
+          <t>Virtual Prompt Injection (VPI)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>supply-chain</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>silent-corruption</t>
+          <t>persistence-backdoor</t>
         </is>
       </c>
       <c r="G3" s="5" t="n"/>
@@ -12318,7 +12326,7 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>60c9fbcba72112937aba067ead90727f43108634</t>
+          <t>37665dd5ae7245f087d663785c17eef068578676</t>
         </is>
       </c>
     </row>
@@ -12328,27 +12336,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Securing AI Agents Against Prompt Injection Attacks</t>
+          <t>MemVenom: Triggered Poisoning of Multimodal Memories in Web Agents</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>UNNAMED: Three-layer defense pipeline for RAG PI (embedding content filtering + hierarchical guardrails + response verification)</t>
+          <t>MemVenom</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>persistence-backdoor</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
@@ -12357,7 +12365,7 @@
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>20d6d4a901b4b535e46e8a086c6a1f64e13948a4</t>
+          <t>cf4df6c19699a57b0bee87a490146ffc99c7c950</t>
         </is>
       </c>
     </row>
@@ -12367,27 +12375,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PRIMA: Operational Patterns for Resilient Multi-Agent Research with Verifiable Identity and Convergent Feedback</t>
+          <t>Document-Authored Control-Signal Impersonation: A Low-Cost Indirect Prompt Attack on RAG Safety Boundaries</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>PRIMA (context-boundary discipline + reference-material sandboxing + poisoned-output rejection)</t>
+          <t>DACSI (Document-Authored Control-Signal Impersonation)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>data-exfiltration</t>
         </is>
       </c>
       <c r="G5" s="5" t="n"/>
@@ -12396,7 +12404,7 @@
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>arxiv:2605.24775</t>
+          <t>c678482d8da6d9f65e629434caf99b6beafff8d7</t>
         </is>
       </c>
     </row>
@@ -12406,22 +12414,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>System-Level Defense against Indirect Prompt Injection Attacks: An Information Flow Control Perspective</t>
+          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>defense / fix</t>
+          <t>attack / failure mechanism</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>f-secure LLM system (information flow control)</t>
+          <t>AutoMalTool</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>tool-output</t>
+          <t>tool-metadata</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -12435,7 +12443,7 @@
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>19a45c70463edc755d54f3d5343e44cd571fe226</t>
+          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
         </is>
       </c>
     </row>
@@ -12445,7 +12453,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Learning What Not to Forget: Long-Horizon Agent Memory from a Few Kilobytes of Learning</t>
+          <t>Parameters vs. Context: Fine-Grained Control of Knowledge Reliance in Language Models</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -12455,17 +12463,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>LRE (Learned Relevance Eviction)</t>
+          <t>CK-PLUG (Controllable Knowledge Plug-in)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G7" s="5" t="n"/>
@@ -12474,7 +12482,7 @@
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>31adb0c460abf3be3ef65356cb072548cd586ccc</t>
+          <t>f0b199b7b9939cfd3d8bd69149d5bed7af40e0d2</t>
         </is>
       </c>
     </row>
@@ -12484,27 +12492,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Automatic Red Teaming LLM-Based Agents With Model Context Protocol Tools</t>
+          <t>End-to-End Context Compression at Scale</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>AutoMalTool</t>
+          <t>LCLM (Latent Context Language Models)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>tool-metadata</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>goal-hijack</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G8" s="5" t="n"/>
@@ -12513,7 +12521,7 @@
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>299ec08b60dbb993f96cf45c011c387477e3f9c8</t>
+          <t>842bcb12b16c0f6000fcbc88a140de703bb4acc9</t>
         </is>
       </c>
     </row>
@@ -12523,7 +12531,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>TRACE: Trajectory Risk-Aware Compression for Long-Horizon Agent Safety</t>
+          <t>RAG-Modulo: Solving Sequential Tasks using Experience, Critics, and Language Models</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -12533,12 +12541,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>TRACE (Trajectory Risk-Aware Compression)</t>
+          <t>RAG-Modulo</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -12552,7 +12560,7 @@
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>6792cb92e343acbf1ccb5edaf59647eb0b6e88c9</t>
+          <t>e06dda96ce8beac38be7d503faf18bb07051d340</t>
         </is>
       </c>
     </row>
@@ -12562,7 +12570,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>CLIOPATRA: Extracting Private Information from LLM Insights</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -12572,17 +12580,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Cliopatra</t>
+          <t>P2SQL injection (prompt-to-SQL)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>memory</t>
+          <t>direct-input</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>data-exfiltration</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -12591,7 +12599,7 @@
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>d45e2718c4ae41fb90436d97eb89542f525dbc1f</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -12601,17 +12609,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>From Prompt Injections to SQL Injection Attacks: How Protected is Your LLM-Integrated Web Application?</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>attack / failure mechanism</t>
+          <t>defense / fix</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Context Pollution (evolutionary search history bias)</t>
+          <t>UNNAMED: P2SQL mitigations (DB permission hardening + query rewriting)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -12621,7 +12629,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>goal-hijack</t>
         </is>
       </c>
       <c r="G11" s="5" t="n"/>
@@ -12630,7 +12638,7 @@
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>0894585294c67193ff3190240554677b56fd79a0</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12648,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve: Enabling Long-Horizon Progress-Aware Consistent Evolution</t>
+          <t>ReMEmbR: Building and Reasoning Over Long-Horizon Spatio-Temporal Memory for Robot Navigation</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -12650,17 +12658,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PACEvolve - Hierarchical Context Management (HCM) component specifically</t>
+          <t>ReMEmbR (Retrieval-augmented Memory for Embodied Robots)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>direct-input</t>
+          <t>memory</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>reasoning-corruption</t>
+          <t>silent-corruption</t>
         </is>
       </c>
       <c r="G12" s="5" t="n"/>
@@ -12669,19 +12677,97 @@
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>230ab088432e2fcc7e34b6148fd08fef30cb2077</t>
+          <t>2058a5f0e4ade9cfc5383c3aade29f9c5efbdd48</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Slipstream: Trajectory-Grounded Compaction Validation for Long-Horizon Agents</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>defense / fix</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Slipstream (asynchronous, judge-validated trajectory-grounded compaction)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>tool-output</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>reasoning-corruption</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>4faf0b5fdbfe974ae6e2c156371f422a1b6eda67</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>AutoRed: Automated Attack Scenario Generation Framework for Red Teaming of LLMs</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>attack / failure mechanism</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>AutoRed</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>direct-input</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>data-exfiltration</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>fb1bc7f717df24bef2a98d1dab26b0d86f069dd2</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="G2:G12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"yes,no,unclear"</formula1>
     </dataValidation>
   </dataValidations>
